--- a/data/output/corpus_run_v5_200/queries.xlsx
+++ b/data/output/corpus_run_v5_200/queries.xlsx
@@ -478,7 +478,7 @@
         <v>Make a little card thing where I can quickly jot down a new task, pick how urgent it is like low, medium, or high, and also tap to choose when it needs to be done by, kind of like a small calendar popup that lets me pick the date without typing it out, and the whole thing should feel simple enough that I actually want to use it every day for tracking my little project ideas.</v>
       </c>
       <c r="J2" t="str">
-        <v>做一个小卡片，让我能快速记下新任务，可以选紧急程度，比如低、中、高，还能点一下弹出个小日历来选截止日期，不用手动输入，整体要足够简洁，让我每天都愿意用它来记录自己的小项目想法。</v>
+        <v>做一个小卡片，让我能快速记下一个新任务，选一下紧急程度，比如低、中、高，还可以点一下选截止日期，就是弹出一个小日历那种，不用手动输入，整体要足够简洁，让我真的愿意每天用它来跟踪自己的一些小项目想法。</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -504,16 +504,16 @@
         <v>medium</v>
       </c>
       <c r="G3">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H3">
         <v>16032</v>
       </c>
       <c r="I3" t="str">
-        <v>Create a little page where I can fill out the details for an event I'm planning — like the name, date, and a spot to type in the address or drop a map pin for the location — and then I can add people I want to invite by typing their names or contact info, and each person gets a simple yes/no/maybe thing they can tap to let me know if they're coming or not.</v>
+        <v>Create an app where I can fill out the details for an event I'm planning — like the name, date, and a spot to type in the address or drop a map pin for the location — and then I can add people I want to invite by typing their names or contact info, and each person gets a simple yes/no/maybe thing they can tap to let me know if they're coming or not.</v>
       </c>
       <c r="J3" t="str">
-        <v>做一个小页面，让我能填写活动的基本信息——比如活动名称、日期，以及一个可以输入地址或在地图上点位置的地方——然后我可以通过输入姓名或联系方式来添加想邀请的人，每个人都有一个简单的"参加／不参加／待定"选项，点一下就能告诉我他们来不来。</v>
+        <v>做一个用来创建活动的应用，我可以填写活动名称、日期，还有一个地点栏，支持手动输入地址或者在地图上直接打点定位。然后我可以添加想邀请的人，输入他们的名字或联系方式，每个人都能看到一个"去／不去／待定"的选项，点一下就能告诉我他们是否参加。</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -539,16 +539,16 @@
         <v>medium</v>
       </c>
       <c r="G4">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H4">
         <v>19238</v>
       </c>
       <c r="I4" t="str">
-        <v>Make a little page where I can either point my phone camera at someone's business card or scan their WeChat QR code, and it'll automatically pull out their name, phone number, and company info and fill in a new contact form for me — I'm always losing paper cards at maker fairs and it'd be so handy to just snap and save without typing everything out by hand, so after the scan the fields should show up ready to edit in case something got read wrong before I hit save.</v>
+        <v>Make an app where I can either point my phone camera at someone's business card or scan their WeChat QR code, and it'll automatically pull out their name, phone number, and company info and fill in a new contact form for me — I'm always losing paper cards at maker fairs and it'd be so handy to just snap and save without typing everything out by hand, so after the scan the fields should show up ready to edit in case something got read wrong before I hit save.</v>
       </c>
       <c r="J4" t="str">
-        <v>做一个小页面，可以用手机摄像头扫名片或者扫微信二维码，自动识别出对方的姓名、电话和公司信息，然后帮我填好新建联系人的表单——我每次参加创客集市都会弄丢纸质名片，要是能直接拍一下就存起来、完全不用手动输入就太方便了，所以扫完之后各个字段要显示出来可以手动改一下，万一有识别错的地方能修正，确认没问题再点保存。</v>
+        <v>做一个这样的应用：我可以用手机摄像头对准别人的名片拍一下，或者直接扫他们的微信二维码，然后自动把姓名、电话和公司信息提取出来，帮我填好新建联系人的表单——我每次去创客集市都会弄丢纸质名片，要是能拍一下就保存下来、不用手动逐字输入就太方便了，所以扫描完之后各个字段要直接显示出来可以编辑，万一哪里识别错了我能在点保存之前改一改。</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -574,16 +574,16 @@
         <v>medium</v>
       </c>
       <c r="G5">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H5">
         <v>15489</v>
       </c>
       <c r="I5" t="str">
-        <v>Need a simple little page where I can save stuff I want to buy someday — like I type in the item name, paste a link to where I found it, and set a price I'd be happy paying, then if the price ever drops to that number it somehow pings me so I don't miss it, and I can always tap the link to jump straight to the shop page and check it out.</v>
+        <v>Need a simple app where I can save stuff I want to buy someday — like I type in the item name, paste a link to where I found it, and set a price I'd be happy paying, then if the price ever drops to that number it somehow pings me so I don't miss it, and I can always tap the link to jump straight to the shop app and check it out.</v>
       </c>
       <c r="J5" t="str">
-        <v>想做一个简单的小页面来记录心愿单，可以输入商品名称、粘贴商品链接，然后设定一个心理价位，如果价格降到这个数就能收到提醒，不错过降价；同时点击链接可以直接跳转到对应的购买页面去看看。</v>
+        <v>想要一个简单的应用，可以保存我以后想买的东西——就是输入商品名称、粘贴找到它的链接、设置一个我愿意接受的目标价格，然后一旦价格降到那个数字就能提醒我，不让我错过，还能随时点链接直接跳转到购物应用去看看。</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -615,10 +615,10 @@
         <v>19899</v>
       </c>
       <c r="I6" t="str">
-        <v>Create a workout log page where I can go back and fix mistakes in my records — like if I put the wrong weight or reps — and it keeps a little history of what I changed and lets me write a quick note explaining why I changed it, so next time I look back I'm not confused about why my numbers look weird.</v>
+        <v>Create a workout log app where I can go back and fix mistakes in my records — like if I put the wrong weight or reps — and it keeps a little history of what I changed and lets me write a quick note explaining why I changed it, so next time I look back I'm not confused about why my numbers look weird.</v>
       </c>
       <c r="J6" t="str">
-        <v>做一个训练记录页面，让我能回去修改之前填错的数据，比如重量或次数记错了，改完之后要保留一个修改历史，还能让我写一句备注说明为什么改，这样以后回头看的时候不会搞不清楚数据为啥对不上。</v>
+        <v>做一个健身记录的应用，能让我回去修改之前填错的数据——比如重量或者次数记错了——同时保留一份修改历史，记录每次改了什么内容，还能让我写一条简短的备注说明修改原因，这样以后回头翻记录的时候，看到数字对不上也不会一头雾水。</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -653,7 +653,7 @@
         <v>Build a mobile budget app where I can tap on any spending category like "food" or "transport" and rename it to whatever I actually call it, plus swap out the little picture next to it from a list of options, and while I'm doing that it immediately shows me what the updated name and picture will look like before I save — because right now I have to save first just to see if it looks wrong and then go back and fix it which is so annoying.</v>
       </c>
       <c r="J7" t="str">
-        <v>做一个手机记账应用，我可以点击任意支出分类，比如"餐饮"或者"交通"，然后把名字改成我自己习惯叫的那种，同时还能从一个图标列表里换掉旁边那个小图标——而且在我操作的时候，应用要实时显示改完之后的名称和图标是什么效果，不用等我保存才能看到。现在的问题是我每次都得先保存，看到显示效果不对再返回去改，真的很烦。</v>
+        <v>做一个手机记账应用，我可以点击任意支出分类，比如"餐饮"或"交通"，把名字改成我自己平时的叫法，还能从一个图标列表里换掉旁边那个小图标，而且在操作的时候就能实时看到改完之后名称和图标长什么样，不用等我保存之后才知道——因为现在每次都得先保存、发现效果不对、再退回去重改，真的很烦。</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -685,10 +685,10 @@
         <v>23561</v>
       </c>
       <c r="I8" t="str">
-        <v>Create a page where I can edit the time or date of an event I already set up, and right after I save the change, a little pop-up comes up asking whether I want to notify everyone who was invited — I'm so tired of having to message each person individually every time a meeting gets pushed back, so I just want a one-tap way to send everyone the updated info at once, with maybe a small text box where I can write a quick reason like "venue changed" before hitting send.</v>
+        <v>Create an app where I can edit the time or date of an event I already set up, and right after I save the change, a little pop-up comes up asking whether I want to notify everyone who was invited — I'm so tired of having to message each person individually every time a meeting gets pushed back, so I just want a one-tap way to send everyone the updated info at once, with maybe a small text box where I can write a quick reason like "venue changed" before hitting send.</v>
       </c>
       <c r="J8" t="str">
-        <v>做一个可以修改已有日程的时间或日期的页面，保存之后马上弹出一个小提示框，问我要不要通知所有被邀请的人——我真的烦透了每次会议往后推都要一个个手动发消息，就想要一个一键把更新信息发给所有人的方式，最好在发送前还有个小文本框可以填一句简短的原因，比如"地点有变"之类的，填完直接点发送就行。</v>
+        <v>做一个可以修改已创建活动的时间或日期的应用，保存更改后立刻弹出一个小提示，询问我是否要通知所有受邀人员——我真的太烦每次会议改期都要一个个手动发消息了，就想要一个一键发送的方式，把更新后的信息同时推给所有人，最好还能有个小文本框让我在发送前简单写一下原因，比如"场地有变"之类的。</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -720,10 +720,10 @@
         <v>18000</v>
       </c>
       <c r="I9" t="str">
-        <v>Make a travel itinerary screen where I can just grab a day and drag it to a different spot in the schedule to reorder things, because right now I have to delete and redo everything manually whenever plans change and it's such a pain — and if moving a day causes some timing clash like two things overlapping or a booking that no longer makes sense, just flag it right there so I don't end up with a broken trip without realizing it.</v>
+        <v>Make a travel itinerary app where I can just grab a day and drag it to a different spot in the schedule to reorder things, because right now I have to delete and redo everything manually whenever plans change and it's such a pain — and if moving a day causes some timing clash like two things overlapping or a booking that no longer makes sense, just flag it right there so I don't end up with a broken trip without realizing it.</v>
       </c>
       <c r="J9" t="str">
-        <v>做一个旅行行程页面，让我可以直接拖住某一天拖到日程里的其他位置来调整顺序，因为现在每次计划有变动我都得手动删掉再重排，太麻烦了——另外，如果拖动某天之后出现时间冲突，比如两个安排撞在一起，或者某个预订变得不合理，就直接在原地标出来提醒我，别让我到最后才发现整个行程已经乱掉了。</v>
+        <v>做一个旅行行程规划的应用，我想直接拖住某一天然后拖到日程里的其他位置来调整顺序，因为现在每次计划有变动我都得手动删掉重新填，实在太麻烦了——另外如果挪动某天之后出现时间冲突，比如两个安排撞在一起、或者某个预订变得不合理了，就直接在原地提示我一下，别让我到最后才发现整个行程已经乱掉了。</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -755,10 +755,10 @@
         <v>21238</v>
       </c>
       <c r="I10" t="str">
-        <v>A search screen where you pick a bunch of filters first — like category, price range, or location — before you even start typing, and then every filter you've picked shows up as a small removable label right above the results so you can actually see what's active without having to remember. I always forget what I filtered by and then wonder why the results look weird, so it needs to be really clear which filters are on, and tapping one of those labels should immediately drop it and refresh the results without making me start over from scratch.</v>
+        <v>A search app where you pick a bunch of filters first — like category, price range, or location — before you even start typing, and then every filter you've picked shows up as a small removable label right above the results so you can actually see what's active without having to remember. I always forget what I filtered by and then wonder why the results look weird, so it needs to be really clear which filters are on, and tapping one of those labels should immediately drop it and refresh the results without making me start over from scratch.</v>
       </c>
       <c r="J10" t="str">
-        <v>做一个搜索页面，进来之后先选筛选条件——比如分类、价格区间、位置之类的——还没开始打字就先把条件定好，然后所有选中的筛选项都以小标签的形式显示在结果列表上方，可以单独删除，这样一眼就能看出当前开了哪些筛选，不用靠脑子记。我经常忘了自己筛了什么，然后搞不懂结果为什么那么奇怪，所以哪些筛选是激活状态一定要显示得很清楚，点某个标签就直接把那个条件移掉并刷新结果，不能让我从头重来。</v>
+        <v>一个搜索应用，用户在开始输入之前就能先选好一堆筛选条件——比如分类、价格区间或者位置，选完之后，所有已选的筛选项会以小标签的形式显示在结果列表正上方，这样就能一眼看清哪些条件是生效的，不用靠自己去记。我老是忘了自己筛了什么，然后搞不懂为什么结果看起来很奇怪，所以一定要让当前生效的筛选条件一目了然，而且点击某个标签就能立刻把它移除并刷新结果，不需要重新从头开始操作。</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -793,7 +793,7 @@
         <v>Need a way to save a search so the app just keeps watching it in the background and pushes me a notification whenever new results pop up, because I'm tired of having to open the app and type the same thing every single day just to check if anything changed — it should let me save a few different searches at once and the notification should actually show me what the new result is so I don't have to tap into the app just to find out it's something useless.</v>
       </c>
       <c r="J11" t="str">
-        <v>想要一个能保存搜索条件的功能，让应用在后台持续监控，一旦有新结果就直接推送通知给我，因为我实在不想每天都要打开应用、重新输入一遍同样的关键词去看看有没有新东西——应该支持同时保存好几个不同的搜索条件，而且通知里要直接显示新结果的内容，这样我就不用点进去才发现根本不是我想要的东西。</v>
+        <v>想要一个能保存搜索条件的功能，让应用在后台一直监控着，一旦有新结果就直接推送通知给我，因为我实在烦透了每天都得打开应用、重新输入同样的关键词去看看有没有什么新东西——应该支持同时保存几个不同的搜索条件，而且通知里要直接显示新结果的内容，这样我就不用点进去才发现根本不是我想要的东西。</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -825,10 +825,10 @@
         <v>37193</v>
       </c>
       <c r="I12" t="str">
-        <v>Create a search feature for a mobile app where I can just search inside one specific folder or album instead of getting results from everything — I have like dozens of folders and it's so annoying when I type something and get a hundred mixed results from all over the place, I just want to tap into a folder first and then search only within that, with the results showing the file name and maybe a small preview so I can find the right one fast without scrolling forever.</v>
+        <v>Create a search tool for a mobile app where I can just search inside one specific folder or album instead of getting results from everything — I have like dozens of folders and it's so annoying when I type something and get a hundred mixed results from all over the place, I just want to tap into a folder first and then search only within that, with the results showing the file name and maybe a small preview so I can find the right one fast without scrolling forever.</v>
       </c>
       <c r="J12" t="str">
-        <v>给移动端 app 做一个搜索功能，可以先进入某个特定文件夹或相册，然后只在这个范围内搜索，而不是每次都把所有地方的结果全混在一起返回——我有几十个文件夹，每次随便输个关键词就跳出来一大堆乱七八糟的结果，真的很烦。我想要的效果是先点进某个文件夹，再在里面搜，搜索结果要能显示文件名，最好还有个小缩略图预览，这样我不用一直往下翻也能快速找到想要的那个文件。</v>
+        <v>帮我做一个手机应用里的搜索功能，可以先选定某个特定文件夹或相册，然后只在这个范围内搜索，而不是一搜就把所有地方的结果全混在一起——我有几十个文件夹，每次输个关键词就蹦出来一堆乱七八糟的结果，真的很烦。我想要的效果是先点进某个文件夹，再在里面搜，搜索结果要显示文件名，最好还有个小缩略图预览，这样我不用一直滑来滑去就能快速找到想要的文件。</v>
       </c>
       <c r="K12" t="str">
         <v/>
@@ -860,10 +860,10 @@
         <v>19659</v>
       </c>
       <c r="I13" t="str">
-        <v>Search bar that automatically remembers what I've looked up before and also shows what's trending right now — when I tap into it, my last few searches show up immediately at the top so I don't have to retype the same stuff every single day, and below that a section for popular searches other people are doing a lot lately. As soon as I start typing even just one or two letters, it should filter and suggest matching things from both my own history and the trending list so I can just tap instead of typing the whole thing out.</v>
+        <v>Search bar that automatically remembers what I've looked up before and also shows what's trending right now — when I tap into it, my last few searches show up immediately at the top so I don't have to retype the same stuff every single day, and below that an app for popular searches other people are doing a lot lately. As soon as I start typing even just one or two letters, it should filter and suggest matching things from both my own history and the trending list so I can just tap instead of typing the whole thing out.</v>
       </c>
       <c r="J13" t="str">
-        <v>搜索框要能自动记住我之前查过的内容，同时显示当前热门搜索——点进去的时候，最近几条历史记录要直接出现在顶部，这样我就不用每天重复输入同样的东西了；下面再单独列一块"大家都在搜"的热门内容区域。只要我开始打字，哪怕就输入一两个字母，就应该同时从我的历史记录和热门列表里过滤出匹配的建议，直接点一下就能用，不用把整个词都打完。</v>
+        <v>搜索框要能自动记住我之前搜过的内容，同时还能显示当前热门搜索——点进去的时候，最近几条历史记录要立刻出现在最上面，这样我就不用每天重复输入同样的东西了，下面再展示一个近期大家搜得比较多的热门词区域。只要我开始打字，哪怕就输了一两个字母，就应该同时从我的搜索历史和热门列表里过滤出匹配的建议项，让我直接点选就行，不用把整个词都打完。</v>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -895,10 +895,10 @@
         <v>23064</v>
       </c>
       <c r="I14" t="str">
-        <v>Build a dropdown picker for a mobile app where users can search through a long list of options that are neatly grouped into categories, so instead of scrolling through everything mixed together, you see things like "Fruits" with its items listed under it, then "Vegetables" with its items under that, and so on — I want a search box at the top so you can just type a few letters and it filters down to matching results across all the groups, and the group headings should stay visible so you still know which section each result belongs to, and once you tap an option it shows your selection clearly at the top of the picker so it's easy to confirm what you picked.</v>
+        <v>Build a dropdown picker for a mobile app where users can search through a long list of options that are neatly grouped into categories, so instead of scrolling through everything mixed together, you see things like "Fruits" with its items listed under it, then "Vegetables" with its items under that, and so on — I want a search box at the top so you can just type a few letters and it filters down to matching results across all the groups, and the group headings should stay visible so you still know which app each result belongs to, and once you tap an option it shows your selection clearly at the top of the picker so it's easy to confirm what you picked.</v>
       </c>
       <c r="J14" t="str">
-        <v>帮我做一个移动端的下拉选择器，用户可以在里面搜索一个很长的选项列表，这些选项要按分类整齐地分组展示，不是把所有东西混在一起让用户上下滑，而是"水果"这个分组下面列出它的选项，然后"蔬菜"分组下面列出它的选项，依此类推——顶部要有一个搜索框，用户输入几个字就能跨所有分组过滤出匹配的结果，过滤后分组标题要保持可见，这样用户还能知道每条结果属于哪个分类，点击某个选项之后，所选内容要醒目地显示在选择器顶部，方便用户确认自己选了什么。</v>
+        <v>帮我做一个移动端的下拉选择器，用户可以在里面搜索一个很长的选项列表，这些选项按分类整齐地分好了组，这样就不用把所有东西混在一起上下滚，而是能看到比如"水果"下面列着它的选项，然后"蔬菜"下面列着它的选项，依此类推——我希望顶部有个搜索框，输入几个字就能跨所有分组筛选出匹配的结果，而且分组标题要一直显示，这样你还能知道每条结果属于哪个分类，点击某个选项之后，在选择器顶部要清晰地显示出你选中的内容，方便确认。</v>
       </c>
       <c r="K14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Build a calendar date-range picker for a mobile app where I can tap a start date and then tap an end date, and all the days in between automatically get a colored highlight so I can see the whole span at a glance — I want the first and last days to look clearly marked with a solid circle or stronger color, and all the days in the middle to show a lighter shaded strip connecting them, so it's easy to tell exactly which dates I've selected without having to count manually.</v>
       </c>
       <c r="J15" t="str">
-        <v>帮我做一个移动端的日历日期区间选择器，支持先点选开始日期、再点选结束日期，两者之间的所有日期自动高亮显示，让我一眼就能看清整段时间范围——首尾两天要用实心圆或更深的颜色明确标出，中间的日期则用一条颜色较浅的色带串联起来，这样不用手动数日子就能清楚知道自己选了哪些日期。</v>
+        <v>帮我在移动端做一个日期区间选择器，点一下起始日期、再点一下结束日期，中间所有的日子自动高亮显示，让我一眼就能看清整个选区范围——起始日和结束日要用实心圆或者更深的颜色明显标出来，中间的日期则用一条颜色较浅的色带连起来，这样不用手动数格子，一眼就能知道自己选了哪些日期。</v>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -965,10 +965,10 @@
         <v>55149</v>
       </c>
       <c r="I16" t="str">
-        <v>A photo grid for picking multiple images at once, where each image you tap gets a small numbered badge in the corner showing the order you selected it — like 1, 2, 3 in sequence — so you always know which ones you picked and in what order. The grid should display images in equal-sized squares, three per row, and selected ones should stay visibly highlighted so it's easy to see at a glance what's already chosen. There should also be a running total count shown at the bottom of the screen that updates as you tap, so I never have to count manually.</v>
+        <v>A photo grid for picking multiple images at once, where each image you tap gets a small numbered badge in the corner showing the order you selected it — like 1, 2, 3 in sequence — so you always know which ones you picked and in what order. The grid should display images in equal-sized squares, three per row, and selected ones should stay visibly highlighted so it's easy to see at a glance what's already chosen. There should also be a running total count shown at the bottom of the app that updates as you tap, so I never have to count manually.</v>
       </c>
       <c r="J16" t="str">
-        <v>做一个支持多选的照片网格，每次点击一张图片，图片角落就会出现一个小数字角标，按照点击的先后顺序显示序号，比如1、2、3，这样随时都能知道选了哪些、顺序是什么。网格里的图片要以等比例正方形展示，每行排三张，选中的图片要保持明显的高亮状态，一眼就能看出哪些已经选过了。屏幕底部还要有一个实时更新的已选数量汇总，每点一张就自动刷新，不用自己手动去数。</v>
+        <v>做一个可以批量选图的照片网格，每张点击后在角落显示一个小数字徽标，按顺序标注1、2、3……这样随时都能看出选了哪些、选的顺序是什么。网格按三列排列，每格是等大的正方形，选中的图片要保持高亮状态，一眼就能看出哪些已经选过了。底部还要有一个实时更新的已选总数，点一张加一张，不用自己数。</v>
       </c>
       <c r="K16" t="str">
         <v/>
@@ -1000,10 +1000,10 @@
         <v>21993</v>
       </c>
       <c r="I17" t="str">
-        <v>Build a color swatch picker page where I can tap any color block and instantly see the hex code and the color name show up right underneath — I want the swatches laid out in a neat grid, the selected one should clearly stand out so I know which one I picked, and the hex code plus the color name need to update right away every time I switch to a different swatch with no lag at all.</v>
+        <v>Build a color swatch picker app where I can tap any color block and instantly see the hex code and the color name show up right underneath — I want the swatches laid out in a neat grid, the selected one should clearly stand out so I know which one I picked, and the hex code plus the color name need to update right away every time I switch to a different swatch with no lag at all.</v>
       </c>
       <c r="J17" t="str">
-        <v>做一个色卡选色页面，点击任意色块后能立刻在下方看到对应的 hex 色值和颜色名称——色块要整齐地排列成网格，选中的那个要有明显的高亮效果让我一眼就能看出来是哪个，而且每次切换色块时 hex 值和颜色名称都要即时更新，不能有任何卡顿。</v>
+        <v>做一个色卡取色器应用，点击任意色块后，下方能立刻显示对应的十六进制色值和颜色名称——所有色块要以整齐的网格排列展示，选中的那个要有明显的突出效果，让我一眼就能看出当前选的是哪个，并且每次切换色块时，色值和颜色名称必须即时刷新，不能有任何卡顿或延迟。</v>
       </c>
       <c r="K17" t="str">
         <v/>
@@ -1035,10 +1035,10 @@
         <v>17343</v>
       </c>
       <c r="I18" t="str">
-        <v>Create a map page where I can just drag a circle to set how far I want to search — like if I only want to see stuff within 2km or 5km around me, I can adjust that range right on the map without having to type in addresses or go back to some separate filter menu, and whatever's inside the circle shows up as results right away so I don't have to keep going back and forth.</v>
+        <v>Create a map app where I can just drag a circle to set how far I want to search — like if I only want to see stuff within 2km or 5km around me, I can adjust that range right on the map without having to type in addresses or go back to some separate filter menu, and whatever's inside the circle shows up as results right away so I don't have to keep going back and forth.</v>
       </c>
       <c r="J18" t="str">
-        <v>做一个地图页面，我可以直接在地图上拖动一个圆圈来设定搜索范围——比如我只想看周围2公里或5公里以内的内容，就直接在地图上调整这个范围，不用手动输入地址，也不用跑去单独的筛选菜单里改，圆圈里的结果直接实时显示出来，不用来来回回切换页面。</v>
+        <v>做一个地图应用，让我可以直接在地图上拖动一个圆圈来设置搜索范围——比如我只想看周围2公里或5公里以内的内容，直接在地图上调整这个范围就行，不用手动输入地址，也不用跑去单独的筛选菜单里设置，圆圈里面的结果马上就能显示出来，不用反复来回切换。</v>
       </c>
       <c r="K18" t="str">
         <v/>
@@ -1073,7 +1073,7 @@
         <v>Need a filter thing where I can pick multiple tags and switch between "show results that match ALL of these tags" vs "show results that match ANY of these tags" — like a little toggle button somewhere obvious so I can flip between the two modes without having to clear everything and start over, because right now I keep having to redo my whole search just to widen or narrow the results and it's driving me crazy.</v>
       </c>
       <c r="J19" t="str">
-        <v>需要一个筛选组件，可以同时选多个标签，然后能在"匹配所有标签"和"匹配任意标签"这两种模式之间切换——在显眼的地方放一个小切换按钮，这样我就能直接在两种模式间来回切，不用把已选的条件全清掉重来。现在每次想扩大或缩小筛选范围都得把整个搜索重做一遍，真的很烦。</v>
+        <v>需要做一个筛选功能，让我能同时选多个标签，然后在"匹配所有标签"和"匹配任意标签"这两种模式之间来回切换——在显眼的地方放一个小切换按钮，这样我不用清空所有条件重头来过，直接就能宽泛或收窄筛选范围。现在每次想调整一下范围都得把整个搜索重做一遍，真的很烦。</v>
       </c>
       <c r="K19" t="str">
         <v/>
@@ -1105,10 +1105,10 @@
         <v>13738</v>
       </c>
       <c r="I20" t="str">
-        <v>Make a simple sorting dropdown for a mobile page where I can switch between relevance, date, rating, and distance without having to reload the whole page or dig through menus — I just want to tap one button, pick how I want things sorted, and have the list instantly reorder itself, nothing fancy, just something that actually works fast so I stop wasting time scrolling through stuff that's not what I need.</v>
+        <v>Make a simple sorting dropdown for a mobile app where I can switch between relevance, date, rating, and distance without having to reload the whole app or dig through menus — I just want to tap one button, pick how I want things sorted, and have the list instantly reorder itself, nothing fancy, just something that actually works fast so I stop wasting time scrolling through stuff that's not what I need.</v>
       </c>
       <c r="J20" t="str">
-        <v>给移动端页面做一个简单的排序下拉菜单，可以在相关性、日期、评分和距离之间切换，不用刷新整个页面，也不用翻来翻去找菜单——就是点一下按钮，选好排序方式，列表马上重新排好，不需要多花哨，只要用起来够快就行，省得我一直在一堆不相关的内容里刷个没完。</v>
+        <v>给移动端做一个简单的排序下拉菜单，可以在相关性、日期、评分和距离之间切换，不用重新加载整个应用，也不用翻来翻去找菜单——就是点一下按钮，选好排序方式，列表马上重新排列，不需要什么花里胡哨的效果，就要能用、反应快，别让我再浪费时间刷一堆不想看的内容。</v>
       </c>
       <c r="K20" t="str">
         <v/>
@@ -1140,10 +1140,10 @@
         <v>17953</v>
       </c>
       <c r="I21" t="str">
-        <v>Create a page where I can drag items around to set my own ranking order — I keep having to filter through a long list every day and the default sorting is never what I actually want, so I just want to grab each item and drag it up or down to a specific spot, with a little number on the side showing its rank so I can see the order clearly, and once I'm done arranging everything it saves that custom order so I don't have to redo it next time I open the app.</v>
+        <v>Create an app where I can drag items around to set my own ranking order — I keep having to filter through a long list every day and the default sorting is never what I actually want, so I just want to grab each item and drag it up or down to a specific spot, with a little number on the side showing its rank so I can see the order clearly, and once I'm done arranging everything it saves that custom order so I don't have to redo it next time I open the app.</v>
       </c>
       <c r="J21" t="str">
-        <v>做一个可以拖拽排序的页面，我每天都要翻一个很长的列表，默认排序完全不是我想要的顺序，所以我希望能直接用手拖住每一项，把它拖到想放的位置，左边或右边显示一个序号，这样能一眼看清当前的排列顺序，全部调整好之后把这个自定义顺序保存下来，下次打开应用不用重新排。</v>
+        <v>做一个可以拖拽排序的应用，让我能自己定义列表的排列顺序——我每天都要在一个很长的列表里翻来翻去，默认的排序完全不是我想要的，所以我就想直接用手拖住每一项，把它拖上去或者拖下去放到指定位置，旁边显示一个小序号，方便我直观地看到当前的排名，调整完之后自动保存这个自定义顺序，下次再打开应用的时候不用重新排一遍。</v>
       </c>
       <c r="K21" t="str">
         <v/>
@@ -1175,10 +1175,10 @@
         <v>13298</v>
       </c>
       <c r="I22" t="str">
-        <v>Make a delete screen for a task management app where if I try to remove a project that still has tasks under it, it shows me a warning telling me exactly what's gonna get affected, and then gives me two clear choices — either delete just the project and keep the tasks somewhere, or wipe everything related to it all at once so I don't have to go clean up the mess manually afterward.</v>
+        <v>Make a delete app for a task management app where if I try to remove a project that still has tasks under it, it shows me a warning telling me exactly what's gonna get affected, and then gives me two clear choices — either delete just the project and keep the tasks somewhere, or wipe everything related to it all at once so I don't have to go clean up the mess manually afterward.</v>
       </c>
       <c r="J22" t="str">
-        <v>帮我做一个任务管理应用的删除页面，当我尝试删除一个底下还有任务的项目时，页面要弹出一个警告，明确告诉我具体哪些内容会受到影响，然后给我两个清晰的选项——要么只删除项目、把里面的任务保留到某个地方，要么直接把项目和所有相关内容一次性全部清掉，省得我事后还要手动去收拾残局。</v>
+        <v>帮我给任务管理应用做一个删除功能，当我想删除一个底下还有任务的项目时，先弹出一个警告，清楚地告诉我哪些内容会受到影响，然后给我两个明确的选项——要么只删除项目本身、把任务保留到别的地方，要么直接把所有相关的东西一次性全清掉，省得我事后还要手动去收拾烂摊子。</v>
       </c>
       <c r="K22" t="str">
         <v/>
@@ -1213,7 +1213,7 @@
         <v>Create a delete thing for a to-do list where you hold your finger down on any item to start deleting it — the phone should give a little vibration buzz when you do that, and then the item should shake left and right like it's asking "are you sure?" before it actually goes away, so I don't keep accidentally killing stuff I still need just by tapping in the wrong spot.</v>
       </c>
       <c r="J23" t="str">
-        <v>帮我在待办清单里做一个删除功能，长按任意条目就能触发——长按的瞬间手机要轻轻震动一下，然后那个条目左右抖动，像是在问"你真的要删吗？"确认之后才真正消失，这样就算手滑点到也不会一下子把还有用的东西给误删掉。</v>
+        <v>给待办事项列表做一个删除功能，长按任意条目就能触发删除——按下去的时候手机要有一下震动反馈，然后那个条目要左右抖动一下，像在问"你确定吗？"之后再真正删掉，这样我就不会因为不小心点错地方把还有用的东西给误删了。</v>
       </c>
       <c r="K23" t="str">
         <v/>
@@ -1245,10 +1245,10 @@
         <v>16699</v>
       </c>
       <c r="I24" t="str">
-        <v>Create a page where I can drag stuff I want to delete into a trash area at the bottom of the screen to get rid of it — I'm so tired of tapping each item and going through a confirm popup every single time just to clean up a list. I want to grab an item, drag it down, and when it hovers over the trash zone that area glows or shakes a little so I know it's ready, then I just drop it and it disappears right away without any extra steps.</v>
+        <v>Create an app where I can drag stuff I want to delete into a trash area at the bottom of the app to get rid of it — I'm so tired of tapping each item and going through a confirm popup every single time just to clean up a list. I want to grab an item, drag it down, and when it hovers over the trash zone that area glows or shakes a little so I know it's ready, then I just drop it and it disappears right away without any extra steps.</v>
       </c>
       <c r="J24" t="str">
-        <v>做一个页面，让我可以把想删除的东西直接拖到屏幕底部的垃圾桶区域来删除——我真的受够了每次都要点一下item、再弹出确认框才能清理列表这种操作。我想直接长按拖动某个条目，往下拽到垃圾桶区域的时候，那块区域能发光或者轻微抖动一下，让我知道可以放了，然后一松手就直接消失，不需要任何多余的步骤。</v>
+        <v>做一个可以把要删除的东西直接拖到底部垃圾区来清除的应用——我真的受够了每次都要点击每个条目、还要经过一个确认弹窗才能删掉，就为了清理个列表。我想直接抓住一个条目往下拖，拖到垃圾区上方的时候那个区域能发光或者轻微抖动一下，让我知道可以放了，然后直接松手它就消失，不需要任何多余的步骤。</v>
       </c>
       <c r="K24" t="str">
         <v/>
@@ -1280,10 +1280,10 @@
         <v>11153</v>
       </c>
       <c r="I25" t="str">
-        <v>Make a page where I can delete something off a shared shopping or to-do list and it automatically lets the other person know what got removed, so they don't text me asking why the item disappeared — I just want a simple remove button and a little note that goes out to whoever else is on the list saying what was deleted and roughly when, nothing fancy, just enough so nobody gets confused.</v>
+        <v>Make an app where I can delete something off a shared shopping or to-do list and it automatically lets the other person know what got removed, so they don't text me asking why the item disappeared — I just want a simple remove button and a little note that goes out to whoever else is on the list saying what was deleted and roughly when, nothing fancy, just enough so nobody gets confused.</v>
       </c>
       <c r="J25" t="str">
-        <v>做一个页面，可以从共享的购物清单或待办清单里删除某个条目，删完之后自动通知其他人删了什么，这样他们就不会发消息来问我为什么那个东西不见了——就要一个简单的删除按钮，然后自动给清单里的其他人发一条小提示，说明删了什么、大概什么时候删的，不需要搞得很复杂，够用就行，别让人看了一头雾水就好。</v>
+        <v>帮我做一个可以从共享购物清单或待办列表里删东西的应用，删完之后自动通知其他人删了什么，这样他们就不会发消息问我为什么那个条目不见了——就是一个简单的删除按钮，然后自动给列表里的其他人发一条小提示，说明删了什么、大概什么时候删的，不用搞得很复杂，够用、不让人困惑就行。</v>
       </c>
       <c r="K25" t="str">
         <v/>
@@ -1315,10 +1315,10 @@
         <v>12767</v>
       </c>
       <c r="I26" t="str">
-        <v>Build a profile editing screen where the location privacy section feels really considered and intentional — like instead of a clunky dropdown or boring radio buttons, there's a sleek little row of three choices (city, country, hidden) that you tap between, and whichever one is active glows or shifts in a way that feels satisfying, almost like those pill-style selectors you see on really polished lifestyle apps, with soft color transitions and maybe a subtle lock icon fading in when you pick "hidden" so it visually communicates the idea of keeping things close to your chest without needing to spell it out with text.</v>
+        <v>Build a profile editing app where the location privacy app feels really considered and intentional — like instead of a clunky dropdown or boring radio buttons, there's a sleek little row of three choices (city, country, hidden) that you tap between, and whichever one is active glows or shifts in a way that feels satisfying, almost like those pill-style selectors you see on really polished lifestyle apps, with soft color transitions and maybe a subtle lock icon fading in when you pick "hidden" so it visually communicates the idea of keeping things close to your chest without needing to spell it out with text.</v>
       </c>
       <c r="J26" t="str">
-        <v>做一个个人资料编辑页面，位置隐私这一块要有设计感、有质感——不要那种笨重的下拉菜单，也不要无聊的单选按钮，而是做一排三个选项（城市、国家、隐藏），点击就能在里面来回切换，选中哪个就哪个亮起来或者产生一个位移动效，点下去要有那种很爽的感觉，就像那些精致的生活类 App 上常见的胶囊式选择器，带柔和的颜色过渡，然后当用户点到"隐藏"那一项时，最好有个小锁头图标轻轻淡入，视觉上直接传达出"保密"的意思，不用加任何文字说明也能让人一眼秒懂。</v>
+        <v>做一个个人资料编辑应用，希望位置隐私这块的设计能真的经过深思熟虑、有设计感——不要那种笨重的下拉菜单或无聊的单选按钮，而是一排简洁的三个选项（城市、国家、隐藏），点击就能切换，选中的那个会发光或有位移感，整体交互很有满足感，有点像那些精致的生活方式类 App 上常见的胶囊式选择器，带柔和的颜色过渡动效，选到「隐藏」的时候还能有个小锁图标淡入进来，不用任何文字说明就能在视觉上传达出把事情藏在心里的那种感觉。</v>
       </c>
       <c r="K26" t="str">
         <v/>
@@ -1350,10 +1350,10 @@
         <v>21021</v>
       </c>
       <c r="I27" t="str">
-        <v>Create a section inside the profile editing flow where people can choose exactly which types of notifications they want to receive — like separately controlling messages, activity updates, promotions, and reminders — and make it feel really refined and intentional, not like a plain list of on/off switches. The whole thing should have a calm, editorial vibe with soft separators between each category, maybe subtle icons that feel cohesive and considered, and the active versus inactive states should look visually distinct in a tasteful way, like the difference between a highlighted bookmark and a greyed-out one — not just a color swap but something that feels designed.</v>
+        <v>Create an app inside the profile editing flow where people can choose exactly which types of notifications they want to receive — like separately controlling messages, activity updates, promotions, and reminders — and make it feel really refined and intentional, not like a plain list of on/off switches. The whole thing should have a calm, editorial vibe with soft separators between each category, maybe subtle icons that feel cohesive and considered, and the active versus inactive states should look visually distinct in a tasteful way, like the difference between a highlighted bookmark and a greyed-out one — not just a color swap but something that feels designed.</v>
       </c>
       <c r="J27" t="str">
-        <v>在个人资料编辑流程里加一个通知偏好设置模块，让用户可以分别控制自己想接收哪些类型的通知——比如消息、动态更新、推广内容、提醒等各自独立管理——整体风格要有质感、有设计感，不能做成那种普通的开关列表的感觉。整个区域希望有一种沉静、editorial 的氛围，每个分类之间用柔和的分隔线隔开，配上风格统一、克制考究的小图标，开启和关闭状态在视觉上要有明显区分，但要做得有品位——就像一个高亮书签和一个灰掉的书签之间的差别那种感觉，不只是换个颜色，而是真正有设计语言在里面。</v>
+        <v>在个人资料编辑流程中设计一个通知偏好设置页面，让用户可以精细地控制自己想接收哪些类型的通知——比如分别管理私信提醒、动态更新、推广活动和日程提醒——整体感觉要精致、有设计感，绝对不能是那种普通的开关列表。整个页面要有一种沉静、有质感的编辑风格，各分类之间用柔和的分隔线区隔，配上统一而克制的小图标，开启和关闭两种状态在视觉上要有明显但不突兀的区分，就像一个高亮书签和一个置灰书签之间的差异——不只是换个颜色，而是真正经过设计打磨的那种感觉。</v>
       </c>
       <c r="K27" t="str">
         <v/>
@@ -1385,10 +1385,10 @@
         <v>17372</v>
       </c>
       <c r="I28" t="str">
-        <v>Need a privacy setting section in my profile edit page that feels really considered and editorial — like three distinct audience tiers (public, followers only, private) shown as soft pill-shaped choices that glow or shift in a warm muted tone when selected, not just plain radio buttons. The whole thing should feel intentional and calm, almost like choosing who gets to read your journal, with maybe a tiny icon or subtle texture for each option that hints at openness versus intimacy without being loud about it.</v>
+        <v>Need a privacy setting app in my profile edit app that feels really considered and editorial — like three distinct audience tiers (public, followers only, private) shown as soft pill-shaped choices that glow or shift in a warm muted tone when selected, not just plain radio buttons. The whole thing should feel intentional and calm, almost like choosing who gets to read your journal, with maybe a tiny icon or subtle texture for each option that hints at openness versus intimacy without being loud about it.</v>
       </c>
       <c r="J28" t="str">
-        <v>想在个人资料编辑页里加一个隐私设置模块，整体要有种经过精心考量的质感，像是杂志排版那种调性——用三个层级来区分受众（公开、仅粉丝可见、私密），以柔和的胶囊形标签来呈现，选中时能发出微微的暖色光晕或色调偏移，而不是普普通通的单选按钮。整个模块要给人一种从容而克制的感觉，就像在慎重地选择谁能翻开你的日记，每个选项可以配一个小图标或淡淡的纹理，隐隐透出开放与私密之间的差异，但不要太刻意、太抢眼。</v>
+        <v>想在个人资料编辑页里加一个隐私设置模块，整体风格要有那种经过精心打磨的质感，像杂志版面一样考究——把"公开""仅关注者""私密"三个受众层级做成柔和的胶囊形选项，选中时带有微微发光或切换到温暖低饱和色调的效果，不要用普通单选按钮那种感觉。整体氛围要克制、沉静，有点像在郑重选择谁有资格读你的日记，每个选项可以搭配一个小图标或细腻的纹理，用来暗示开放与私密之间的差异，但不要做得太显眼或刻意。</v>
       </c>
       <c r="K28" t="str">
         <v/>
@@ -1420,10 +1420,10 @@
         <v>17367</v>
       </c>
       <c r="I29" t="str">
-        <v>Create a two-factor authentication setup flow for the profile editing section that feels calm and trustworthy — think clean white space, soft slate or sage tones, and a quiet sense of security rather than anything alarming or clinical. The part where backup codes appear should feel intentional and almost beautiful, like a well-composed grid of short codes that users genuinely want to keep safe, with a download option that looks polished and considered, not like a forgotten footnote at the bottom of the screen.</v>
+        <v>Create a two-factor authentication setup flow for the profile editing app that feels calm and trustworthy — think clean white space, soft slate or sage tones, and a quiet sense of security rather than anything alarming or clinical. The part where backup codes appear should feel intentional and almost beautiful, like a well-composed grid of short codes that users genuinely want to keep safe, with a download option that looks polished and considered, not like a forgotten footnote at the bottom of the app.</v>
       </c>
       <c r="J29" t="str">
-        <v>在个人资料编辑模块里做一套双因素认证的设置流程，整体基调要沉稳、可信赖——大量干净的留白，搭配柔和的石板灰或鼠尾草绿色调，传递一种低调的安全感，不要有任何让人紧张或过于冷硬的医疗感。备用码出现的那个环节要有仪式感，甚至带点美感，像一个排版讲究的短码网格，让用户打心底里觉得这些码值得好好保存；下载功能的样式也要精致、有分量，绝对不能像随手丢在页面最底部、事后才想起来加的一个边角按钮。</v>
+        <v>为个人资料编辑应用设计一套双因素认证的引导流程，整体风格要让人感到沉稳可信——大量留白，搭配柔和的石板灰或鼠尾草绿色调，营造出一种安静的安全感，而不是让人紧张或觉得冷冰冰的。备用码展示的部分要有一种精心设计过的美感，像是一组排列考究的短码网格，让用户发自内心地想要妥善保存；下载按钮的样式也要精致有质感，不能像是随手扔在页面底部、事后才想起来补上去的东西。</v>
       </c>
       <c r="K29" t="str">
         <v/>
@@ -1455,10 +1455,10 @@
         <v>16548</v>
       </c>
       <c r="I30" t="str">
-        <v>Need a simple way to pull files into an upload screen straight from Google Drive, Dropbox, or iCloud without having to download everything to my phone first and then re-upload it, because that whole back-and-forth is such a waste of time — just let me tap a button, pick which cloud service I'm using, browse my folders, select the file, and have it show up ready to submit, ideally without asking me to log in again every single time.</v>
+        <v>Need a simple way to pull files into an upload app straight from Google Drive, Dropbox, or iCloud without having to download everything to my phone first and then re-upload it, because that whole back-and-forth is such a waste of time — just let me tap a button, pick which cloud service I'm using, browse my folders, select the file, and have it show up ready to submit, ideally without asking me to log in again every single time.</v>
       </c>
       <c r="J30" t="str">
-        <v>想在上传界面直接从 Google Drive、Dropbox 或 iCloud 里选文件，不用先把东西下载到手机上再重新上传，这样来回折腾太浪费时间了——就希望点一个按钮，选好要用的云存储服务，浏览一下文件夹，选中文件，它就直接出现在提交界面里，而且最好不要每次都让我重新登录一遍。</v>
+        <v>想在上传应用里直接从 Google Drive、Dropbox 或 iCloud 导入文件，不用先把东西下载到手机再重新上传，这种来回折腾太浪费时间了——就希望点一个按钮，选我用的云服务，浏览一下文件夹，选好文件，它就直接出现在提交界面里，而且最好不要每次都让我重新登录一遍。</v>
       </c>
       <c r="K30" t="str">
         <v/>
@@ -1493,7 +1493,7 @@
         <v>Need a simple way to just paste a link into my phone and have the file load up right there so I can see what it is before I decide to actually save it — I'm so tired of having to download stuff first, then open it, then figure out if it's even the right file, it's such a waste of time. Like if I paste a URL to a PDF or an image or whatever, it should just show me a little preview of the content right away, and then I can tap a button to actually bring it into the app if I want it.</v>
       </c>
       <c r="J31" t="str">
-        <v>想要一个简单的方式，直接把链接粘贴到手机上就能马上预览文件内容，这样我可以先看看是不是我要的东西，再决定要不要保存——真的受够了那种先下载、再打开、再确认的流程，太浪费时间了。就是说，不管粘贴的是 PDF 链接还是图片链接什么的，都应该直接给我显示一个内容预览，然后我再点个按钮决定要不要把它导入到 app 里。</v>
+        <v>想要一个简单的方式，直接把链接粘贴到手机上就能立刻预览文件内容，这样我就能先看看是不是我要的东西，再决定要不要保存——真的受够了那种先下载、再打开、再确认是不是对的文件的流程，太浪费时间了。就是说，不管粘贴的是PDF链接还是图片链接什么的，都应该马上给我显示一个内容预览，然后我再点个按钮决定要不要把它导入到应用里。</v>
       </c>
       <c r="K31" t="str">
         <v/>
@@ -1525,10 +1525,10 @@
         <v>16254</v>
       </c>
       <c r="I32" t="str">
-        <v>Create a page where I can pick a photo from my phone and it automatically squishes the file size down before uploading, but also lets me slide a bar to choose between like small, medium, or original quality so I can actually see what the image looks like at each level before I hit send — because I'm always getting rejected for files being too big and I just want it to handle that for me without me having to go open some other app to compress it first.</v>
+        <v>Create an app where I can pick a photo from my phone and it automatically squishes the file size down before uploading, but also lets me slide a bar to choose between like small, medium, or original quality so I can actually see what the image looks like at each level before I hit send — because I'm always getting rejected for files being too big and I just want it to handle that for me without me having to go open some other app to compress it first.</v>
       </c>
       <c r="J32" t="str">
-        <v>做一个页面，让我能从手机相册里选照片，选完之后自动帮我压缩文件大小再上传，同时还要有个滑动条可以在小、中、原图这几个质量档位之间切换，这样我在点发送之前就能预览一下每个档位的效果到底是什么样的——因为我老是因为文件太大被拒，每次都得跑去开别的 app 压缩，太烦了，我就想要它自己帮我把这事搞定。</v>
+        <v>做一个可以从手机相册选图的应用，选完之后自动帮我把文件压缩一下再上传，同时还能拖动一个滑条在"小""中""原图"几个画质档位之间切换，让我在真正点发送之前能预览每个档位的实际效果——因为我老是因为文件太大被系统拒掉，每次还得专门跑去开别的压缩软件处理，太麻烦了，我就想要这个应用直接帮我搞定这一切。</v>
       </c>
       <c r="K32" t="str">
         <v/>
@@ -1560,10 +1560,10 @@
         <v>13556</v>
       </c>
       <c r="I33" t="str">
-        <v>Build a mobile file upload page where I can start uploading a big file and then lock my phone or switch to another app without the upload dying on me, because right now every time my screen turns off the upload just stops and I have to start over which is so annoying especially for large videos, so I need it to keep running in the background the whole time and just show me a little progress notification so I know it's still going.</v>
+        <v>Build a mobile file upload app where I can start uploading a big file and then lock my phone or switch to another app without the upload dying on me, because right now every time my app turns off the upload just stops and I have to start over which is so annoying especially for large videos, so I need it to keep running in the background the whole time and just show me a little progress notification so I know it's still going.</v>
       </c>
       <c r="J33" t="str">
-        <v>帮我做一个手机端的文件上传页面，要能支持上传大文件的时候锁屏或者切换到其他App，上传也不会中断，因为现在每次屏幕一关闭上传就停了，只能重头来过，上传大视频的时候真的超烦，所以需要它全程在后台持续运行，同时给我显示一个小小的进度通知，让我知道还在上传中。</v>
+        <v>帮我做一个手机端的文件上传应用，我上传大文件的时候可以直接锁屏或者切到别的app，上传不会中断，因为现在每次退出应用上传就直接停了，只能重新来过，碰到大视频的时候真的很烦，所以需要它能一直在后台跑，同时顶部显示一个小的进度通知，让我知道还在上传中。</v>
       </c>
       <c r="K33" t="str">
         <v/>
@@ -1598,7 +1598,7 @@
         <v>Build a mobile tool where I can copy something — like a messy block of text or a table — and before it actually sends it to another app, I get a quick little picker letting me choose what format I want it converted to first, like plain text, or markdown, or maybe just a clean single line with no extra spacing, because right now I always end up pasting a wall of garbage into WeChat or wherever and then having to clean it up manually which is such a waste of time, so I just want to pick the format right there before I hit share and have it done.</v>
       </c>
       <c r="J34" t="str">
-        <v>做一个手机工具，我复制了什么东西之后——比如一段乱糟糟的文字或者一个表格——在真正发给其他应用之前，能弹出一个小面板让我选一下要转成什么格式，比如纯文本、Markdown，或者把多余的空格全去掉压成干净的一行，因为现在我粘贴到微信或者其他地方每次都是一坨乱七八糟的内容，还得自己手动整理，真的太费事了，我就想在点分享之前直接在那里选好格式，直接搞定。</v>
+        <v>做一个手机工具，让我复制内容之后——比如一段乱七八糟的文字或者一个表格——在真正发送到其他应用之前，弹出一个小选择框，让我挑一下要转成什么格式，比如纯文本、Markdown，或者去掉多余空格的单行文本，因为我现在每次粘贴到微信或者别的地方都是一堆乱码和奇怪排版，还得手动去整理，特别浪费时间，所以就想在点分享之前直接选好格式，一步到位。</v>
       </c>
       <c r="K34" t="str">
         <v/>
@@ -1630,10 +1630,10 @@
         <v>15605</v>
       </c>
       <c r="I35" t="str">
-        <v>Make a page where I can paste in a chunk of text that has bold parts, different sized headings, bullet points, and colored words, and then copy the whole thing out again with all that formatting still intact — because every time I copy something from a doc or article and paste it somewhere else, everything turns into plain boring text and I have to redo all the formatting by hand which takes forever, so I just want a simple tool where I drop the content in, hit copy, and whatever I paste somewhere else looks exactly the same as what I put in.</v>
+        <v>Make an app where I can paste in a chunk of text that has bold parts, different sized headings, bullet points, and colored words, and then copy the whole thing out again with all that formatting still intact — because every time I copy something from a doc or article and paste it somewhere else, everything turns into plain boring text and I have to redo all the formatting by hand which takes forever, so I just want a simple tool where I drop the content in, hit copy, and whatever I paste somewhere else looks exactly the same as what I put in.</v>
       </c>
       <c r="J35" t="str">
-        <v>做一个页面，让我能把带格式的文字粘贴进去——比如粗体、不同级别的标题、项目符号列表、彩色文字——然后一键复制出来，粘贴到其他地方时格式完全保留。因为每次从文档或文章里复制内容，粘到别处就会变成毫无格式的纯文本，所有排版都要重新手动调一遍，特别费时间。我就想要一个简单的工具：把内容扔进去，点复制，然后粘到任何地方，呈现效果跟放进来的时候一模一样。</v>
+        <v>做一个能粘贴带格式文本的工具，支持粗体、不同层级的标题、项目符号列表和彩色文字，粘贴进去之后能把整段内容连同所有格式一起复制出来——因为每次从文档或文章里复制内容粘贴到别的地方，格式全都丢了，变成一堆普通纯文本，还要自己重新手动排版，太浪费时间了，所以就想要一个简单的工具，把内容扔进去，点一下复制，粘贴到其他地方的效果跟放进去时完全一样。</v>
       </c>
       <c r="K35" t="str">
         <v/>
@@ -1665,10 +1665,10 @@
         <v>17319</v>
       </c>
       <c r="I36" t="str">
-        <v>Create a design canvas page where duplicating a layer automatically places the copy with a small offset — like shifted down and to the right by a set amount — instead of landing exactly on top of the original, because every time I copy something it stacks right on top and I waste time dragging it out just to see what I'm working with, so I want the offset to be something I can set once and forget about.</v>
+        <v>Create a design canvas app where duplicating a layer automatically places the copy with a small offset — like shifted down and to the right by a set amount — instead of landing exactly on top of the original, because every time I copy something it stacks right on top and I waste time dragging it out just to see what I'm working with, so I want the offset to be something I can set once and forget about.</v>
       </c>
       <c r="J36" t="str">
-        <v>做一个设计画布页面，复制图层时副本能自动按偏移量错位摆放——比如向右下方偏移固定距离——而不是直接堆在原图层上面。每次复制东西都叠在一起，还得费时间把它拖开才能看清楚，太麻烦了。我希望这个偏移量可以一次设好就不用再动，以后复制都自动按这个走。</v>
+        <v>做一个设计画布应用，复制图层的时候能自动把副本偏移一点放置，比如向右下方错开固定距离，而不是直接叠在原图层上面——因为现在每次复制完都是重叠在一起的，还得手动拖开才能看清在做什么，特别浪费时间。希望这个偏移量可以自己设定一次，之后就不用再管了。</v>
       </c>
       <c r="K36" t="str">
         <v/>
@@ -1700,10 +1700,10 @@
         <v>19066</v>
       </c>
       <c r="I37" t="str">
-        <v>Need a feature where I can browse public templates other people already set up, and with just one tap copy the whole thing into my own personal space so I can start filling it in right away — the original stays untouched, I get my own clean copy, and I don't have to rebuild any of the structure myself from zero, because honestly I just want to skip all that setup work and get straight to the part where I'm actually using it.</v>
+        <v>Need a tool where I can browse public templates other people already set up, and with just one tap copy the whole thing into my own personal space so I can start filling it in right away — the original stays untouched, I get my own clean copy, and I don't have to rebuild any of the structure myself from zero, because honestly I just want to skip all that setup work and get straight to the part where I'm actually using it.</v>
       </c>
       <c r="J37" t="str">
-        <v>想做一个功能，让我可以浏览其他人公开分享的模板，然后只需轻点一下，就能把整个模板完整复制到我自己的空间里，直接开始填内容——原版保持不变，我拿到的是一份干净的副本，完全不需要自己从头搭结构，说实话我就是不想花时间在那些初始配置上，想直接跳到真正用起来的那一步。</v>
+        <v>想要一个能浏览别人公开模板的工具，点一下就能把整个模板复制到我自己的空间里，然后直接开始填内容——原模板不会动，我得到的是一份干净的副本，完全不用自己从头搭结构，说真的我就是想跳过那些前期设置，直接进入实际使用的环节。</v>
       </c>
       <c r="K37" t="str">
         <v/>
@@ -1735,10 +1735,10 @@
         <v>18292</v>
       </c>
       <c r="I38" t="str">
-        <v>Need a little pop-up thing that shows up when my app asks for camera or location access, but instead of just throwing a boring "allow or deny" at the user it actually explains why the app needs it in plain words — like "we need your camera so you can snap a photo of your handmade piece and add it to your collection" — so people actually get what's going on before they decide, and it should feel warm and friendly, not like some scary warning screen, maybe with a little picture or icon that matches whichever permission is being asked for so it all makes sense at a glance.</v>
+        <v>Need a little pop-up thing that shows up when my app asks for camera or location access, but instead of just throwing a boring "allow or deny" at the user it actually explains why the app needs it in plain words — like "we need your camera so you can snap a photo of your handmade piece and add it to your collection" — so people actually get what's going on before they decide, and it should feel warm and friendly, not like some scary warning app, maybe with a little picture or icon that matches whichever permission is being asked for so it all makes sense at a glance.</v>
       </c>
       <c r="J38" t="str">
-        <v>需要做一个小弹窗，在 App 申请相机或位置权限的时候弹出来，但不要直接甩给用户一个冷冰冰的"允许或拒绝"，而是用大白话解释清楚为什么需要这个权限——比如"我们需要访问你的相机，这样你就能拍下自己的手工作品并添加到收藏里"——让用户在做决定之前真正明白是怎么回事。整体风格要温暖、亲切，不能像个吓人的警告页面，最好还能配一张和当前申请权限对应的小图或者图标，让人一眼就能看懂在说什么。</v>
+        <v>想要一个权限申请的小弹窗，在应用请求相机或位置权限的时候弹出来，但不是那种直接甩给用户"允许还是拒绝"的冷冰冰提示，而是用大白话好好解释一下为什么需要这个权限——比如"我们需要访问你的相机，这样你就能拍下自己的手工作品并添加到收藏集里"——让用户在做决定之前真正明白是怎么回事。整体风格要温暖亲切，不能像那种让人紧张的安全警告，最好能配上一个和当前申请权限对应的小插图或图标，让人一眼就能理解。</v>
       </c>
       <c r="K38" t="str">
         <v/>
@@ -1770,10 +1770,10 @@
         <v>12097</v>
       </c>
       <c r="I39" t="str">
-        <v>Create a little thing for my mobile page where if the user loses internet, a small strip shows up at the top telling them they're offline, and underneath it shows a list of whatever actions they tried to do while disconnected — like tapping a save button or submitting a form — so nothing just silently disappears, and then once the connection comes back the strip turns green and all those saved-up actions automatically go through one by one without the user having to do anything.</v>
+        <v>Create a little thing for my mobile app where if the user loses internet, a small strip shows up at the top telling them they're offline, and underneath it shows a list of whatever actions they tried to do while disconnected — like tapping a save button or submitting a form — so nothing just silently disappears, and then once the connection comes back the strip turns green and all those saved-up actions automatically go through one by one without the user having to do anything.</v>
       </c>
       <c r="J39" t="str">
-        <v>帮我在移动端页面做一个小功能：用户断网时，顶部出现一条小提示横幅告知当前已离线，横幅下方列出他们在断网期间触发过的所有操作——比如点了保存按钮或者提交了某个表单——确保这些操作不会就这么悄无声息地丢掉；等网络恢复之后，横幅自动变成绿色，之前积压的那些操作依次自动执行完毕，整个过程用户不需要做任何额外操作。</v>
+        <v>帮我在手机 app 里做一个这样的功能：用户断网的时候，顶部弹出一条小横幅提示他们当前已离线，横幅下方列出他们在断网期间尝试过的所有操作，比如点了保存按钮或者提交了表单，这样就不会有任何操作悄无声息地丢失掉；等网络恢复之后，横幅自动变成绿色，之前积压的那些操作按顺序逐条自动执行，用户完全不需要手动做任何事。</v>
       </c>
       <c r="K39" t="str">
         <v/>
@@ -1799,16 +1799,16 @@
         <v>medium</v>
       </c>
       <c r="G40">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H40">
         <v>13749</v>
       </c>
       <c r="I40" t="str">
-        <v>Create a little page where when stuff is loading, instead of just showing a blank gray blob the whole time, the different pieces kind of pop in one by one as they get ready — like first the picture area fades in, then the title text, then the description underneath, each one revealing itself smoothly rather than everything just suddenly appearing all at once, so it feels less like the app is frozen and more like something is actually happening while you wait.</v>
+        <v>Create an app where when stuff is loading, instead of just showing a blank gray blob the whole time, the different pieces kind of pop in one by one as they get ready — like first the picture area fades in, then the title text, then the description underneath, each one revealing itself smoothly rather than everything just suddenly appearing all at once, so it feels less like the app is frozen and more like something is actually happening while you wait.</v>
       </c>
       <c r="J40" t="str">
-        <v>做一个页面，加载内容的时候，不要一直显示那种灰灰的占位块，而是让各个部分依次一块一块地出现——比如先淡入图片区域，接着显示标题文字，然后再是下面的描述内容，每一块都平滑地展示出来，而不是所有东西一下子同时冒出来，这样用户在等待的时候不会觉得应用卡住了，而是能感受到内容正在一点点加载进来。</v>
+        <v>做一个加载效果，别让页面一直顶着一整块灰色占位块不动，而是让各个部分加载好了之后依次出现——比如先淡入图片区域，接着是标题文字，然后再是下面的描述内容，每一块都平滑地渐显出来，而不是所有东西突然一起蹦出来，这样用户等待的时候不会觉得应用卡死了，而是能感受到页面在一点点加载。</v>
       </c>
       <c r="K40" t="str">
         <v/>
@@ -1843,7 +1843,7 @@
         <v>Make a little pop-up warning thing that shows up when someone tries to delete something important — like it blocks you from instantly clicking confirm, and instead there's a countdown timer ticking down from maybe 5 seconds before the red delete button actually becomes clickable, so people can't accidentally wipe something out in a rush, and maybe the countdown number is big and obvious so you feel the weight of what you're about to do.</v>
       </c>
       <c r="J41" t="str">
-        <v>做一个删除警告弹窗，当用户要删除重要内容时弹出——不能让人直接点确认，而是要先跑一个从5秒开始的倒计时，倒计时没走完之前那个红色的删除按钮一直是禁用状态，这样就算手速太快也不会手滑误删。倒计时的数字要大、要显眼，让人真实感受到这个操作的分量，点下去之前能多想一秒是一秒。</v>
+        <v>做一个删除确认弹窗，当用户要删除重要内容时弹出来——不能让人直接点确认，而是要有一个倒计时，比如从5秒开始往下数，等倒计时结束后那个红色的删除按钮才变成可点击状态，这样就不会手快误删了。倒计时的数字要显示得大一点、醒目一点，让人真实感受到这个操作的分量。</v>
       </c>
       <c r="K41" t="str">
         <v/>
@@ -1878,7 +1878,7 @@
         <v>Need a simple phone tool that helps me figure out how much I'm actually paying when something is "20% off" or "buy at 7折" because I'm always standing in the store doing mental math and getting it wrong — just let me type in the original price and the discount percentage or折扣 number and it instantly shows me the final price, and maybe also let me flip it around so if I know the sale price I can see what percentage off it actually is, nothing fancy just make it work fast without me having to think.</v>
       </c>
       <c r="J42" t="str">
-        <v>需要一个简单的手机小工具，帮我搞清楚"打七折"或者"优惠20%"之后实际要付多少钱——因为我总是站在店里靠心算，还老算错。就是让我输入原价，再输折扣百分比或者几折，马上显示出最终要付的价格就够了。最好还能反过来用：如果我已经知道优惠价，能反推出实际打了几折或者优惠了多少个百分点。不需要什么花里胡哨的功能，就是要快、不用费脑子。</v>
+        <v>想做一个简单的手机小工具，专门帮我算打折后到底要付多少钱——比如"优惠20%"或者"打七折"这种，因为我每次站在店里心算总会算错。就是让我输入原价和折扣力度，不管是百分比还是几折都行，然后立刻显示出实际要付的价格；最好还能反过来查，就是我已经知道了促销价，能看出来到底打了几折或者省了百分之多少。不用搞得多复杂，就要用起来快、不用费脑子。</v>
       </c>
       <c r="K42" t="str">
         <v/>
@@ -1910,10 +1910,10 @@
         <v>13520</v>
       </c>
       <c r="I43" t="str">
-        <v>Build a simple tool where I just punch in my birthday and it immediately tells me my exact age in years, months, and days, plus shows my Chinese zodiac sign and Western star sign right there — I'm so tired of doing the math in my head every time someone asks how old I am or what my zodiac is, just want one page where I enter the date and everything shows up instantly without any extra steps.</v>
+        <v>Build a simple tool where I just punch in my birthday and it immediately tells me my exact age in years, months, and days, plus shows my Chinese zodiac sign and Western star sign right there — I'm so tired of doing the math in my head every time someone asks how old I am or what my zodiac is, just want one app where I enter the date and everything shows up instantly without any extra steps.</v>
       </c>
       <c r="J43" t="str">
-        <v>做一个简单的工具，我输入生日之后立刻显示我的精确年龄——精确到年、月、天——同时也把我的生肖和星座一起展示出来。每次有人问我多大了或者是什么星座，我都得自己在脑子里算，烦死了。就想要一个页面，填上日期，所有信息马上就出来，不需要任何多余的操作。</v>
+        <v>做一个简单的小工具，我只需要输入生日，它就能马上告诉我精确的年龄——精确到年、月、天，同时还能直接显示我的生肖和星座。每次有人问我多大了或者是什么星座，我都得自己在脑子里算，真的烦透了，就想要一个这样的应用，输入日期之后所有信息一下子全出来，不用多余的操作。</v>
       </c>
       <c r="K43" t="str">
         <v/>
@@ -1948,7 +1948,7 @@
         <v>Build a time zone difference calculator app where I can just pick two cities and instantly see what time it is there right now and how many hours apart they are, because I'm constantly messaging people in different countries and always doing the math wrong in my head — it should show a simple world clock list for like 5-6 common cities at the same time so I can glance at all of them without having to search one by one, and let me add or remove cities from that list myself.</v>
       </c>
       <c r="J44" t="str">
-        <v>做一个时区差异计算器，我只需要选两个城市，就能立刻看到那边现在是几点、两地相差几个小时——因为我经常要给不同国家的人发消息，脑子里换算老是算错。同时还要有一个简单的世界时钟列表，显示五六个常用城市的当前时间，让我一眼扫过去就全看到，不用一个个去搜，而且我要能自己手动添加或删除列表里的城市。</v>
+        <v>做一个时区差异计算工具，让我能直接选两个城市，马上看到那边现在几点、相差几个小时，因为我经常要给不同国家的人发消息，老是在脑子里算错时差——同时还要显示一个简单的世界时钟列表，大概放5到6个常用城市，这样我扫一眼就能全看到，不用一个个去搜，而且我可以自己往这个列表里加城市或者删城市。</v>
       </c>
       <c r="K44" t="str">
         <v/>
@@ -1980,10 +1980,10 @@
         <v>13472</v>
       </c>
       <c r="I45" t="str">
-        <v>Make a simple page where I can pick an activity from a list — like running, cycling, walking, swimming, that kind of thing — then enter my body weight and how many minutes I did it, and it just tells me how many calories I burned, I'm tired of googling this every single time after the gym and getting different numbers from different sites, so just keep it straightforward with a clean result shown big enough to read at a glance, and maybe remember my weight so I don't have to retype it every time.</v>
+        <v>Make a simple app where I can pick an activity from a list — like running, cycling, walking, swimming, that kind of thing — then enter my body weight and how many minutes I did it, and it just tells me how many calories I burned, I'm tired of googling this every single time after the gym and getting different numbers from different sites, so just keep it straightforward with a clean result shown big enough to read at a glance, and maybe remember my weight so I don't have to retype it every time.</v>
       </c>
       <c r="J45" t="str">
-        <v>做一个简单的页面，让我能从列表里选一种运动——比如跑步、骑车、走路、游泳这类——然后输入我的体重和运动了多少分钟，直接告诉我消耗了多少卡路里。我每次健身完都得去谷歌搜，而且每个网站给的数字还不一样，真的烦透了，所以就保持简洁，结果显示得大一点，一眼就能看清楚，最好能记住我的体重，这样就不用每次都重新输入了。</v>
+        <v>做一个简单的应用，让我能从列表里选一种运动——比如跑步、骑车、散步、游泳之类的——然后输入我的体重和运动了几分钟，直接告诉我消耗了多少卡路里。我每次健身完都要去谷歌搜，还老是搜出一堆不同的数字，烦死了，所以界面就别搞得太复杂，结果用大字显示出来，扫一眼就能看清楚，最好还能记住我的体重，这样我就不用每次都重新输入了。</v>
       </c>
       <c r="K45" t="str">
         <v/>
@@ -2018,7 +2018,7 @@
         <v>Need a simple fabric yardage calculator for sewing because I'm so tired of doing the math wrong and ending up with way too little fabric or wasting money buying too much — I want to just punch in what I'm making (like a shirt or a skirt or curtains), enter the measurements, and have it spit out exactly how many yards or meters I need to buy, with a little toggle to switch between yards and meters since fabric stores in my area use different units.</v>
       </c>
       <c r="J46" t="str">
-        <v>想要一个简单的缝纫布料用量计算器，因为每次自己算都会算错，要么买少了不够用，要么买多了白白浪费钱，真的烦透了——我希望能直接选择要做的东西（比如衬衫、半身裙或者窗帘），然后输入尺寸，它就能直接告诉我到底需要买多少码或者多少米的布料，另外最好有个单位切换按钮可以在码和米之间来回切换，因为我这边的布料店用的单位不统一。</v>
+        <v>我真的受够了每次算布料用量都算错，要么买少了不够用，要么买多了白花钱，想做一个简单的布料用量计算器——就是选一下我要做什么（比如衬衫、半裙还是窗帘），输入尺寸，然后直接告诉我需要买多少码或者多少米，另外还要有个切换按钮能在码和米之间来回换，因为我附近的布料店用的单位不统一。</v>
       </c>
       <c r="K46" t="str">
         <v/>
@@ -2053,7 +2053,7 @@
         <v>Need a little phone app where I can jot down my dreams right after waking up, and each entry lets me pick a mood or feeling for that dream — like was it scary, happy, weird, peaceful — and also slap a few labels on it like "flying" or "chased" or "old house" so I can later look back and see which kinds of dreams I keep having most often, maybe show it as a simple count or tiny chart somewhere so I notice the patterns over time.</v>
       </c>
       <c r="J47" t="str">
-        <v>想做一个手机小应用，方便我一睁眼就能把梦记下来，每条记录可以选一个当时的心情或感受，比如是恐怖的、开心的、奇怪的还是平静的，还能贴几个标签，像"飞翔""被追""老房子"这类的，这样我以后回头看的时候能知道自己最常做哪种梦，最好在某个地方用简单的数字统计或者小图表展示出来，让我能慢慢发现自己做梦的规律。</v>
+        <v>想做一个手机小应用，专门用来在刚睡醒的时候记录梦境，每条记录可以选一个当时的情绪或感受，比如恐怖、开心、奇怪、平静这类，还能打几个标签，像"飞翔""被追""老房子"之类的，这样之后回头看的时候能知道自己最常做哪种梦，最好在某个地方用简单的数字统计或者小图表展示出来，方便发现自己做梦的规律。</v>
       </c>
       <c r="K47" t="str">
         <v/>
@@ -2085,10 +2085,10 @@
         <v>11501</v>
       </c>
       <c r="I48" t="str">
-        <v>Create a little mobile page where I can log my period each month and jot down how I'm feeling — like if I have cramps, feel super tired, or get headaches — and I want it to show a simple visual of my cycle so I can see roughly when my next one is coming, the whole thing should feel clean and easy to tap through quickly since I usually do it while half-awake in the morning.</v>
+        <v>Create a little mobile app where I can log my period each month and jot down how I'm feeling — like if I have cramps, feel super tired, or get headaches — and I want it to show a simple visual of my cycle so I can see roughly when my next one is coming, the whole thing should feel clean and easy to tap through quickly since I usually do it while half-awake in the morning.</v>
       </c>
       <c r="J48" t="str">
-        <v>做一个小的手机页面，让我可以每个月记录经期，顺便写下自己的身体感受——比如有没有痛经、特别疲惫，或者头痛之类的——还想有一个简单的周期可视化图，能大概看出下次来的时间，整体风格要干净清爽、点起来顺手，因为我一般都是早上迷迷糊糊的时候用。</v>
+        <v>做一个手机小应用，让我能记录每个月的经期，还能写下自己的感受，比如有没有痛经、特别累或者头疼之类的——我希望它能有一个简单的周期图，让我大概能看出下次来的时间。整体要干净清爽、操作顺手，因为我一般早上迷迷糊糊的时候就顺手记了，点几下就要能搞定。</v>
       </c>
       <c r="K48" t="str">
         <v/>
@@ -2120,10 +2120,10 @@
         <v>13093</v>
       </c>
       <c r="I49" t="str">
-        <v>Create a simple little phone page where I can quickly log every time I feed my baby or change their diaper, like just tap a button for "fed" or "diaper changed" and it saves the time automatically, then shows a running list of today's entries so I can see at a glance how long ago the last feeding was and how many diapers we've gone through today.</v>
+        <v>Create a simple little phone app where I can quickly log every time I feed my baby or change their diaper, like just tap a button for "fed" or "diaper changed" and it saves the time automatically, then shows a running list of today's entries so I can see at a glance how long ago the last feeding was and how many diapers we've gone through today.</v>
       </c>
       <c r="J49" t="str">
-        <v>做一个简单的手机页面，方便我快速记录每次给宝宝喂奶或换尿布的情况，就是点一下"已喂奶"或"已换尿布"的按钮，自动保存当前时间，然后下面显示今天的记录列表，让我一眼就能看出上次喂奶是多久前、今天总共换了几次尿布。</v>
+        <v>做一个简单的手机应用，让我能快速记录每次给宝宝喂奶或换尿布的情况，就是点一下"已喂奶"或"已换尿布"的按钮，自动保存当前时间，然后显示今天的记录列表，这样我一眼就能看出上次喂奶是多久前、今天一共换了几次尿布。</v>
       </c>
       <c r="K49" t="str">
         <v/>
@@ -2155,10 +2155,10 @@
         <v>13906</v>
       </c>
       <c r="I50" t="str">
-        <v>Need a simple little app where I can jot down notes about my cat every day — like if she ate weird, was super hyper, or seemed tired and didn't move much — and also track health stuff like when I gave her medicine or noticed something off about her fur or poop, so I don't forget to mention it at the vet later. I want it to feel like a little diary where each day has its own page and I can quickly tap to add a note with the time it happened, and maybe pick from a few common things like "ate normally," "vomited," "played a lot" so I don't have to type everything from scratch every time.</v>
+        <v>Need a simple little app where I can jot down notes about my cat every day — like if she ate weird, was super hyper, or seemed tired and didn't move much — and also track health stuff like when I gave her medicine or noticed something off about her fur or poop, so I don't forget to mention it at the vet later. I want it to feel like a little diary where each day has its own app and I can quickly tap to add a note with the time it happened, and maybe pick from a few common things like "ate normally," "vomited," "played a lot" so I don't have to type everything from scratch every time.</v>
       </c>
       <c r="J50" t="str">
-        <v>想做一个简单的小应用，可以每天记录我家猫的状态——比如她今天吃东西吃得怪怪的、特别亢奋，或者无精打采不爱动——也可以记健康相关的事，像什么时候喂了药、发现毛发或便便有点不对劲，这样去看兽医的时候不会忘记跟医生说。希望整体感觉像一本小日记，每天有自己的一页，可以快速点一下添加一条记录并带上发生的时间，最好还能从几个常用选项里直接选，比如"正常进食""呕吐了""玩得很疯"之类的，不用每次都手打一遍。</v>
+        <v>想做一个简单的小应用，可以每天记录我家猫咪的状态——比如她今天吃东西吃得奇怪、特别亢奋，或者没什么精神、不爱动——还能记健康方面的事，比如什么时候喂了药、发现她的毛或者便便有点不对劲，这样去看兽医的时候就不会忘了跟医生说。整体感觉要像一本小日记，每天有自己单独的页面，可以快速点一下添加一条记录，顺便标上发生的时间，最好还能从几个常用选项里直接选，比如"正常吃饭""呕吐了""玩得很嗨"之类的，不用每次都从头手打。</v>
       </c>
       <c r="K50" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>Build a little mobile app where I can keep track of when I water my plants and do other care stuff like trimming or adding fertilizer, basically just a simple log where I pick the plant, tap what I did, and it saves the date automatically, and I can scroll back and see the history for each plant so I actually remember when I last watered my cactus instead of guessing.</v>
       </c>
       <c r="J51" t="str">
-        <v>帮我做个手机小应用，用来记录给植物浇水和日常养护的情况，比如修剪啊、施肥啊之类的，就是个简单的日志，选好植物、点一下做了什么，日期自动保存，然后可以往上翻每棵植物的历史记录，这样我就不用靠猜来想上次给仙人掌浇水到底是哪天了。</v>
+        <v>帮我做一个简单的手机应用，用来记录我给植物浇水和做其他养护操作的时间，比如修剪或者施肥，就是一个简单的日志，我选好植物之后点一下做了什么，它自动保存日期，然后我可以往上滚动查看每株植物的历史记录，这样我就不用靠猜来想上次给仙人掌浇水是什么时候了。</v>
       </c>
       <c r="K51" t="str">
         <v/>
@@ -2228,7 +2228,7 @@
         <v>A gift idea suggester where you first pick what kind of person the recipient is — like whether they're an outdoorsy adventure type, a cozy homebody, a total foodie, or something like that — shown as a few simple picture cards you tap on, and once you choose one it shows you a bunch of gift ideas that actually fit that personality, each with a little price range label so you can filter to what you can actually afford. The whole thing is for those moments right before a birthday when you have no clue what to get someone and you just want a starting point that isn't totally generic.</v>
       </c>
       <c r="J52" t="str">
-        <v>一个送礼灵感推荐工具，先让你选收礼人是哪种类型的人——比如热爱户外探险的、喜欢宅在家的、超级吃货之类的——用几张简单的图片卡片展示，点击选择后，就会出现一批真正符合那种性格的礼物建议，每条都带一个价格区间标签，方便筛选出自己实际能接受的价位。整个工具就是为了解决那种生日快到了却完全不知道送什么的尴尬时刻，想要一个不那么千篇一律的起点。</v>
+        <v>一个送礼灵感推荐工具，先让你选收礼人是哪种类型的人——比如爱户外冒险的、喜欢宅在家里的、超级吃货之类的——用几张简单的图片卡片展示，点一下就能选，选完之后会给你列出一堆真正适合这种性格的礼物建议，每个都带个价格区间标签，方便筛选出自己实际能接受的价位。整个工具就是为了那种生日快到了却完全不知道送什么、只想要个不那么千篇一律的起点的时刻准备的。</v>
       </c>
       <c r="K52" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Create a little tool where I type in a topic I want to argue about — like "should schools ban phones" or whatever — and it gives me a bunch of points I could use to argue for it, plus the opposite side's comebacks so I can think about how to fight back, all shown in a simple back-and-forth way so I can actually read through both sides without getting lost.</v>
       </c>
       <c r="J53" t="str">
-        <v>做一个小工具，我输入一个想辩论的话题——比如"学校该不该禁手机"之类的——然后它给我列出一堆支持这个立场的论点，同时也把对方可能的反驳列出来，让我想想该怎么回击，整体用简单的一来一回的形式展示，这样我能顺着看完双方的观点，不会看着看着就乱了。</v>
+        <v>做一个小工具，我输入一个想辩论的话题——比如"学校该不该禁止手机"之类的——然后它给我列出一堆支持该观点的论点，同时也把对方可能提出的反驳意见一起列出来，让我能想想怎么见招拆招，整体用一来一回对比的方式呈现，这样我看双方的论点时不会乱，能清清楚楚地读下去。</v>
       </c>
       <c r="K53" t="str">
         <v/>
@@ -2295,10 +2295,10 @@
         <v>19049</v>
       </c>
       <c r="I54" t="str">
-        <v>Make a mobile page for picking party games when a group of friends can't decide what to play — you tap a big spinning button to randomly land on one game from a built-in list of maybe a dozen fun classics like truth or dare or charades, and once it picks one it shows the rules right there on the same screen so everyone can gather around and read them without hunting for instructions anywhere else, and I'd love to be able to add my own homemade game ideas with a name and a short description so the list isn't just the defaults.</v>
+        <v>Make a mobile app for picking party games when a group of friends can't decide what to play — you tap a big spinning button to randomly land on one game from a built-in list of maybe a dozen fun classics like truth or dare or charades, and once it picks one it shows the rules right there on the same app so everyone can gather around and read them without hunting for instructions anywhere else, and I'd love to be able to add my own homemade game ideas with a name and a short description so the list isn't just the defaults.</v>
       </c>
       <c r="J54" t="str">
-        <v>做一个手机页面，专门帮一群朋友解决"不知道玩什么"的问题——页面上有一个大大的旋转按钮，点下去会从内置列表里随机转出一个游戏，列表里预设十几个经典好玩的项目，比如真心话大冒险、猜词表演这类的，转到结果之后，游戏规则直接显示在同一个屏幕上，大家围过来就能一起看，不用再跑去别的地方找说明。另外我还希望能自己添加自创游戏，填一个名字和简短描述，这样列表就不只是默认的那些了。</v>
+        <v>做一个手机应用，专门帮一群朋友在不知道玩什么派对游戏的时候做决定——点一下屏幕中间那个大转盘按钮，就能从内置的十几个经典游戏里随机抽一个，比如真心话大冒险或者猜谜表演之类的，抽到之后直接在同一个页面显示这个游戏的规则，大家围过来看就行，不用到处找说明。另外我希望能自己添加自制游戏，填个名字和简单介绍，这样游戏列表就不只是默认的那些了。</v>
       </c>
       <c r="K54" t="str">
         <v/>
@@ -2333,7 +2333,7 @@
         <v>Make a simple little app where you pick a tricky everyday situation — like going to the doctor, riding the bus for the first time, or asking a classmate for help — and it builds a short friendly story that walks through what's going to happen step by step, written in a really calm and clear way that's easy to follow for kids or anyone who gets anxious about new social stuff, with small pictures or little drawings next to each step so it's not just plain text, and once the story is ready you can save it and share it easily so a parent or teacher can use it with the person who needs it.</v>
       </c>
       <c r="J55" t="str">
-        <v>做一个简单的小应用，让用户选择一个可能让人紧张的日常场景——比如去看医生、第一次自己坐公交车、或者向同学开口求助——然后自动生成一个简短温馨的小故事，一步一步地讲清楚整件事会怎么发生，语气平和、表达清晰，方便孩子或者容易在陌生社交场合感到焦虑的人理解；每个步骤旁边配上小插图或简单的小图标，不要让页面显得只有一大堆文字；故事生成好之后可以方便地保存和分享，让家长或老师能直接拿去给需要的孩子使用。</v>
+        <v>做一个小应用，让用户选择一个日常生活中容易让人犯难的场景——比如去看医生、第一次坐公交车、或者向同学开口求助——然后自动生成一段简短温馨的小故事，一步一步地把接下来会发生的事情说清楚，语气平和、表达简单易懂，特别适合小朋友或者对陌生社交场合容易感到紧张焦虑的人阅读；每个步骤旁边配上小插图或简单的小画，让内容不只是纯文字；故事生成之后可以方便地保存和分享，让家长或老师能直接拿去陪有需要的孩子一起用。</v>
       </c>
       <c r="K55" t="str">
         <v/>
@@ -2368,7 +2368,7 @@
         <v>Need a little phone tool that helps people find the right words when they're in the middle of a fight or awkward situation with someone — like a phrase guide where you pick what kind of conflict you're dealing with (argument with a friend, tense moment with a coworker, that kind of thing) and it shows you a few calm, non-aggressive ways to say what you're feeling, with a short note explaining why that phrasing works better than just blurting out the first thing that comes to mind.</v>
       </c>
       <c r="J56" t="str">
-        <v>想做一个手机小工具，专门帮人在吵架或跟别人陷入尴尬僵局的时候找到合适的措辞——类似一个用语指南，先选你遇到的是哪种冲突场景（比如和朋友闹矛盾、和同事关系紧张之类的），然后给你列出几句平和、不带攻击性的表达方式，每句话附一小段说明，解释为什么这样说比脱口而出的第一反应更管用。</v>
+        <v>想做一个小的手机工具，帮助人们在跟别人吵架或者陷入尴尬局面的时候找到合适的表达方式——类似一个措辞指南，用户先选择自己面对的是哪种冲突场景（比如跟朋友起争执、跟同事关系变得紧张之类的），然后系统会给出几种平和、不带攻击性的说法来表达自己的感受，同时附上一句简短的说明，解释为什么这样说比直接脱口而出效果更好。</v>
       </c>
       <c r="K56" t="str">
         <v/>
@@ -2400,10 +2400,10 @@
         <v>22119</v>
       </c>
       <c r="I57" t="str">
-        <v>A vacation departure countdown screen that feels like a beautifully curated travel mood board — warm sandy and terracotta tones, maybe a soft linen-textured background, with the days remaining shown in a large airy number front and center, the kind of typography that makes you feel the trip is already happening. Below that, a packing reminder section that looks like handwritten notes in a little travel journal, loosely grouped by vibe — beach stuff, documents, camera gear — rather than a cold clinical checklist. The whole thing should have that golden-hour anticipation feeling, something you'd genuinely want to open every morning leading up to the trip just because it looks so good.</v>
+        <v>A vacation departure countdown app that feels like a beautifully curated travel mood board — warm sandy and terracotta tones, maybe a soft linen-textured background, with the days remaining shown in a large airy number front and center, the kind of typography that makes you feel the trip is already happening. Below that, a packing reminder app that looks like handwritten notes in a little travel journal, loosely grouped by vibe — beach stuff, documents, camera gear — rather than a cold clinical checklist. The whole thing should have that golden-hour anticipation feeling, something you'd genuinely want to open every morning leading up to the trip just because it looks so good.</v>
       </c>
       <c r="J57" t="str">
-        <v>做一个度假出发倒计时页面，整体风格要像一块精心策划的旅行情绪板——暖沙色和砖红色调，背景带一点柔和的亚麻纹理质感，剩余天数用一个大而通透的数字居中显示在页面核心位置，那种字体排版要让人一眼看上去就觉得旅程已经开始了。下方是一个行李提醒区域，要做成旅行日记里随手记下的手写便签风格，按感觉松散地分个类——海滩用品、证件材料、相机器材之类的——而不是那种冷冰冰的标准化清单。整个页面要有一种黄金时刻里才有的期待感，那种让人每天早上都忍不住打开来看一眼的感觉，就因为它本身就已经足够好看。</v>
+        <v>想做一个出发倒计时应用，整体感觉像一块精心布置的旅行情绪板——用暖沙色和陶土色调，背景带点柔软的亚麻布纹理，剩余天数用一个大大的、透气感十足的数字摆在最显眼的位置，那种字体要让人一看就觉得旅程好像已经开始了。下面再配一个行李提醒模块，风格像是随手写在小旅行日记本上的手写便签，按照感觉分成几组——海滩装备、证件、相机器材之类的，要那种随性自然的分组方式，不要冷冰冰的清单格式。整体要有一种黄金时刻前那种满怀期待的氛围，就是那种你每天早上打开它不是因为要查什么，纯粹是因为它看起来太好看了、让你忍不住想看的感觉。</v>
       </c>
       <c r="K57" t="str">
         <v/>
@@ -2435,10 +2435,10 @@
         <v>21639</v>
       </c>
       <c r="I58" t="str">
-        <v>Build a mobile page that shows your anniversary date and how many years you've been together in a way that feels warm and a little cinematic — like a love letter, not a calendar app. The years-together number should be the visual centerpiece, displayed large and soft with a handwritten-style font, and beneath it the actual date written out in full (like "May 14, 2019") in a quieter, smaller text so it feels like a caption under a memory. The whole thing should have a muted, film-photo color palette — creamy whites, dusty roses, maybe a faint grain texture in the background — so it looks like something you'd screenshot and save, not just read and close.</v>
+        <v>Build a mobile app that shows your anniversary date and how many years you've been together in a way that feels warm and a little cinematic — like a love letter, not a calendar app. The years-together number should be the visual centerpiece, displayed large and soft with a handwritten-style font, and beneath it the actual date written out in full (like "May 14, 2019") in a quieter, smaller text so it feels like a caption under a memory. The whole thing should have a muted, film-photo color palette — creamy whites, dusty roses, maybe a faint grain texture in the background — so it looks like something you'd screenshot and save, not just read and close.</v>
       </c>
       <c r="J58" t="str">
-        <v>做一个手机页面，用来展示你们的纪念日和在一起多少年，整体感觉要温柔、有点电影感——像情书，不像日历软件。"在一起X年"这个数字要作为视觉核心，用手写风格的字体显示得大而柔和，下面用更小、更安静的文字把完整日期写出来（比如"2019年5月14日"），读起来像是一张旧照片下面的注脚。整个页面要用那种低饱和的胶片色调——米白、灰玫瑰粉，背景加一点淡淡的颗粒感纹理——让人看完想截图收藏，而不是看完就关掉。</v>
+        <v>做一个手机应用，用来展示你们的纪念日和在一起多少年，整体风格要有温度、带点电影感——像一封情书，而不是日历软件。在一起的年数要作为视觉核心，用手写风格的字体大大地、柔柔地显示在屏幕中央，下方再用小一号、更低调的字体把具体日期完整写出来（比如"2019年5月14日"），像是一张老照片下面的注脚。整体配色要用那种偏复古胶片的感觉——奶白色、藕粉色，背景还可以加一点淡淡的颗粒质感——让人看完想截图收藏，而不是随手关掉。</v>
       </c>
       <c r="K58" t="str">
         <v/>
@@ -2470,10 +2470,10 @@
         <v>18274</v>
       </c>
       <c r="I59" t="str">
-        <v>Create a memorial and tribute date reminder screen that feels quiet and reverent — like flipping through an old photo album in the late afternoon light — where each remembered person or moment gets their own soft card with a portrait-style photo, their name, and the annual date that marks them, and as the date draws near the whole page shifts into a warmer, more muted tone almost like candlelight, so it never feels like a cold calendar alert but more like a gentle nudge to pause and remember.</v>
+        <v>Create a memorial and tribute date reminder app that feels quiet and reverent — like flipping through an old photo album in the late afternoon light — where each remembered person or moment gets their own soft card with a portrait-style photo, their name, and the annual date that marks them, and as the date draws near the whole app shifts into a warmer, more muted tone almost like candlelight, so it never feels like a cold calendar alert but more like a gentle nudge to pause and remember.</v>
       </c>
       <c r="J59" t="str">
-        <v>做一个用于纪念与追思的日期提醒页面，整体氛围要安静、庄重，像是在午后斜阳里翻着一本老相册——每一位被铭记的人或每一段值得珍藏的时光，都有自己专属的柔和卡片，卡片上放一张竖版人像照片，配上他们的名字和每年对应的那个日子；当日期临近时，整个页面要自动过渡到更暖、更低饱和的色调，像烛光一样，绝对不能有那种冷冰冰的日历提醒感，而是像一个轻柔的提示，让人不知不觉放慢脚步、静静回想。</v>
+        <v>做一个纪念与追思日期提醒的应用，整体氛围要安静而庄重，就像在午后柔和的光线里慢慢翻阅一本老相册——每一位被铭记的人或每一段值得珍藏的时刻，都有专属的柔和卡片，配上竖版人像照片、姓名，以及每年循环的纪念日期；当日期临近时，整个应用的色调会自动过渡到更温暖、更沉静的感觉，像烛光一样，让人感受不到任何冰冷的日历提醒，更像是一次轻柔的提示，让你停下来，静静地想起那个人。</v>
       </c>
       <c r="K59" t="str">
         <v/>
@@ -2505,10 +2505,10 @@
         <v>17484</v>
       </c>
       <c r="I60" t="str">
-        <v>A sobriety streak screen that feels like a quiet, proud exhale — the kind of thing you'd actually want to open every morning just to see your number sitting there, clean and unhurried, like a stone you've been polishing. The day count should be the visual centerpiece, displayed in a large, calm typeface with a lot of breathing room around it, maybe in soft off-white or warm cream tones against a deep muted background — nothing clinical or gym-app aggressive. Below it, a subtle row of small glowing dots or minimal tick marks representing the past weeks, so you can feel the accumulation without it being loud about it. The whole mood should feel like slow, intentional living — grounded, a little meditative, the kind of design you'd see on a wellness journal app that takes itself seriously aesthetically.</v>
+        <v>A sobriety streak app that feels like a quiet, proud exhale — the kind of thing you'd actually want to open every morning just to see your number sitting there, clean and unhurried, like a stone you've been polishing. The day count should be the visual centerpiece, displayed in a large, calm typeface with a lot of breathing room around it, maybe in soft off-white or warm cream tones against a deep muted background — nothing clinical or gym-app aggressive. Below it, a subtle row of small glowing dots or minimal tick marks representing the past weeks, so you can feel the accumulation without it being loud about it. The whole mood should feel like slow, intentional living — grounded, a little meditative, the kind of design you'd see on a wellness journal app that takes itself seriously aesthetically.</v>
       </c>
       <c r="J60" t="str">
-        <v>做一个戒断打卡的连续记录页面，整体气质要像一次安静而自豪的深呼吸——那种每天早上都真的想打开的界面，就为了看那个数字安安静静地待在那里，干净、不慌不忙，像一块你一直在细细打磨的石头。天数应该是整个页面的视觉核心，用大号、沉稳的字体呈现，四周留出充足的留白，颜色可以考虑柔和的米白或温暖的奶油色，背景用深沉低饱和的色调来衬托——不要任何临床感，也不要健身类app那种咄咄逼人的劲儿。天数下方放一排细腻的小发光圆点或极简刻度线，用来呈现过去几周的记录，让人感受到时间的积累，但不喧嚷、不刻意强调。整个页面的氛围要像慢节奏、有意识的生活方式本身——沉稳，带一点冥想的禅意，是那种美学上很认真的健康日记类app才会有的设计风格。</v>
+        <v>做一个戒断打卡应用，整体氛围要像一次平静而自豪的深呼吸——那种你每天早上都真的想打开的东西，就为了看到那个数字静静地待在那里，干净、从容，像一块你一直在细细打磨的石头。天数计数要作为视觉核心，用大号、沉稳的字体展示，四周留出充足的留白，配色可以考虑柔和的米白或暖奶油色，搭配深沉低饱和的背景——不要那种医疗感，也不要健身类应用那种咄咄逼人的风格。数字下方放一排细腻的小光点或极简刻度线，代表过去几周的积累，让人感受到时间的沉淀，但不要喧宾夺主。整体气质应该是缓慢、有意识的生活感——沉稳、带一点冥想意味，就像那种在审美上很认真对待自己的健康生活类日记应用的设计风格。</v>
       </c>
       <c r="K60" t="str">
         <v/>
@@ -2540,10 +2540,10 @@
         <v>16957</v>
       </c>
       <c r="I61" t="str">
-        <v>Make a fitness challenge day-counter screen that feels clean and motivating, centered around a big glowing progress ring that slowly fills up as the days go by — like the kind you'd see on a premium wellness app, with a satisfying gradient arc in coral and violet tones, and the current day number displayed boldly in the middle so it's the first thing your eyes land on. The overall vibe should feel airy and focused, maybe a soft dark background to make the ring really pop, with a small note underneath showing how many days are left in the challenge so you always know where you stand.</v>
+        <v>Make a fitness challenge day-counter app that feels clean and motivating, centered around a big glowing progress ring that slowly fills up as the days go by — like the kind you'd see on a premium wellness app, with a satisfying gradient arc in coral and violet tones, and the current day number displayed boldly in the middle so it's the first thing your eyes land on. The overall vibe should feel airy and focused, maybe a soft dark background to make the ring really pop, with a small note underneath showing how many days are left in the challenge so you always know where you stand.</v>
       </c>
       <c r="J61" t="str">
-        <v>做一个健身挑战的天数计数页面，整体风格要干净利落、充满动力感，核心视觉是一个大型发光进度环，随着挑战天数的推进缓慢填满——就像高端健康应用里常见的那种效果，弧形轨道用珊瑚色到紫罗兰色的渐变，当前天数的数字加粗显示在圆环正中央，让人一眼就能看到。整体氛围要通透、聚焦，背景用柔和的深色调，把发光圆环衬托得更有冲击力，圆环下方配一行小字，显示挑战还剩多少天，让用户随时清楚自己的进度。</v>
+        <v>做一个健身挑战天数打卡应用，整体风格要干净、有激励感，核心视觉是一个大大的发光进度环，随着挑战天数的推进缓缓填充——就像高端健康类应用里常见的那种设计，用珊瑚色和紫罗兰色调的渐变弧线来呈现，当前天数以粗体大字显示在环的正中央，让人一眼就能注意到。整体氛围要通透、专注，考虑用柔和的深色背景来衬托进度环，让它更加突出；环的下方放一行小字，显示挑战剩余天数，让用户随时清楚自己还剩多少天。</v>
       </c>
       <c r="K61" t="str">
         <v/>
@@ -2575,10 +2575,10 @@
         <v>18979</v>
       </c>
       <c r="I62" t="str">
-        <v>A password generator page where you just tap a button and get a random password, and there's some kind of strength bar or score underneath that tells you how hard it would actually be to crack — I keep reusing the same three passwords for everything because coming up with new ones every time is exhausting, so I need something where I can slide the length up or down and toggle whether to include numbers and symbols, and it shows me clearly whether what it generated is genuinely strong or just looks messy without actually being secure.</v>
+        <v>A password generator app where you just tap a button and get a random password, and there's some kind of strength bar or score underneath that tells you how hard it would actually be to crack — I keep reusing the same three passwords for everything because coming up with new ones every time is exhausting, so I need something where I can slide the length up or down and toggle whether to include numbers and symbols, and it shows me clearly whether what it generated is genuinely strong or just looks messy without actually being secure.</v>
       </c>
       <c r="J62" t="str">
-        <v>做一个密码生成器页面，点一下按钮就能生成一个随机密码，下面有个强度条或者评分，告诉我这个密码实际上有多难被破解——我一直在所有账号上反复用那三个老密码，因为每次想新密码真的太累了，所以我需要能滑动调节密码长度、还能开关是否包含数字和符号的功能，而且要清楚地告诉我生成出来的密码是真的够强，还是只是看起来乱糟糟的、实际上根本不安全。</v>
+        <v>一个密码生成器应用，点一下按钮就能随机生成一个密码，下面有某种强度条或评分，告诉我这个密码实际上有多难被破解——我一直在所有地方反复用同那三个密码，因为每次都要想新密码实在太累了，所以我需要一个能滑动调整密码长度、切换是否包含数字和符号的工具，而且能清楚地告诉我生成出来的密码是真的强，还是看起来乱糟糟但其实根本不安全。</v>
       </c>
       <c r="K62" t="str">
         <v/>
@@ -2610,10 +2610,10 @@
         <v>15910</v>
       </c>
       <c r="I63" t="str">
-        <v>Make a page where I can type markdown on one side and instantly see how it actually looks on the other side, because I'm so tired of writing stuff in markdown and having no clue if the headers and bold text and bullet points are actually coming out right until I paste it somewhere else — just split the screen in half with a text input area on top and the rendered result showing below it in real time as I type, and make sure it handles the common stuff like headings, code blocks, and links without me having to do anything extra.</v>
+        <v>Make an app where I can type markdown on one side and instantly see how it actually looks on the other side, because I'm so tired of writing stuff in markdown and having no clue if the headers and bold text and bullet points are actually coming out right until I paste it somewhere else — just split the app in half with a text input area on top and the rendered result showing below it in real time as I type, and make sure it handles the common stuff like headings, code blocks, and links without me having to do anything extra.</v>
       </c>
       <c r="J63" t="str">
-        <v>做一个页面，左边可以输入Markdown，右边实时预览渲染效果，因为每次写完Markdown都不知道标题、加粗、列表到底有没有正确显示，得粘贴到别的地方才能确认，真的很烦——就把屏幕左右各占一半，左边是文本输入区，右边实时渲染，我一边打字一边就能看到效果，而且常见的语法比如标题、代码块、链接这些都要能直接支持，不需要我做任何额外配置。</v>
+        <v>做一个左边可以输入 Markdown、右边实时预览渲染效果的应用，因为每次写完 Markdown 都不知道标题、加粗、列表到底有没有显示正确，非得粘到别的地方才能看到，真的很烦——就把页面分成两半，上面是文本输入区，下面实时显示渲染结果，边打字边更新，而且常见的那些语法比如标题、代码块、链接这些都要能直接支持，不用我额外做任何配置。</v>
       </c>
       <c r="K63" t="str">
         <v/>
@@ -2645,10 +2645,10 @@
         <v>14917</v>
       </c>
       <c r="I64" t="str">
-        <v>Build a simple mobile page where I can paste in a messy chunk of JSON and it automatically cleans it up into something readable with proper spacing and indentation, and if there's a mistake in the JSON it tells me exactly which line is broken so I don't have to stare at a wall of text trying to figure out why my code keeps crashing — I just need it to work fast, one paste box at the top, the fixed result shows up below, and a clear error message when something's wrong.</v>
+        <v>Build a simple mobile app where I can paste in a messy chunk of JSON and it automatically cleans it up into something readable with proper spacing and indentation, and if there's a mistake in the JSON it tells me exactly which line is broken so I don't have to stare at a wall of text trying to figure out why my code keeps crashing — I just need it to work fast, one paste box at the top, the fixed result shows up below, and a clear error message when something's wrong.</v>
       </c>
       <c r="J64" t="str">
-        <v>做一个简单的手机页面，我可以把乱糟糟的 JSON 粘进去，它自动帮我整理成有正确缩进和间距的可读格式，如果 JSON 有错误就直接告诉我是哪一行出了问题，这样我就不用盯着一堆文字干猜为什么代码一直报错了——就希望响应快一点，顶部一个粘贴框，下面显示格式化后的结果，出错的时候有清晰的报错提示。</v>
+        <v>做一个简单的手机应用，让我能把乱糟糟的 JSON 粘进去，它自动帮我整理成带有合适空格和缩进的可读格式，如果 JSON 本身有问题就直接告诉我是哪一行出了错，省得我盯着一堆文字苦苦排查代码崩溃的原因——功能越快越好，顶部一个粘贴框，下面直接显示处理后的结果，出错时给出清晰的报错提示就行。</v>
       </c>
       <c r="K64" t="str">
         <v/>
@@ -2683,7 +2683,7 @@
         <v>CSV file viewer that opens any CSV and lays it out as a plain scrollable table on your phone — the annoying part is every time someone sends me a CSV I have to drag out my laptop just to fix one wrong cell or delete a duplicate row, which kills like 20 minutes for no reason. Should let me tap a cell to edit the text right there in place, and once I'm done there's a button to export the updated file so I can send it back or save it.</v>
       </c>
       <c r="J65" t="str">
-        <v>一个CSV文件查看器，能在手机上打开任意CSV文件并以简洁的可滚动表格形式展示内容——最烦的就是每次有人发给我一个CSV，我都得专门把笔记本电脑搬出来，就为了改一个填错的单元格或者删一行重复数据，白白浪费二十分钟，完全没必要。应该支持直接点击某个单元格就能在原位编辑文字，改完之后有一个导出按钮，可以把更新后的文件发出去或者保存下来。</v>
+        <v>做一个手机上的 CSV 文件查看器，能打开任意 CSV 文件，把内容以最基础的可滚动表格形式展示出来——最烦的就是每次有人发给我一个 CSV，我就得专门打开电脑，就为了改一个填错的单元格或者删掉一行重复数据，白白浪费二十分钟，完全没必要。要能点击某个单元格直接在原地编辑文字内容，改完之后有个按钮可以导出修改后的文件，方便发回去或者存起来。</v>
       </c>
       <c r="K65" t="str">
         <v/>
@@ -2715,10 +2715,10 @@
         <v>12315</v>
       </c>
       <c r="I66" t="str">
-        <v>Create a mobile page where I can just paste any text or link and instantly get a QR code I can screenshot and send — I'm so tired of googling random QR generator sites every time I need to share a WiFi password or a link with someone who doesn't want to type it out, just make it work fast with a big clear QR code in the middle and a download button so I can save it straight to my phone.</v>
+        <v>Create a mobile app where I can just paste any text or link and instantly get a QR code I can screenshot and send — I'm so tired of googling random QR generator sites every time I need to share a WiFi password or a link with someone who doesn't want to type it out, just make it work fast with a big clear QR code in the middle and a download button so I can save it straight to my phone.</v>
       </c>
       <c r="J66" t="str">
-        <v>做一个手机页面，让我能直接粘贴任何文字或链接，立刻生成二维码截图发给别人——我真的烦透了每次要分享WiFi密码或链接的时候都得去搜一个二维码生成网站，对方又懒得手打，就想要个能快速出结果的页面，中间放一个大大的清晰二维码，再加一个下载按钮，方便我直接保存到手机里。</v>
+        <v>做一个手机应用，我可以直接把任意文字或链接粘贴进去，马上生成一个二维码截图发给别人——我真的受够了每次要分享 WiFi 密码或者链接的时候还得去搜一堆乱七八糟的二维码生成网站，对方又懒得手动输入，就想要个能快速出结果的 app，界面简单点，中间放一个大大的清晰二维码，再加一个下载按钮可以直接保存到手机相册就行。</v>
       </c>
       <c r="K66" t="str">
         <v/>
@@ -2750,10 +2750,10 @@
         <v>25185</v>
       </c>
       <c r="I67" t="str">
-        <v>Need a little tool for writers where you tap a button and it spits out a random story plot idea plus a matching character all at once — like the plot might say "two childhood friends reunite after a secret is uncovered" and the character comes with a name, an odd job, and one or two personality traits so you've got something real to actually start writing from instead of just staring at a blank page, and it'd be great if you could lock whichever part you like and only re-roll the other half when you want something different.</v>
+        <v>Need a little tool for writers where you tap a button and it spits out a random story plot idea plus a matching character all at once — like the plot might say "two childhood friends reunite after a secret is uncovered" and the character comes with a name, an odd job, and one or two personality traits so you've got something real to actually start writing from instead of just staring at a blank app, and it'd be great if you could lock whichever part you like and only re-roll the other half when you want something different.</v>
       </c>
       <c r="J67" t="str">
-        <v>想做一个给写作者用的小工具，点一下按钮就能同时随机生成一个故事情节和一个配套角色——比如情节可能是"两个青梅竹马的老友因为一个秘密被揭开而重逢"，角色那边则附带名字、一份奇奇怪怪的职业，再加一两条性格特点，这样就有真实的素材可以直接动笔，不用对着空白页发呆了。最好还能把喜欢的那部分锁住，只重新随机另一半，这样想换其中一块的时候不会把另一块也搞丢。</v>
+        <v>想做一个给写作者用的小工具，点一下按钮就能同时生成一个随机故事情节和一个配套角色——情节比如说"两个青梅竹马因为一个秘密被揭穿而重逢"，角色那边则附带姓名、一份奇奇怪怪的职业，还有一两条性格特点，让你手头有真实的东西可以直接开始写，而不是对着空白页发呆。最好还能把自己满意的那部分锁住，想换的时候只重新随机另一半。</v>
       </c>
       <c r="K67" t="str">
         <v/>
@@ -2788,7 +2788,7 @@
         <v>Make a little tool where you can type in a bunch of names and then hit a button to randomly split them into pairs or small groups, like for team activities or study sessions — I want it to show the results in a fun way, maybe shuffle with a quick animation so it feels satisfying, and let me set how many people go in each group before the draw happens.</v>
       </c>
       <c r="J68" t="str">
-        <v>做一个小工具，可以输入一堆名字，然后点个按钮把他们随机分成两两一对或者小组，适合用来搞团队活动或者学习搭档之类的——希望结果呈现得有点意思，比如加个快速的洗牌动画，看着很爽那种，另外在开始分组之前能让我设置好每组几个人。</v>
+        <v>做一个小工具，可以输入一堆名字，然后点击按钮把他们随机分成两两一组或者小组，适合团队活动或者学习搭档那种场景——希望结果展示得有点意思，比如加一个快速洗牌的动画，看起来比较爽，另外在开始抽签之前可以设置每组几个人。</v>
       </c>
       <c r="K68" t="str">
         <v/>
@@ -2823,7 +2823,7 @@
         <v>Create a spinning wheel thing for my household where me and my roommates can add everyone's names and a list of chores, then spin it to randomly pick who does what each week, and it'd be really nice if the wheel looks fun and colorful when it spins so people actually want to use it instead of arguing about who cleans the bathroom.</v>
       </c>
       <c r="J69" t="str">
-        <v>帮我做一个给家里用的转盘抽签工具，我和室友可以把大家的名字和家务列表都录进去，然后转一下随机决定这周谁做哪项家务。最好转盘转起来的时候又好看又花哨，颜色丰富一点，这样大家才会真的想用它，而不是每次都为了谁去刷卫生间的事吵来吵去。</v>
+        <v>给我们合租的几个人做一个转盘抽签工具，大家可以把各自的名字和家务清单都填进去，然后转一下转盘，随机决定这周谁负责哪项家务。最好转盘转起来能好看一点、颜色鲜艳一点，这样大家才会真的想用它，而不是每次都为谁去刷厕所吵来吵去。</v>
       </c>
       <c r="K69" t="str">
         <v/>
@@ -2858,7 +2858,7 @@
         <v>Create a little tool where I pick a few words that describe my pet's vibe — like lazy, fluffy, grumpy, silly — and it spits out a bunch of cute name ideas that actually match that personality, so I can find something that feels just right instead of just googling generic pet names lists, and I want it to show maybe 8 or so name suggestions at a time with a button to get a fresh batch if I don't like what I see.</v>
       </c>
       <c r="J70" t="str">
-        <v>做一个小工具，让我可以选几个描述宠物气质的词——比如慵懒、蓬松、暴躁、傻乎乎——然后根据这些词给我生成一批真正符合那种性格的可爱名字，这样我就不用去搜那种千篇一律的宠物名字大全了，每次显示大概8个名字建议，如果不满意还能点按钮换一批新的。</v>
+        <v>做一个小工具，让我能选几个描述宠物气质的词——比如慵懒、毛茸茸、臭脸、傻乎乎之类的——然后它会根据这些性格特点给我生成一堆可爱的名字，这样就不用去搜那种千篇一律的宠物名字大全了，能找到一个真正对味的名字。每次展示八个左右的名字建议，如果看了不喜欢，可以点个按钮换一批新的。</v>
       </c>
       <c r="K70" t="str">
         <v/>
@@ -2890,10 +2890,10 @@
         <v>16208</v>
       </c>
       <c r="I71" t="str">
-        <v>A dice rolling page for D&amp;D sessions where you can tap the different dice types — d4, d6, d8, d10, d12, d20 — and it shows a big satisfying result number, then underneath automatically pulls a matching encounter from a table, like "a goblin scouting party" or "abandoned campfire still warm", so my friends and I don't have to dig through rulebooks mid-game to figure out what we run into next.</v>
+        <v>A dice rolling app for D&amp;D sessions where you can tap the different dice types — d4, d6, d8, d10, d12, d20 — and it shows a big satisfying result number, then underneath automatically pulls a matching encounter from a table, like "a goblin scouting party" or "abandoned campfire still warm", so my friends and I don't have to dig through rulebooks mid-game to figure out what we run into next.</v>
       </c>
       <c r="J71" t="str">
-        <v>做一个跑团用的掷骰页面，可以点击不同的骰子类型——d4、d6、d8、d10、d12、d20——掷完之后大大地显示结果数字，然后在下方根据点数自动从遭遇表里匹配一条对应内容，比如"一队哥布林斥候"或者"尚有余温的废弃营地"，这样我和朋友打游戏的时候就不用临时翻规则书去查下一个遭遇是什么了。</v>
+        <v>做一个跑团专用的骰子应用，可以点击不同面数的骰子——d4、d6、d8、d10、d12、d20——然后大大地显示出投掷结果，下方自动根据点数从遭遇表里匹配一条随机事件，比如"一支哥布林侦察小队"或者"一处还有余温的废弃营地"，这样我和朋友打本的时候就不用在游戏进行到一半时翻规则书去查下一个遭遇是什么了。</v>
       </c>
       <c r="K71" t="str">
         <v/>
@@ -2928,7 +2928,7 @@
         <v>Build a mobile tool app that has a "simple mode" you can turn on when your brain is just too tired to deal with a bunch of tiny buttons and cluttered screens — like after a long shift or during exam week — where everything gets stripped down to just the few things you actually need, the text gets bigger, and there's only one thing to tap at a time so you don't accidentally do the wrong thing, and it should remember you had it on so you don't have to go hunting through settings every time to switch it back.</v>
       </c>
       <c r="J72" t="str">
-        <v>做一个手机工具应用，里面有一个"简单模式"，专门给那种脑子已经转不动、懒得对付一堆小按钮和乱糟糟界面的时候用——比如上完一个大夜班之后，或者考试周熬夜的时候——开启之后把所有东西都精简掉，只留下真正用得着的几个功能，字体变大，每次只有一个按钮可以点，这样就不会手滑按错，而且要记住上次有没有开过这个模式，下次打开直接保持原样，不用每次都去设置里翻来翻去重新打开。</v>
+        <v>做一个手机工具类应用，里面有一个"简洁模式"，专门应对那种大脑已经累到不想对付一堆小按钮和乱糟糟界面的时候——比如上完一个长班之后，或者考试周期间——开启之后把界面精简到只剩真正用得到的那几个功能，字体也变大，每次只有一个可以点的东西，这样就不会手滑误操作，而且应用要记住你上次开了这个模式，下次打开直接保持原样，不用每次都跑去设置里重新找开关。</v>
       </c>
       <c r="K72" t="str">
         <v/>
@@ -2960,10 +2960,10 @@
         <v>10990</v>
       </c>
       <c r="I73" t="str">
-        <v>Create a mobile page where I can upload a video and it just automatically figures out what people are saying and puts the words on screen as subtitles — I'm tired of watching lecture recordings or meeting clips and having to strain to catch every word, so I just want to drop the video in, wait a bit, and then watch it back with the captions already burned into the bottom of the video so I don't have to keep rewinding.</v>
+        <v>Create a mobile app where I can upload a video and it just automatically figures out what people are saying and puts the words on app as subtitles — I'm tired of watching lecture recordings or meeting clips and having to strain to catch every word, so I just want to drop the video in, wait a bit, and then watch it back with the captions already burned into the bottom of the video so I don't have to keep rewinding.</v>
       </c>
       <c r="J73" t="str">
-        <v>做一个手机页面，让我能上传视频，然后它自动识别里面的人说了什么，把文字以字幕的形式显示在画面上——我实在受够了看课程录像或者会议片段时要使劲竖起耳朵听每一个字，我就想把视频丢进去，等一会儿，然后直接看一个底部已经烧录好字幕的视频，再也不用反复回放了。</v>
+        <v>做一个手机app，让我可以上传视频，然后它自动识别里面的人说了什么，把字幕直接显示在app里——我实在受够了看课程录像或者会议片段还要竖起耳朵使劲听每一个字，我就想把视频丢进去，等一会儿，然后直接看带字幕的版本，字幕已经压在视频底部了，这样我就不用反复倒带了。</v>
       </c>
       <c r="K73" t="str">
         <v/>
@@ -2995,10 +2995,10 @@
         <v>15125</v>
       </c>
       <c r="I74" t="str">
-        <v>Voice control that floats on the screen the whole time so I never have to tap around looking for the right button — when I hold it and say something like "go to settings" or "search for flights tomorrow" it just does it, and while I'm talking it shows me the words it's picking up so I can tell if it misheard me before it actually runs the command. The button should sit somewhere my thumb can reach without shifting my grip and there should be a tiny list of common commands I can glance at if I forget what to say.</v>
+        <v>Voice control that floats on the app the whole time so I never have to tap around looking for the right button — when I hold it and say something like "go to settings" or "search for flights tomorrow" it just does it, and while I'm talking it shows me the words it's picking up so I can tell if it misheard me before it actually runs the command. The button should sit somewhere my thumb can reach without shifting my grip and there should be a tiny list of common commands I can glance at if I forget what to say.</v>
       </c>
       <c r="J74" t="str">
-        <v>屏幕上要有一个一直悬浮的语音控制按钮，这样我就不用到处找按钮了——长按住说"去设置"或者"搜索明天的航班"之类的话，它直接就执行，而且我说话的时候要实时把识别到的文字显示出来，这样在真正执行命令之前我能看出来有没有听错。按钮的位置要在拇指自然能够到的地方，不用换握姿，另外还要有一个小小的常用指令列表，忘了说什么的时候能瞄一眼。</v>
+        <v>一个始终悬浮在应用界面上的语音控制按钮，这样我就不用到处找按钮了——长按住它说"去设置"或者"搜索明天的航班"之类的话，它直接就执行，而且我说话的时候界面上会实时显示识别到的文字，这样在真正执行指令之前我就能看出它有没有听错。按钮的位置要在大拇指自然能够到的地方，不需要换握姿，另外还要有一个小小的常用指令列表，忘了说什么的时候可以瞄一眼。</v>
       </c>
       <c r="K74" t="str">
         <v/>
@@ -3030,10 +3030,10 @@
         <v>14475</v>
       </c>
       <c r="I75" t="str">
-        <v>Make a simple screen where I can adjust how strong and what kind of vibration my phone does for different things, like I'm so tired of my phone buzzing way too hard during meetings or barely feeling it when I actually need to notice something, so I want sliders to set how strong the buzz is and a few preset patterns I can tap to feel before saving them, and it should remember different settings for like silent mode versus normal mode so I don't have to keep changing it every time.</v>
+        <v>Make a simple app where I can adjust how strong and what kind of vibration my phone does for different things, like I'm so tired of my phone buzzing way too hard during meetings or barely feeling it when I actually need to notice something, so I want sliders to set how strong the buzz is and a few preset patterns I can tap to feel before saving them, and it should remember different settings for like silent mode versus normal mode so I don't have to keep changing it every time.</v>
       </c>
       <c r="J75" t="str">
-        <v>做一个可以调整手机震动强度和震动类型的设置页面，我现在真的很烦，开会的时候震动强得吓人，但真正需要注意到通知的时候又几乎感觉不到，所以我想要能分别调节震动强弱的滑块，还有几种预设的震动模式可以直接点一下感受一下效果再决定要不要保存，另外最好能分开记住静音模式和正常模式下各自的震动设置，这样我就不用每次切换都重新调一遍了。</v>
+        <v>做一个可以调节手机震动强度和震动类型的简单应用，针对不同场景分别设置，因为真的很烦每次开会时手机震得太猛，或者真正需要注意到来电通知时又完全感觉不到，所以希望有滑块来调整震动力度，还有几个预设震动模式可以点一下先试试感觉再保存，另外要能分别记住静音模式和正常模式下的不同设置，这样就不用每次手动来回切换了。</v>
       </c>
       <c r="K75" t="str">
         <v/>
@@ -3065,10 +3065,10 @@
         <v>16594</v>
       </c>
       <c r="I76" t="str">
-        <v>Need a mobile tool that lets someone control their whole phone using just one or two physical buttons instead of having to tap all over the screen — basically a switch scanning mode for people who can't easily use their hands — because my relative has limited hand movement and right now using any app takes way too long since they struggle to hit the right spot on the touchscreen, so I want something where a single switch button can cycle through the items on screen one by one and then confirm a selection, and there should be a way to adjust how fast it scans so it's not too rushed or too slow for them to keep up.</v>
+        <v>Need a mobile tool that lets someone control their whole phone using just one or two physical buttons instead of having to tap all over the app — basically a switch scanning mode for people who can't easily use their hands — because my relative has limited hand movement and right now using any app takes way too long since they struggle to hit the right spot on the touchscreen, so I want something where a single switch button can cycle through the items on app one by one and then confirm a selection, and there should be a way to adjust how fast it scans so it's not too rushed or too slow for them to keep up.</v>
       </c>
       <c r="J76" t="str">
-        <v>想做一个手机端的辅助工具，让用户只需要按一两个实体按键就能操控整个手机，不用在屏幕上到处点——说白了就是针对手部行动不便的人设计的开关扫描模式。我有个亲戚手部活动受限，现在用任何一个app都特别费劲，因为他很难准确点到触摸屏上的目标位置。我希望做成这样：按一下开关按键，屏幕上的元素就一个一个轮流高亮，再按一下就能确认当前选中的项目；同时还需要一个可以调节扫描速度的设置，让他可以按照自己的节奏来，不会太快跟不上、也不会太慢等得烦。</v>
+        <v>需要做一个手机工具，让用户只靠一两个实体按键就能操控整个手机，不用在屏幕上到处点——也就是一种开关扫描模式，专门为手部活动不便的人设计——因为我有个亲属手部活动受限，现在用任何 app 都特别费劲，根本点不准屏幕上的位置，所以我想要那种用单个开关按键就能逐个切换界面元素、然后确认选中的方式，同时还得有办法调节扫描速度，让他们能跟上节奏，不会太快也不会太慢。</v>
       </c>
       <c r="K76" t="str">
         <v/>
@@ -3103,7 +3103,7 @@
         <v>Make a bubble level tool for my phone so I can hang pictures straight on the wall without having to borrow a real one from a neighbor — I want to see that classic ball-in-a-circle bubble thing that floats around when I tilt my phone, and it should turn green and maybe give a little vibration when I've got it perfectly level, with a plain dark background so the bubble is easy to see even in bad lighting.</v>
       </c>
       <c r="J77" t="str">
-        <v>帮我做一个手机水平仪工具，这样挂画的时候就不用再去邻居家借真水平仪了——我想要那种经典的"圆圈里有个气泡球"的效果，手机倾斜的时候气泡会跟着晃动，当手机完全水平时气泡变成绿色，最好再震动一下提示我，背景用简单的深色，这样就算光线不好也能清楚看到气泡。</v>
+        <v>做一个手机用的水平仪，这样挂画的时候就不用跑去借邻居的真水平仪了——我想看到那种经典的圆圈里有个小球的气泡效果，倾斜手机的时候小球会跟着晃动，校准到完全水平时变成绿色，最好还能轻轻震动一下提示我，背景用简单的深色，这样就算光线不好也能看清楚气泡在哪里。</v>
       </c>
       <c r="K77" t="str">
         <v/>
@@ -3135,10 +3135,10 @@
         <v>13022</v>
       </c>
       <c r="I78" t="str">
-        <v>Create a mobile screen ruler tool that actually matches real-world measurements — like when I hold my phone up to a piece of paper I want to cut, the ruler on screen should show actual centimeters and inches that line up for real, not just pixels stretched weirdly across different phone sizes, so I need it to ask me what phone I have or let me pick from a list so it can figure out the right scale, and then show a clean ruler along the edge of the screen I can slide my finger along to measure small things like fabric scraps or card sizes.</v>
+        <v>Create a mobile app ruler tool that actually matches real-world measurements — like when I hold my phone up to a piece of paper I want to cut, the ruler on app should show actual centimeters and inches that line up for real, not just pixels stretched weirdly across different phone sizes, so I need it to ask me what phone I have or let me pick from a list so it can figure out the right scale, and then show a clean ruler along the edge of the app I can slide my finger along to measure small things like fabric scraps or card sizes.</v>
       </c>
       <c r="J78" t="str">
-        <v>做一个手机屏幕上的尺子工具，要能真正对应现实中的实际尺寸——就是说我把手机贴在要裁剪的纸旁边时，屏幕上显示的刻度必须是真实的厘米和英寸，能和实物对齐，而不是根据不同手机屏幕大小随便拉伸像素那种，所以需要让用户选择自己用的是什么型号的手机，或者从列表里挑，这样才能算出正确的缩放比例，然后在屏幕边缘展示一把干净整洁的尺子，用户可以用手指沿着滑动来测量像布料碎片或卡片这类小东西的尺寸。</v>
+        <v>做一个手机端的标尺工具，要能真正对应现实中的实际尺寸——比如我把手机贴着要裁剪的纸张比划的时候，app上的刻度显示的厘米和英寸得跟真实长度对得上，不能只是把像素随便拉伸一下在不同手机上糊弄人，所以需要让用户选择自己的手机型号，或者从列表里挑，这样app才能算出正确的缩放比例，然后在屏幕边缘展示一把干净清晰的标尺，我可以用手指沿着它滑动来量一些小东西，比如布料边角料或者卡片的尺寸。</v>
       </c>
       <c r="K78" t="str">
         <v/>
@@ -3170,10 +3170,10 @@
         <v>15450</v>
       </c>
       <c r="I79" t="str">
-        <v>Build a simple metronome tool for my phone where I can either type in the BPM number directly or just tap a button a few times to figure out the tempo automatically, and there should be a little picker where I can choose different click sounds like a woodblock, a beep, or a cowbell kind of thing, plus a big start/stop button that's easy to hit while I'm playing guitar without looking too carefully at the screen.</v>
+        <v>Build a simple metronome tool for my phone where I can either type in the BPM number directly or just tap a button a few times to figure out the tempo automatically, and there should be a little picker where I can choose different click sounds like a woodblock, a beep, or a cowbell kind of thing, plus a big start/stop button that's easy to hit while I'm playing guitar without looking too carefully at the app.</v>
       </c>
       <c r="J79" t="str">
-        <v>帮我做一个手机用的简易节拍器，我可以直接输入 BPM 数值，也可以连续点几下按钮让它自动算出当前的速度，另外需要一个小选择器让我挑不同的节拍音效，比如木鱼声、滴滴声或者牛铃那种感觉，还要有一个超大的开始/停止按钮，方便我弹吉他的时候不用盯着屏幕也能准确按到。</v>
+        <v>帮我做一个手机用的简易节拍器，可以直接输入BPM数值，也能连续点几下按钮自动识别当前节奏，还要有个小选择器能切换不同的点击音效，比如木鱼声、电子滴声或者牛铃那种感觉，另外要有一个大大的开始/停止按钮，方便我弹吉他的时候不用太仔细盯着屏幕也能一下按到。</v>
       </c>
       <c r="K79" t="str">
         <v/>
@@ -3208,7 +3208,7 @@
         <v>Make a compass tool for my phone where I can put in the magnetic declination for wherever I am so the needle points to true north instead of magnetic north, because I keep getting confused when I'm out hiking and the map doesn't line up with what the compass says, and I want a simple dial or circle that shows the needle moving in real time plus a little spot where I can type in the declination number myself.</v>
       </c>
       <c r="J80" t="str">
-        <v>帮我做一个手机用的指南针工具，可以输入我当前所在地的磁偏角，让指针指向真北而不是磁北——我每次出去徒步都被搞晕，地图和指南针对不上根本没法用。我想要一个简单的表盘或者圆形界面，能实时显示指针的转动，再加一个小输入框，让我自己手动填写磁偏角的数值就行。</v>
+        <v>帮我做一个手机用的指南针工具，可以手动输入我所在位置的磁偏角，这样指针就能指向真北而不是磁北，因为我每次去徒步的时候总是搞不清楚，地图和指南针对不上，很烦。界面要有一个简单的刻度盘或圆形显示区，指针实时转动，另外还要有一个小输入框让我自己填磁偏角的数值。</v>
       </c>
       <c r="K80" t="str">
         <v/>
@@ -3243,7 +3243,7 @@
         <v>Build a phone mirror app that uses the front camera so I can use it like a real mirror, but with a few extra handy things — I want to be able to pinch to zoom in on a specific part of my face, tap a button to freeze the image so it stays still while I do my makeup or check something without having to hold the phone perfectly, and optionally turn on a light grid over the picture so I can line things up more evenly, like when I'm trying to get my eyeliner symmetrical or check if a sticker is straight on my face.</v>
       </c>
       <c r="J81" t="str">
-        <v>做一个用前置摄像头当镜子用的手机应用，让我可以像照真镜子一样用，但要多几个实用功能——我希望能捏合缩放来放大脸部某个局部，点一下按钮就能把画面冻住，这样我补妆或者检查什么的时候不用一直把手机拿得稳稳的，另外还想有个可以开关的辅助线网格叠在画面上，方便我对齐，比如画眼线的时候想看两边是不是对称，或者确认贴纸有没有贴歪。</v>
+        <v>做一个用前置摄像头当镜子用的手机应用，功能要跟真镜子一样，但再多几个实用的小功能——我想要能双指捏合缩放，放大看脸上某个局部；可以点一个按钮把画面冻住，这样我化妆或者检查什么细节的时候不用一直把手机拿得稳稳的；另外还想有个选项，可以在画面上叠加一层辅助网格线，方便对齐，比如画眼线的时候看两边对不对称，或者确认脸上贴的贴纸有没有歪。</v>
       </c>
       <c r="K81" t="str">
         <v/>
@@ -3275,10 +3275,10 @@
         <v>17552</v>
       </c>
       <c r="I82" t="str">
-        <v>Create a chemistry periodic table element quiz page for a study app where you go through elements one at a time like flashcards — the front shows just the element symbol, and when you tap it, it flips to reveal the full name, atomic number, and element category. I want a simple way to mark each one as "got it" or "still learning" so the app can keep track of which ones I need to review again, and there should be a small progress indicator at the top so I can see how far I am through the current set.</v>
+        <v>Create a chemistry periodic table element quiz app for a study app where you go through elements one at a time like flashcards — the front shows just the element symbol, and when you tap it, it flips to reveal the full name, atomic number, and element category. I want a simple way to mark each one as "got it" or "still learning" so the app can keep track of which ones I need to review again, and there should be a small progress indicator at the top so I can see how far I am through the current set.</v>
       </c>
       <c r="J82" t="str">
-        <v>做一个化学元素周期表的背单词测验页面，用于学习类应用，每次显示一个元素，像翻卡片一样——正面只显示元素符号，点击后翻转到背面，展示完整名称、原子序数和元素分类。我希望有一个简单的方式来标记每张卡片是"已掌握"还是"还在学"，方便应用记录哪些元素需要再次复习，另外页面顶部要有一个小的进度条或进度提示，让我知道当前这组卡片做到哪了。</v>
+        <v>帮我做一个化学元素周期表的闯关测验应用，用在学习类 App 里。形式类似抽认卡，每次只显示一个元素——正面只展示元素符号，点击后卡片翻转，背面显示元素全名、原子序数和元素分类。我希望有一个简单的方式来标记每张卡是"已掌握"还是"仍需学习"，这样 App 可以记录哪些元素需要再次复习。另外顶部要有一个小进度条，让我能随时看到当前这组卡片完成了多少。</v>
       </c>
       <c r="K82" t="str">
         <v/>
@@ -3313,7 +3313,7 @@
         <v>Build a flashcard app for memorizing programming language keywords where each card shows the keyword name on the front and the correct syntax plus a short usage example on the back, I want to be able to flip through cards one by one and mark each one as "got it" or "still learning" so I can keep track of my progress, and the cards should be sorted by language like Python, JavaScript, or Java so I can go through one language at a time without mixing everything up.</v>
       </c>
       <c r="J83" t="str">
-        <v>做一个用来记忆编程语言关键字的闪卡应用，每张卡片正面显示关键字名称，背面显示对应的正确语法和一个简短的使用示例，我希望能够一张一张地翻看卡片，并把每张标记为"已掌握"或"还在学"，这样可以随时了解自己的学习进度，另外卡片要按编程语言分类，比如 Python、JavaScript、Java 各归各的，这样我可以每次只专注学一门语言，不把不同语言的内容混在一起。</v>
+        <v>做一个用来记忆编程语言关键字的闪卡应用，每张卡片正面显示关键字名称，背面显示正确的语法格式和一个简短的使用示例，我希望能一张一张地翻阅卡片，并且可以把每张标记为"已掌握"或"还在学"，这样方便追踪自己的学习进度，另外卡片要按编程语言分类，比如 Python、JavaScript、Java 各归各的，这样我可以一次只专注学一门语言，不会把所有内容混在一起。</v>
       </c>
       <c r="K83" t="str">
         <v/>
@@ -3348,7 +3348,7 @@
         <v>Create a history date and event memory flashcard app where I can flip through cards that each show a specific date on the front and the matching historical event on the back, and I want to be able to mark each card as "remembered" or "need to review again" so I can keep a clear record of which ones I still need to work on, and it should also let me organize the cards by time period like ancient history, modern history, and so on so everything stays in order and easy to find.</v>
       </c>
       <c r="J84" t="str">
-        <v>做一个历史日期与事件记忆闪卡应用，我可以翻看每张卡片，正面显示具体日期，背面显示对应的历史事件，同时能把每张卡片标记为"已记住"或"需要再复习"，方便随时掌握哪些还没背熟，另外还希望能按时间段来整理卡片，比如古代史、近现代史之类的分类，让所有内容都井井有条、方便查找。</v>
+        <v>做一个历史日期与事件记忆闪卡应用，每张卡片正面显示具体日期，背面显示对应的历史事件，我可以翻转卡片来记忆内容，同时能把每张卡标记为"已记住"或"需要再复习"，方便随时掌握哪些还没掌握，另外还希望能按时间段对卡片进行分类整理，比如古代史、近现代史之类的，让所有内容保持有序、便于查找。</v>
       </c>
       <c r="K84" t="str">
         <v/>
@@ -3380,10 +3380,10 @@
         <v>14707</v>
       </c>
       <c r="I85" t="str">
-        <v>Flashcard screen for bar exam legal definitions where each card shows the term on one side and the full definition on the back when you tap to flip it, with the cards grouped by subject area like Contracts, Torts, Criminal Law, and Constitutional Law so I can go through one section at a time without mixing everything together. There should be a simple way to mark each card as "got it" or "still working on it" so I always know exactly which ones I still need to review.</v>
+        <v>Flashcard app for bar exam legal definitions where each card shows the term on one side and the full definition on the back when you tap to flip it, with the cards grouped by subject area like Contracts, Torts, Criminal Law, and Constitutional Law so I can go through one app at a time without mixing everything together. There should be a simple way to mark each card as "got it" or "still working on it" so I always know exactly which ones I still need to review.</v>
       </c>
       <c r="J85" t="str">
-        <v>律师资格考试法律术语记忆卡片界面，每张卡片正面显示术语名称，点击翻转后背面展示完整释义。卡片按学科分类整理，包括合同法、侵权法、刑法和宪法，方便我每次专注复习一个模块，不同科目的内容互不混淆。同时需要一个简单的标记功能，让我能把每张卡片标注为"已掌握"或"还在练"，这样随时都能清楚知道哪些内容还需要继续复习。</v>
+        <v>做一个用于司法考试法律术语记忆的闪卡应用，每张卡片正面显示术语，点击翻转后背面展示完整释义。卡片按学科分类整理，比如合同法、侵权法、刑法和宪法，这样我可以一次专注于一个模块，不会把所有内容混在一起。另外需要一个简单的标记功能，让我能把每张卡片标为"已掌握"或"还在练"，这样随时都能清楚地知道哪些还需要继续复习。</v>
       </c>
       <c r="K85" t="str">
         <v/>
@@ -3415,10 +3415,10 @@
         <v>14020</v>
       </c>
       <c r="I86" t="str">
-        <v>Make a bar exam multiple choice question bank for mobile where questions are organized by subject area so I can work through them one category at a time, and I want to be able to see at a glance how many questions I've finished and how many I got wrong in each section, plus have a separate place where I can go back and redo only the ones I answered incorrectly.</v>
+        <v>Make a bar exam multiple choice question bank for mobile where questions are organized by subject area so I can work through them one category at a time, and I want to be able to see at a glance how many questions I've finished and how many I got wrong in each app, plus have a separate place where I can go back and redo only the ones I answered incorrectly.</v>
       </c>
       <c r="J86" t="str">
-        <v>做一个手机端的司法考试选择题题库，题目按科目分类整理，方便我一个专题一个专题地刷，同时能一眼看出每个科目已经完成了多少题、答错了几道，另外还要有个单独的地方，专门用来重做之前答错的题目。</v>
+        <v>做一个手机端的法考选择题题库，题目按科目分类整理，这样我可以一个模块一个模块地刷，每个科目里能一眼看到已完成多少题、答错了多少题，另外还要有一个单独的错题专区，方便我随时回去只重做答错的那些题。</v>
       </c>
       <c r="K86" t="str">
         <v/>
@@ -3450,10 +3450,10 @@
         <v>10230</v>
       </c>
       <c r="I87" t="str">
-        <v>Create a mobile quiz page for USMLE Step 1 clinical case practice where each question shows a short patient scenario at the top, then four answer choices below it, and after I pick one it immediately shows whether I got it right or wrong along with a brief explanation of why — I want to be able to track how many questions I've done and how many I got correct in a simple running count at the top of the screen, and there should be a clear way to move to the next question without accidentally skipping the explanation.</v>
+        <v>Create a mobile quiz app for USMLE Step 1 clinical case practice where each question shows a short patient scenario at the top, then four answer choices below it, and after I pick one it immediately shows whether I got it right or wrong along with a brief explanation of why — I want to be able to track how many questions I've done and how many I got correct in a simple running count at the top of the app, and there should be a clear way to move to the next question without accidentally skipping the explanation.</v>
       </c>
       <c r="J87" t="str">
-        <v>做一个手机端的USMLE Step 1临床病例练习答题页面，每道题顶部显示一段简短的患者病例描述，下方列出四个选项，选完之后立即反馈答对还是答错，并附上简要解析说明原因——我希望页面顶部有一个简单的累计计数，能实时显示我已完成的题数和答对的题数，同时要有一个明确的"下一题"按钮，确保我看完解析之后再跳转，不会误操作跳过解析。</v>
+        <v>做一个手机端的 USMLE Step 1 临床病例刷题应用，每道题顶部显示一段简短的患者情景描述，下方列出四个选项，选完之后立即告诉我答对还是答错，并附上简短的解析说明为什么——我希望在应用顶部有一个实时计数，能看到我一共做了多少题、答对了多少题，同时要有一个明确的"下一题"按钮，让我在看完解析之前不会误操作跳过。</v>
       </c>
       <c r="K87" t="str">
         <v/>
@@ -3488,7 +3488,7 @@
         <v>Build a mobile study app for PMP project management scenario questions where I can practice exam-style situations like handling scope changes, dealing with a team conflict, or deciding what to do when a project is behind schedule, and I want each question to show the four answer choices clearly one by one so I can think before I tap, then after I answer it should tell me which option is correct and give a short reason why, and I also want to keep a simple list of all the questions I got wrong so I can go back and review just those ones later.</v>
       </c>
       <c r="J88" t="str">
-        <v>做一个手机端的PMP项目管理情景题练习应用，支持练习考试风格的场景题，比如如何处理范围变更、解决团队冲突、或者项目进度落后时该怎么办，每道题的四个选项要清晰地逐一呈现，让我有时间思考后再点击作答，答完之后告诉我哪个选项是正确的，并给出简短的解析说明原因，同时还要有一个简单的错题列表，把我答错的题都记录下来，方便我之后随时回来专门复习这些题。</v>
+        <v>做一个手机端的PMP项目管理备考应用，专门用来练习情景判断题，比如如何处理范围变更、解决团队冲突，或者项目进度落后时该怎么办，每道题要把四个选项一个一个清晰地展示出来，让我有时间思考再点选，答完之后告诉我哪个选项是正确答案并给出简短的解析说明原因，另外还需要有一个简单的错题本，把我答错的题目都记录下来，方便我之后单独回去复习。</v>
       </c>
       <c r="K88" t="str">
         <v/>
@@ -3520,10 +3520,10 @@
         <v>13115</v>
       </c>
       <c r="I89" t="str">
-        <v>A practice quiz screen for CPA financial accounting exam prep where questions are organized by topic — things like revenue recognition, inventory valuation, and lease accounting — so I can go through one category at a time and not have everything mixed up randomly. Each question should clearly show whether my last answer was right or wrong, and once I finish a topic batch there should be a small results summary telling me how many I got correct out of how many I tried, so I know exactly where I still need to review.</v>
+        <v>A practice quiz app for CPA financial accounting exam prep where questions are organized by topic — things like revenue recognition, inventory valuation, and lease accounting — so I can go through one category at a time and not have everything mixed up randomly. Each question should clearly show whether my last answer was right or wrong, and once I finish a topic batch there should be a small results summary telling me how many I got correct out of how many I tried, so I know exactly where I still need to review.</v>
       </c>
       <c r="J89" t="str">
-        <v>CPA财务会计备考练习题界面，题目按专题分类整理——比如收入确认、存货计价、租赁会计等——这样我可以一个专题一个专题地刷题，不会所有题目都混在一起随机出现。每道题要清楚显示我上一次作答是对还是错，做完一个专题的题目后还要有一个小的结果汇总，告诉我答对了几道、一共做了几道，让我清楚知道哪些地方还需要重点复习。</v>
+        <v>做一个CPA财务会计备考刷题应用，题目要按专题分类整理，比如收入确认、存货计价、租赁会计这些知识点，让我可以一次专门刷一个专题，不要把所有题目随机混在一起。每道题都要清楚地标出我上一次作答是对还是错，刷完一个专题之后要有一个小结页面，显示这个专题我一共做了多少题、答对了多少，这样我就能清楚地知道自己哪些地方还需要继续复习。</v>
       </c>
       <c r="K89" t="str">
         <v/>
@@ -3555,10 +3555,10 @@
         <v>13330</v>
       </c>
       <c r="I90" t="str">
-        <v>A workout skill milestone tracker screen where each exercise skill — things like pull-ups, handstands, or push-up variations — has its own little progress path laid out from beginner level to advanced, with clearly labeled steps I can check off one by one as I hit them, and I really want two things: first, a small visual bar or something showing how far I've gotten through that skill overall, and second, a section that lists my recently completed milestones so I can look back and see what I've actually accomplished instead of just seeing what's left.</v>
+        <v>A workout skill milestone tracker app where each exercise skill — things like pull-ups, handstands, or push-up variations — has its own little progress path laid out from beginner level to advanced, with clearly labeled steps I can check off one by one as I hit them, and I really want two things: first, a small visual bar or something showing how far I've gotten through that skill overall, and second, an app that lists my recently completed milestones so I can look back and see what I've actually accomplished instead of just seeing what's left.</v>
       </c>
       <c r="J90" t="str">
-        <v>想做一个健身技能里程碑追踪页面，每项动作技能——比如引体向上、倒立、各种俯卧撑变体——都有自己独立的进阶路径，从入门级一直延伸到高级，每个阶段都有清晰的标注，我可以逐一打卡完成。我特别想要两个功能：第一，每项技能下面要有一个小进度条或者类似的可视化组件，能直观看出我在这个技能上总体完成了多少；第二，页面里要有一个专区，列出我最近打卡完成的里程碑记录，这样我能回头看看自己实际攒下了哪些成果，而不是只盯着还剩多少没做。</v>
+        <v>一个健身技能里程碑追踪应用，每项运动技能——比如引体向上、倒立或各种俯卧撑变式——都有自己专属的一条进阶路径，从入门级一路延伸到高阶，每个阶段都有清晰的步骤标注，达到之后可以逐一打勾；我特别希望实现两点：第一，每项技能要有一个小进度条或类似的可视化元素，能直观显示我在这项技能上的整体完成进度；第二，应用要有一个板块专门列出我最近完成的里程碑，让我能回头看看自己到底练成了哪些东西，而不是只看到还剩多少没完成。</v>
       </c>
       <c r="K90" t="str">
         <v/>
@@ -3590,10 +3590,10 @@
         <v>12152</v>
       </c>
       <c r="I91" t="str">
-        <v>Make a music practice session log screen where I can record each session by song name, how many minutes I practiced, and a short note on what I focused on, and each song should have its own little progress section showing milestones I can mark off one by one — like "learned intro," "memorized chorus," "played full song clean" — so I can clearly see how far along I am with each piece without having to dig through old entries.</v>
+        <v>Make a music practice session log app where I can record each session by song name, how many minutes I practiced, and a short note on what I focused on, and each song should have its own little progress app showing milestones I can mark off one by one — like "learned intro," "memorized chorus," "played full song clean" — so I can clearly see how far along I am with each piece without having to dig through old entries.</v>
       </c>
       <c r="J91" t="str">
-        <v>做一个音乐练习记录页面，能按曲目名称记录每次练习，填写练习时长（分钟数）以及本次重点练了什么的简短备注。每首曲目要有一个独立的进度模块，里面是可以逐一勾选的里程碑节点，比如"学会前奏""背熟副歌""完整流畅演奏全曲"，让我不用翻旧记录就能一眼看出每首曲子目前练到哪个阶段了。</v>
+        <v>做一个音乐练习记录应用，让我能按曲目名称、练习时长（分钟数）和简短的练习重点备注来记录每次练习；每首曲子都要有自己的小进度追踪器，里面列出可以逐一打卡的里程碑节点——比如"学会前奏""背熟副歌""完整弹下来不出错"——这样我不用翻以前的记录，就能一眼看出每首曲子练到哪里了。</v>
       </c>
       <c r="K91" t="str">
         <v/>
@@ -3625,10 +3625,10 @@
         <v>14249</v>
       </c>
       <c r="I92" t="str">
-        <v>Need a calendar page for a math study tracking app that shows how well I've learned each topic using color blocks — darker color means I've really nailed that topic, lighter means I still need to review it. I want to tap on any day and see a neat list of exactly which math topics I practiced that day and how strong my understanding was for each one, and the calendar should make it easy to spot at a glance which topics I've been skipping for too many days in a row.</v>
+        <v>Need a calendar app for a math study tracking app that shows how well I've learned each topic using color blocks — darker color means I've really nailed that topic, lighter means I still need to review it. I want to tap on any day and see a neat list of exactly which math topics I practiced that day and how strong my understanding was for each one, and the calendar should make it easy to spot at a glance which topics I've been skipping for too many days in a row.</v>
       </c>
       <c r="J92" t="str">
-        <v>需要为一个数学学习追踪应用做一个日历页面，用色块来直观呈现每个知识点的掌握程度——颜色越深代表这个知识点已经学得很扎实，颜色越浅则说明还需要继续复习。我希望点击任意一天后，能看到一个清晰的列表，显示当天具体练习了哪些数学知识点，以及每个知识点的理解程度。另外，日历还应该让我一眼就能看出哪些知识点已经连续好多天没有复习了。</v>
+        <v>想给一个数学学习追踪应用做一个日历功能，用色块来直观展示每个知识点的掌握程度——颜色越深说明这个知识点已经吃透了，颜色越浅说明还需要继续复习。希望能点击任意一天，看到一个清晰的列表，显示当天具体练习了哪些数学知识点，以及每个知识点的理解程度如何。另外，日历还要能让人一眼就看出哪些知识点已经连续好几天没有复习了。</v>
       </c>
       <c r="K92" t="str">
         <v/>
@@ -3660,10 +3660,10 @@
         <v>13601</v>
       </c>
       <c r="I93" t="str">
-        <v>A grammar rule completion progress ring on the study check-in screen that shows exactly how many rules I've finished out of the total, with a circular ring that fills in as I complete each one and a number in the center showing the percentage, plus a small line of text underneath like "8 of 25 rules completed" so I always know where I stand — I want the ring to turn a different color, maybe gold or green, once I hit 100% so it feels satisfying when I finish the whole set.</v>
+        <v>A grammar rule completion progress ring on the study check-in app that shows exactly how many rules I've finished out of the total, with a circular ring that fills in as I complete each one and a number in the center showing the percentage, plus a small line of text underneath like "8 of 25 rules completed" so I always know where I stand — I want the ring to turn a different color, maybe gold or green, once I hit 100% so it feels satisfying when I finish the whole set.</v>
       </c>
       <c r="J93" t="str">
-        <v>学习打卡页面上有一个语法规则完成进度环，能清楚显示我已学完的规则数量和总数的比例——圆环随着每条规则的完成逐渐填充，中间显示当前百分比，下方还有一行小字，比如"已完成 25 条中的 8 条"，让我随时掌握自己的进度。我希望完成全部规则、达到 100% 时，圆环能变成另一种颜色，比如金色或绿色，这样全部学完的时候会有一种满满的成就感。</v>
+        <v>学习打卡应用里有一个语法规则完成进度环，能清楚显示我已经学完了多少条规则、总共有多少条，圆环随着我完成每一条逐渐填充，中间显示百分比数字，下方还有一行小字比如"已完成 8 / 25 条规则"，让我随时掌握自己的进度——我希望完成全部规则、进度达到 100% 时圆环能变成另一种颜色，比如金色或绿色，这样学完整套规则的时候会有一种满满的成就感。</v>
       </c>
       <c r="K93" t="str">
         <v/>
@@ -3695,10 +3695,10 @@
         <v>10516</v>
       </c>
       <c r="I94" t="str">
-        <v>Build a mobile page for when a student finishes signing up for a course, where it clearly shows a confirmation that they're enrolled, then walks them through what to do next in a few simple steps — things like when the first class starts, where to find their materials, and how to reach the teacher — and I want each step to feel like a checklist item so nothing gets missed, with a clear button at the end to go straight into the course.</v>
+        <v>Build a mobile app for when a student finishes signing up for a course, where it clearly shows a confirmation that they're enrolled, then walks them through what to do next in a few simple steps — things like when the first class starts, where to find their materials, and how to reach the teacher — and I want each step to feel like a checklist item so nothing gets missed, with a clear button at the end to go straight into the course.</v>
       </c>
       <c r="J94" t="str">
-        <v>做一个手机端页面，用于学生完成课程报名之后的跳转，页面上要醒目地显示报名成功的确认信息，然后用几个简单的步骤引导他们接下来该做什么——比如第一节课什么时候开始、去哪里找课程资料、怎么联系老师这类内容，每个步骤都要有清单打勾那种感觉，让人一目了然、不会遗漏，最后放一个明显的按钮，点击后直接进入课程。</v>
+        <v>做一个移动端页面，用于学生完成课程报名后的确认环节——页面要清晰显示已成功报名的提示，然后用几个简单的步骤引导他们了解接下来该做什么，比如第一节课什么时候开始、去哪里找学习资料、怎么联系老师等，每个步骤都要有清单条目的感觉，让人一目了然、不会遗漏，最后放一个醒目的按钮，直接跳转进入课程。</v>
       </c>
       <c r="K94" t="str">
         <v/>
@@ -3730,10 +3730,10 @@
         <v>9204</v>
       </c>
       <c r="I95" t="str">
-        <v>Build a mobile page for an instructor profile that clearly shows their name, photo, and a short bio at the top, then lists their credentials and certifications one by one in a clean section below, and includes a star rating along with a count of how many students have rated them so I can quickly judge whether the instructor is trustworthy before signing up for a course.</v>
+        <v>Build a mobile app for an instructor profile that clearly shows their name, photo, and a short bio at the top, then lists their credentials and certifications one by one in a clean app below, and includes a star rating along with a count of how many students have rated them so I can quickly judge whether the instructor is trustworthy before signing up for a course.</v>
       </c>
       <c r="J95" t="str">
-        <v>做一个讲师个人资料的移动端页面，顶部清晰展示讲师姓名、照片和简短介绍，下方用整洁的区块逐一列出他们的资质和认证信息，并显示星级评分及参与评价的学生人数，方便我在报名课程前快速判断这位讲师是否靠谱。</v>
+        <v>做一个教练个人主页的移动端应用，页面顶部要清晰展示教练的姓名、头像和简短介绍，下方用简洁的列表逐条列出他们的资质和认证信息，同时显示星级评分以及参与评分的学员人数，让我在报名课程前能快速判断这位教练是否值得信赖。</v>
       </c>
       <c r="K95" t="str">
         <v/>
@@ -3765,10 +3765,10 @@
         <v>21650</v>
       </c>
       <c r="I96" t="str">
-        <v>Create a student discussion board page for a course app where students can post questions and others can reply in threads under each post, I want each post to clearly show the student's name, the question text, and a small count of how many replies it has already, and when you tap into a post you can see all the replies lined up underneath in order so it's easy to follow who responded to whom, and the whole layout should be clean and not too busy so nothing feels cluttered when there are a lot of replies.</v>
+        <v>Create a student discussion board app for a course app where students can post questions and others can reply in threads under each post, I want each post to clearly show the student's name, the question text, and a small count of how many replies it has already, and when you tap into a post you can see all the replies lined up underneath in order so it's easy to follow who responded to whom, and the whole layout should be clean and not too busy so nothing feels cluttered when there are a lot of replies.</v>
       </c>
       <c r="J96" t="str">
-        <v>为课程应用做一个学生讨论板页面，学生可以在上面发布问题，其他人可以在每条帖子下面以回复串的形式跟帖，每条帖子要清楚地显示发帖学生的姓名、问题内容，以及已有多少条回复的小计数，点进帖子后能看到所有回复按顺序依次排列在下方，方便跟踪谁回复了谁，整体布局要简洁清爽，回复多的时候也不会显得杂乱拥挤。</v>
+        <v>为课程应用开发一个学生讨论板块，让学生可以发帖提问，其他人可以在每个帖子下以回复串的形式进行回复。每个帖子需要清晰展示发帖学生的姓名、问题内容，以及当前已有多少条回复的小计数。点进某个帖子后，可以按顺序看到所有回复依次排列在下方，方便追踪谁回复了谁。整体界面要简洁清爽，即使回复很多也不会显得拥挤杂乱。</v>
       </c>
       <c r="K96" t="str">
         <v/>
@@ -3800,10 +3800,10 @@
         <v>11201</v>
       </c>
       <c r="I97" t="str">
-        <v>Create a mobile page for submitting assignments where students can upload their work and also see the grading rubric right there on the same page, so they can check off each requirement before they hit submit — I want the rubric to show each criterion clearly with the point values next to it, and there should be a simple list of what files have been uploaded so nothing gets missed.</v>
+        <v>Create a mobile app for submitting assignments where students can upload their work and also see the grading rubric right there on the same app, so they can check off each requirement before they hit submit — I want the rubric to show each criterion clearly with the point values next to it, and there should be a simple list of what files have been uploaded so nothing gets missed.</v>
       </c>
       <c r="J97" t="str">
-        <v>做一个移动端的作业提交页面，学生可以在上面上传作业，同时在同一页面查看评分标准，方便在点击提交前逐项核对每条要求——评分标准要清晰地列出每个评分维度，并在旁边标注对应分值，另外还需要有一个简单的已上传文件清单，确保不会遗漏任何文件。</v>
+        <v>做一个用于提交作业的手机应用，学生可以在里面上传作业文件，同时在同一个页面直接查看评分标准，这样在点击提交之前就能逐条核对每项要求是否都达到了——评分标准要清晰列出每一个评分细则，旁边标注对应的分值，另外还要有一个简单的已上传文件列表，方便确认没有遗漏任何文件。</v>
       </c>
       <c r="K97" t="str">
         <v/>
@@ -3829,16 +3829,16 @@
         <v>medium</v>
       </c>
       <c r="G98">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H98">
         <v>16689</v>
       </c>
       <c r="I98" t="str">
-        <v>Need a simple Big-O cheatsheet page I can open on my phone whenever I blank out during coding problems or interviews, instead of digging through random articles every time — just a clean table showing all the common complexities like O(1), O(log n), O(n), O(n log n), O(n²) and so on, with a quick note next to each one saying which algorithms actually fall into that bucket, like "binary search is O(log n), bubble sort is O(n²)," that kind of thing, and maybe a tiny section for space complexity too so I don't have to keep two tabs open.</v>
+        <v>Need a simple Big-O cheatsheet app I can open on my phone whenever I blank out during coding problems or interviews, instead of digging through random articles every time — just a clean table showing all the common complexities like O(1), O(log n), O(n), O(n log n), O(n²) and so on, with a quick note next to each one saying which algorithms actually fall into that bucket, like "binary search is O(log n), bubble sort is O(n²)," that kind of thing, and maybe an app for space complexity too so I don't have to keep two tabs open.</v>
       </c>
       <c r="J98" t="str">
-        <v>想做一个简单的 Big-O 速查页面，刷题或者面试突然脑子空白的时候直接掏出手机看，不用每次都去翻各种文章——就是一张干净的表格，把常见的时间复杂度都列出来，比如 O(1)、O(log n)、O(n)、O(n log n)、O(n²) 这些，然后每行旁边附一句简短说明，标注哪些算法属于这个复杂度，像"二分查找是 O(log n)，冒泡排序是 O(n²)"这种感觉，另外最好再加一个小板块讲空间复杂度，这样就不用同时开两个标签页了。</v>
+        <v>想做一个简单的大O复杂度速查小应用，刷题或者面试的时候脑子突然卡壳了，掏出手机就能看，省得每次还要翻一堆文章——就是一张干净的表格，把常见的时间复杂度都列出来，像O(1)、O(log n)、O(n)、O(n log n)、O(n²)这些，然后每个旁边附一句简短的说明，点出哪些算法属于这个级别，比如"二分查找是O(log n)，冒泡排序是O(n²)"之类的，最好再加一个空间复杂度的模块，这样就不用同时开两个标签页了。</v>
       </c>
       <c r="K98" t="str">
         <v/>
@@ -3870,10 +3870,10 @@
         <v>11173</v>
       </c>
       <c r="I99" t="str">
-        <v>Build a mobile page where I can quickly look up all the common financial ratios like P/E ratio, debt-to-equity, current ratio, and stuff like that, and each one has a short plain-English explanation of what it actually means and whether a higher or lower number is better, because I'm always stuck trying to remember this during exams or when reading company reports and I don't want to google every single one separately — just let me tap a ratio name and see the formula plus a one-sentence takeaway, grouped roughly by category like profitability, liquidity, and leverage so I can find things fast.</v>
+        <v>Build a mobile app where I can quickly look up all the common financial ratios like P/E ratio, debt-to-equity, current ratio, and stuff like that, and each one has a short plain-English explanation of what it actually means and whether a higher or lower number is better, because I'm always stuck trying to remember this during exams or when reading company reports and I don't want to google every single one separately — just let me tap a ratio name and see the formula plus a one-sentence takeaway, grouped roughly by category like profitability, liquidity, and leverage so I can find things fast.</v>
       </c>
       <c r="J99" t="str">
-        <v>做一个手机页面，让我能快速查到所有常见的财务比率，比如市盈率、债务权益比、流动比率之类的，每个指标都配一段简单易懂的说明，讲清楚它到底是什么意思、数值越高还是越低越好，因为我每次考试或者看公司财报的时候总记不住这些，又不想一个个去谷歌搜——只要点一下指标名称，就能看到计算公式加一句话总结，然后按盈利能力、流动性、杠杆这几个大类分组归类，方便我快速找到想看的内容。</v>
+        <v>帮我做一个手机应用，可以快速查到各种常见的财务比率，比如市盈率、债务权益比、流动比率这些，每个比率下面都有一段简单易懂的解释，说清楚这个指标到底是什么意思、数值越高还是越低才算好，因为我每次考试或者看公司财报的时候总是记不住这些东西，又不想一个个去谷歌搜——就是让我点一下某个比率的名字，就能看到公式和一句话总结，然后按类别分好组，比如盈利能力、流动性、杠杆这几类，方便我快速找到想看的内容。</v>
       </c>
       <c r="K99" t="str">
         <v/>
@@ -3905,10 +3905,10 @@
         <v>14071</v>
       </c>
       <c r="I100" t="str">
-        <v>Create a mobile page where I can quickly look up how much of a common medicine to take — like ibuprofen, paracetamol, antihistamines, antacids, that kind of thing — because every time I need it I'm either sick or in a rush and I end up squinting at the tiny print on the box or falling down a rabbit hole of contradicting articles online. Just show me the drug name, standard adult dose, and how many times a day the max is, in a plain table I can scan in two seconds, and put a search box at the top so I can type the name and jump straight to it instead of scrolling through everything.</v>
+        <v>Create a mobile app where I can quickly look up how much of a common medicine to take — like ibuprofen, paracetamol, antihistamines, antacids, that kind of thing — because every time I need it I'm either sick or in a rush and I end up squinting at the tiny print on the box or falling down a rabbit hole of contradicting articles online. Just show me the drug name, standard adult dose, and how many times a day the max is, in a plain table I can scan in two seconds, and put a search box at the top so I can type the name and jump straight to it instead of scrolling through everything.</v>
       </c>
       <c r="J100" t="str">
-        <v>做一个手机页面，让我能快速查到常见药物的用量——比如布洛芬、对乙酰氨基酚、抗组胺药、抗酸药这类——因为每次需要查的时候不是正在生病就是赶时间，结果要么对着药盒上的小字眯眼看，要么在一堆互相矛盾的文章里越陷越深。页面只需要显示药品名称、成人标准剂量、每日最多服用次数，用一张简洁的表格呈现，让我两秒钟就能扫完。顶部放一个搜索框，这样我直接输入药名就能跳到对应条目，不用翻遍整个列表。</v>
+        <v>帮我做一个手机应用，能快速查到常见药物的用量，比如布洛芬、对乙酰氨基酚、抗组胺药、抗酸药这类——每次需要查的时候不是正在生病就是赶时间，结果只能眯着眼睛看药盒上的小字，要不就是在网上翻一堆互相矛盾的文章。界面就给我显示药品名称、成人标准剂量、每天最多服几次，用一个简单的表格呈现，两秒钟扫一眼就能看完。顶部放一个搜索框，输入药名直接跳到对应条目，不用一条条往下滑。</v>
       </c>
       <c r="K100" t="str">
         <v/>
@@ -3940,10 +3940,10 @@
         <v>9781</v>
       </c>
       <c r="I101" t="str">
-        <v>Build a mobile page where I can quickly look up cooking temperatures without having to Google it every single time I'm in the kitchen, like when I forget whether chicken needs to hit 165°F or what that is in Celsius, or what "medium heat" on a stove actually means in degrees — just show me a simple lookup thing organized by food type (meat, fish, baked stuff, etc.) with both Fahrenheit and Celsius side by side so I don't have to do the math myself.</v>
+        <v>Build a mobile app where I can quickly look up cooking temperatures without having to Google it every single time I'm in the kitchen, like when I forget whether chicken needs to hit 165°F or what that is in Celsius, or what "medium heat" on a stove actually means in degrees — just show me a simple lookup thing organized by food type (meat, fish, baked stuff, etc.) with both Fahrenheit and Celsius side by side so I don't have to do the math myself.</v>
       </c>
       <c r="J101" t="str">
-        <v>做一个手机页面，让我在厨房里能快速查烹饪温度，不用每次都跑去搜索——比如总是记不住鸡肉要达到华氏165度、换算成摄氏是多少，或者炉子上的"中火"到底对应多少度之类的问题。就做一个简单的查询工具，按食材类型分类（肉类、鱼类、烘焙类之类的），华氏度和摄氏度并排显示，这样我就不用自己去换算了。</v>
+        <v>做一个手机 app，让我在厨房做饭的时候能快速查到各种食材的烹饪温度，不用每次都去搜索——比如我老是忘记鸡肉要烤到几度才安全，或者 165°F 换成摄氏度是多少，再或者炉灶上说的"中火"到底对应几度。就做一个简单的查询页面，按食材类型分类（肉类、鱼类、烘焙类之类的），华氏度和摄氏度并排显示，这样我就不用自己换算了。</v>
       </c>
       <c r="K101" t="str">
         <v/>
@@ -3978,7 +3978,7 @@
         <v>Build a mobile to-do app where I can set tasks that repeat on flexible schedules — like every 3 days, every other Tuesday, or the last day of each month — because I'm tired of manually re-adding the same stuff over and over every week and always forgetting when it's due again, so I just need it to automatically pop the task back up on the right day, and I should be able to pick things like "repeat every X days" or "repeat on specific weekdays" when I'm creating the task, nothing complicated, just so I don't have to think about it.</v>
       </c>
       <c r="J102" t="str">
-        <v>帮我做一个手机端的待办事项应用，可以给任务设置灵活的重复周期——比如每隔3天、每隔一个周二、或者每个月的最后一天——因为我实在烦透了每周手动重新添加同样的任务，而且总是忘记下次该什么时候做，所以我就需要它能在正确的日期自动把任务重新弹出来，在创建任务的时候我应该能选择"每隔X天重复"或者"在指定的星期几重复"这类选项，不需要搞得多复杂，就是让我不用再费脑子去想这些事情。</v>
+        <v>做一个手机待办App，可以给任务设置灵活的重复周期，比如每隔3天、每隔一个周二、或者每个月的最后一天都能支持，因为我实在受不了每周手动重新添加同样的事情，而且老是忘记下次到期是哪天，所以就希望App能在对的那天自动把任务重新弹出来，创建任务的时候能选"每隔X天重复"或者"指定每周几重复"这类选项就行，不用搞得多复杂，就是让我不需要再费心记这些事。</v>
       </c>
       <c r="K102" t="str">
         <v/>
@@ -4010,10 +4010,10 @@
         <v>15824</v>
       </c>
       <c r="I103" t="str">
-        <v>Make a page in my task app where I can connect tasks to each other so it shows which ones are blocking other ones, and then highlight the most important chain — the one I absolutely cannot fall behind on if I want everything to finish on time — in a clear visual line so I can finally stop doing random tasks first and then realizing halfway through that I missed something critical that's holding up like five other things.</v>
+        <v>Make an app in my task app where I can connect tasks to each other so it shows which ones are blocking other ones, and then highlight the most important chain — the one I absolutely cannot fall behind on if I want everything to finish on time — in a clear visual line so I can finally stop doing random tasks first and then realizing halfway through that I missed something critical that's holding up like five other things.</v>
       </c>
       <c r="J103" t="str">
-        <v>在我的任务应用里做一个页面，可以把任务互相连接起来，显示哪些任务在卡着其他任务，然后把最关键的那条链路——就是想按时完成所有事情就绝对不能拖的那条——用一条清晰的视觉线高亮出来，这样我就不会再随手先做一堆任务，然后做到一半才发现漏掉了某个关键环节，结果一口气卡住了后面好几件事。</v>
+        <v>在我的任务应用里加一个功能，能把任务互相关联起来，看清哪些任务在卡着其他任务，然后把最关键的那条依赖链——就是如果想按时完成所有事情就绝对不能拖的那条——用一条醒目的视觉线标出来，这样我就不会再随便挑任务做，做到一半才发现漏掉了某个关键节点，结果一下子卡住后面好几件事。</v>
       </c>
       <c r="K103" t="str">
         <v/>
@@ -4045,10 +4045,10 @@
         <v>15322</v>
       </c>
       <c r="I104" t="str">
-        <v>Team task assignment page where each person on the team has a colored block showing how loaded they are this week — darker color means more tasks, lighter means they still have bandwidth — so when the manager needs to hand out new work they can actually see who's already buried instead of just guessing or asking everyone one by one. The blocks should be arranged by person in a simple grid and update the moment a task gets assigned to someone, so nobody ends up with five things due Friday while someone else is sitting there doing nothing.</v>
+        <v>Team task assignment app where each person on the team has a colored block showing how loaded they are this week — darker color means more tasks, lighter means they still have bandwidth — so when the manager needs to hand out new work they can actually see who's already buried instead of just guessing or asking everyone one by one. The blocks should be arranged by person in a simple grid and update the moment a task gets assigned to someone, so nobody ends up with five things due Friday while someone else is sitting there doing nothing.</v>
       </c>
       <c r="J104" t="str">
-        <v>团队任务分配页面，每个成员对应一个带颜色的色块，直观展示他这周的任务饱和度——颜色越深说明任务越多，颜色越浅说明还有余力承接新工作。这样管理者在分配任务时能一眼看出谁已经排得满满当当，不用靠猜或者挨个去问。色块按人员排列成简单的网格布局，只要有新任务分配给某人就立即刷新，避免出现有人周五要交五件事、另一个人却闲着没事干的情况。</v>
+        <v>做一个团队任务分配的应用，每个成员对应一个带颜色的色块，直观显示他这周的工作饱和度——颜色越深代表任务越多，颜色越浅代表还有余力——这样负责人在分派新工作的时候，一眼就能看出谁已经排得满满当当，不用靠猜或者挨个去问。所有人的色块按简单的网格布局排列，只要有任务分配出去就立刻更新，杜绝出现有人周五同时压着五件事要交、而另一个人却闲着没事干的情况。</v>
       </c>
       <c r="K104" t="str">
         <v/>
@@ -4080,10 +4080,10 @@
         <v>13155</v>
       </c>
       <c r="I105" t="str">
-        <v>Make a page where I can add tasks with a deadline and just tell it roughly how many hours of work it'll take, then it automatically shows me how many days are left and whether I'm actually on track or already screwed — like if I have 3 days left but estimated 10 hours of work, it should flag that as a problem, not just silently count down.</v>
+        <v>Make an app where I can add tasks with a deadline and just tell it roughly how many hours of work it'll take, then it automatically shows me how many days are left and whether I'm actually on track or already screwed — like if I have 3 days left but estimated 10 hours of work, it should flag that as a problem, not just silently count down.</v>
       </c>
       <c r="J105" t="str">
-        <v>做一个页面，能添加任务、设定截止日期，然后大概填一下这个任务需要几个小时完成，页面自动帮我算出还剩几天，并且告诉我到底是来得及还是已经凉了——比如还剩3天但估计要10小时的工作量，就应该直接标出来说有问题，而不是啥也不提示只是在那默默倒计时。</v>
+        <v>做一个可以添加任务的应用，每个任务能设截止日期，然后大概填一下预计要花多少小时，之后自动显示还剩几天，同时告诉我到底来不来得及——比如只剩3天但预估要花10小时，就应该直接报警提示有问题，而不是就这么默默倒计时假装没事。</v>
       </c>
       <c r="K105" t="str">
         <v/>
@@ -4115,10 +4115,10 @@
         <v>14936</v>
       </c>
       <c r="I106" t="str">
-        <v>90-minute deep work block timer screen where the countdown is front and center in huge numbers so I can glance at it without squinting — the whole point is I keep losing track of how long I've actually been focused versus just sitting there zoning out, so it needs to clearly show me when the 90 minutes starts, count all the way down without me having to touch it again, and then give me a loud alert when it's done. Also somewhere on the same screen I want to see how many full 90-minute blocks I've completed today, nothing fancy, just a small counter, so I can actually feel like I did something productive instead of wondering where my day went.</v>
+        <v>90-minute deep work block timer app where the countdown is front and center in huge numbers so I can glance at it without squinting — the whole point is I keep losing track of how long I've actually been focused versus just sitting there zoning out, so it needs to clearly show me when the 90 minutes starts, count all the way down without me having to touch it again, and then give me a loud alert when it's done. Also somewhere on the same app I want to see how many full 90-minute blocks I've completed today, nothing fancy, just a small counter, so I can actually feel like I did something productive instead of wondering where my day went.</v>
       </c>
       <c r="J106" t="str">
-        <v>做一个90分钟深度专注计时器界面，倒计时要用超大字体显示在屏幕正中央，瞄一眼就能看清，不用眯眼去找——我现在最大的问题就是根本搞不清自己到底专注了多久，还是只是坐在那发呆，所以必须能清楚地告诉我90分钟是从什么时候开始的，启动之后一路倒计时到零不需要我再碰它，时间到了给我一个响亮的提醒。另外同一个界面上还要显示我今天完整跑完了几个90分钟，不用多花哨，就一个小计数器就行，这样我能真实感受到今天做了点事情，而不是到晚上回头看完全不知道时间都去哪了。</v>
+        <v>一个90分钟深度专注计时器应用，倒计时数字要超大、放在最显眼的位置，抬眼就能看清，不用凑近眯眼看——我总是搞不清楚自己到底专注了多久还是只是发呆坐在那里，所以它必须能清楚地显示90分钟从什么时候开始倒计时，全程自动跑完不需要我再动它，时间到了给我一个响亮的提示音。另外在同一个页面里，我还想看到今天已经完成了几个完整的90分钟专注块，不用做得多复杂，就一个小计数器就行，这样我才能真实感受到自己做了些有意义的事，而不是一天过完了还不知道时间都去哪了。</v>
       </c>
       <c r="K106" t="str">
         <v/>
@@ -4153,7 +4153,7 @@
         <v>Build a mobile pomodoro timer app where me and my remote study partner can stay in sync without having to constantly message each other "okay starting now" — we both join the same session with a code or link, and the timer counts down together for both of us at the same time so when it hits break we both stop, no one is ahead or behind, and we can see a little indicator showing the other person is still in the session so I know they haven't quietly disappeared.</v>
       </c>
       <c r="J107" t="str">
-        <v>做一个手机版番茄钟应用，让我和异地一起自习的小伙伴能保持同步，不用每次都发消息说"好了我现在开始哦"——我们俩用一个邀请码或者链接加入同一个房间，倒计时对两个人同时进行，到休息的时候大家一起停，不会有人快有人慢，另外还能看到一个小状态指示器显示对方还在线，这样我就知道他没有悄悄跑路了。</v>
+        <v>做一个手机端的番茄钟应用，让我和异地的学习搭档可以同步计时，不用每次都发消息说"好了我现在开始"——我们通过一个邀请码或者链接加入同一个房间，两个人的倒计时同时跑，到了休息时间就一起停，不会有人快有人慢，另外还能看到一个小标识显示对方仍然在线，这样我就知道他没有悄悄溜走了。</v>
       </c>
       <c r="K107" t="str">
         <v/>
@@ -4188,7 +4188,7 @@
         <v>Build a focus timer app where whenever a random thought pops into my head mid-session — like remembering I need to reply to someone or something I want to look up — I can tap one button, quickly type it in, and immediately get back to my timer without losing my place, and all those little interruptions get saved to a simple list I can scroll through after the session is done so I actually deal with them instead of either forgetting or letting them break my concentration the whole time.</v>
       </c>
       <c r="J108" t="str">
-        <v>做一个专注计时器应用，在专注过程中，每当脑子里突然蹦出什么杂念——比如想起要回复某人的消息、或者有什么东西想搜一下——能点一个按钮，快速把它打下来，然后立刻回到计时器继续专注，不打断当前进度；所有这些临时冒出来的想法都自动保存到一个简单列表里，等专注结束后我可以滑动查看并逐一处理，这样既不会把它们忘掉，也不会让这些念头在整个专注期间一直分散我的注意力。</v>
+        <v>做一个专注计时器应用，在计时过程中如果脑子里突然冒出什么杂念——比如想起要回复某人、或者有什么东西想查——我可以点一个按钮，快速把它记下来，然后立刻回到计时界面继续专注，完全不影响进度。所有这些临时冒出的想法都自动存进一个简单的列表，等这一轮专注结束后我可以翻看并逐一处理，既不会忘掉，也不会让这些杂念在整个过程中一直干扰我的状态。</v>
       </c>
       <c r="K108" t="str">
         <v/>
@@ -4223,7 +4223,7 @@
         <v>Seven-day pomodoro count chart where each day of the current week shows how many focus sessions I actually finished, because I keep second-guessing myself whether I worked hard or just sat there zoning out — just a simple bar or dot for each day labeled Mon through Sun with the session numbers on them, nothing fancy at all, and it should flip to the new week automatically so I never have to touch a reset button or do any math myself.</v>
       </c>
       <c r="J109" t="str">
-        <v>做一个七天番茄钟统计图，显示本周每天实际完成了多少个专注时段，因为我老是不确定自己到底是真的在认真工作还是只是发呆坐在那里——每天就用一个简单的柱子或者圆点表示就行，从周一到周日依次排列，上面标出当天完成的次数，不需要任何花哨的东西，然后到了新的一周要能自动切换，我永远不用去按什么重置按钮或者自己算日期。</v>
+        <v>想做一个本周七天的番茄钟完成情况图，每天显示我实际完成了多少个专注时段，因为我总是搞不清楚自己到底是真的在认真工作，还是只是坐在那里发呆而已——每天对应一个简单的柱子或者圆点，从周一到周日依次排开，上面直接标出当天的次数就行，不需要任何花里胡哨的东西，另外到了新的一周要能自动切换过去，不用我手动点重置按钮或者自己去算日期。</v>
       </c>
       <c r="K109" t="str">
         <v/>
@@ -4255,10 +4255,10 @@
         <v>17133</v>
       </c>
       <c r="I110" t="str">
-        <v>Need a shared calendar app for me and my partner where we can both add events and see everything in one combined view, with each person's entries shown in a different color so it's instantly clear whose plans are whose, and I also want a simple way to set up repeating events like weekly grocery trips or monthly date nights so I don't have to add them one by one every time.</v>
+        <v>Need a shared calendar app for me and my partner where we can both add events and see everything in one combined app, with each person's entries shown in a different color so it's instantly clear whose plans are whose, and I also want a simple way to set up repeating events like weekly grocery trips or monthly date nights so I don't have to add them one by one every time.</v>
       </c>
       <c r="J110" t="str">
-        <v>想做一个我和伴侣共用的日历应用，两个人都能添加事项，所有内容汇总在同一个视图里显示，而且每个人的日程用不同颜色区分，一眼就能看出来是谁的安排。另外还想要一个简单的方式来设置重复事项，比如每周的采购或者每月的约会之夜，这样就不用每次都手动一条一条地添加了。</v>
+        <v>想做一个我和另一半共用的日历应用，两个人都能添加日程，所有内容汇总在同一个界面里，而且每个人的日程要用不同颜色区分，一眼就能看出哪条是谁的安排。另外还想要一个方便的方式来设置重复日程，比如每周的采购或者每月的约会之夜，这样就不用每次都手动一条条重新添加了。</v>
       </c>
       <c r="K110" t="str">
         <v/>
@@ -4290,10 +4290,10 @@
         <v>12174</v>
       </c>
       <c r="I111" t="str">
-        <v>Build a mobile page where I can see everyone on my team's free and busy times all stacked on top of each other so I can figure out when to schedule a meeting, I want each person to show as a colored bar across a daily time grid so it's easy to spot where everyone is free at the same time, and there should be a clear way to mark a time slot as the chosen meeting time once I find a gap that works for everyone.</v>
+        <v>Build a mobile app where I can see everyone on my team's free and busy times all stacked on top of each other so I can figure out when to schedule a meeting, I want each person to show as a colored bar across a daily time grid so it's easy to spot where everyone is free at the same time, and there should be a clear way to mark a time slot as the chosen meeting time once I find a gap that works for everyone.</v>
       </c>
       <c r="J111" t="str">
-        <v>做一个手机页面，把团队里所有人的空闲和忙碌时间叠加在一起展示，方便我判断什么时候适合开会。每个人用一条不同颜色的横条显示在按天划分的时间格上，这样一眼就能看出哪些时段大家都有空。找到合适的空档后，还要有一个清晰的操作方式，能把那个时间段标记为最终确定的会议时间。</v>
+        <v>做一个手机应用，把团队里所有人的空闲和忙碌时段叠加显示在一起，方便我判断什么时候适合安排会议，每个人用一条不同颜色的横条在每日时间表上表示，这样可以一眼看出大家同时有空的时段，另外一旦我找到一个对所有人都合适的空档，要有一个明确的操作可以把这个时间段标记为最终确定的会议时间。</v>
       </c>
       <c r="K111" t="str">
         <v/>
@@ -4325,10 +4325,10 @@
         <v>13418</v>
       </c>
       <c r="I112" t="str">
-        <v>Make a mobile page for tracking RSVPs to an event, where I can add each person's name and mark them as coming, not coming, or maybe, and at the top there's a clear count showing how many said yes, how many said no, and how many haven't decided yet, so I always know the totals without having to count manually — the list of names below should be easy to scroll through and each entry should show the person's name and their current answer side by side.</v>
+        <v>Make a mobile app for tracking RSVPs to an event, where I can add each person's name and mark them as coming, not coming, or maybe, and at the top there's a clear count showing how many said yes, how many said no, and how many haven't decided yet, so I always know the totals without having to count manually — the list of names below should be easy to scroll through and each entry should show the person's name and their current answer side by side.</v>
       </c>
       <c r="J112" t="str">
-        <v>做一个手机端的活动回执追踪页面，可以添加每个人的名字并标记他们的出席状态：参加、不参加或待定，页面顶部要有一个清晰的统计区域，分别显示确认参加的人数、不参加的人数以及还没决定的人数，这样不用手动数也能随时掌握总体情况——下方的名单列表要方便上下滚动，每一条记录左右并排显示当事人的名字和他们目前的回复状态。</v>
+        <v>做一个手机应用，用来追踪活动的出席回复，可以添加每个人的名字，并标记他们的状态为"出席"、"不出席"或"待定"，页面顶部有一个清晰的汇总数字，显示有多少人说来、多少人说不来、多少人还没决定，这样我随时都能看到总数，不用自己一个个去数——下方的名单列表要方便滑动浏览，每一条记录并排显示该联系人的姓名和当前回复状态。</v>
       </c>
       <c r="K112" t="str">
         <v/>
@@ -4360,10 +4360,10 @@
         <v>14393</v>
       </c>
       <c r="I113" t="str">
-        <v>Need a feature in my schedule app where every time I add a meeting to my calendar, a checklist automatically gets attached to that meeting — things like printing documents, confirming who's attending, booking the room — so I can check off each item one by one before the meeting happens. I want to be able to set my own default list of prep tasks that show up every time a meeting is added, and there should be a reminder the day before that nudges me to go through the list and make sure everything is ticked off.</v>
+        <v>Need a tool in my schedule app where every time I add a meeting to my calendar, a checklist automatically gets attached to that meeting — things like printing documents, confirming who's attending, booking the room — so I can check off each item one by one before the meeting happens. I want to be able to set my own default list of prep tasks that show up every time a meeting is added, and there should be a reminder the day before that nudges me to go through the list and make sure everything is ticked off.</v>
       </c>
       <c r="J113" t="str">
-        <v>我的日程应用里需要这样一个功能：每次往日历里添加会议的时候，系统自动给这个会议挂一个待办清单，比如打印材料、确认参会人员、预订会议室这类事项，让我可以在会议开始前逐一打勾完成。我希望能自己设置一套默认的会前准备任务，每次新增会议时自动带出来；另外还要有一个提醒，在会议前一天推送一下，提示我去过一遍清单、确认所有事项都已完成。</v>
+        <v>我的日程应用里需要一个功能：每次往日历里添加会议的时候，系统能自动给那场会议挂上一个准备清单——比如打印文件、确认参会人员、预订会议室这类事项——这样我就能在会议开始前逐项打勾确认。我希望能自己设定一套默认的准备任务，以后每次新增会议都自动带出这套清单。另外还需要有一个提醒，在会议前一天推送，提醒我去过一遍清单、确保每一项都已经完成。</v>
       </c>
       <c r="K113" t="str">
         <v/>
@@ -4395,10 +4395,10 @@
         <v>12511</v>
       </c>
       <c r="I114" t="str">
-        <v>Build a simple page where I can see at a glance how much stock is left for each item, and it automatically flags anything that's running low so I don't have to check everything one by one every morning — I keep forgetting to reorder stuff until it's completely gone and then my boss yells at me, so I just need a list that shows current quantity next to each product name, turns red or something when stock drops below a number I set, and maybe a separate section at the top that groups all the low-stock items together so I can deal with those first without scrolling through everything.</v>
+        <v>Build a simple app where I can see at a glance how much stock is left for each item, and it automatically flags anything that's running low so I don't have to check everything one by one every morning — I keep forgetting to reorder stuff until it's completely gone and then my boss yells at me, so I just need a list that shows current quantity next to each product name, turns red or something when stock drops below a number I set, and maybe a separate app at the top that groups all the low-stock items together so I can deal with those first without scrolling through everything.</v>
       </c>
       <c r="J114" t="str">
-        <v>做一个简单的页面，让我一眼就能看到每个商品还剩多少库存，而且能自动把快断货的东西标出来，这样我就不用每天早上一个个去检查了——我老是忘了补货，等到彻底卖完了才发现，然后被老板骂，所以我就需要一个列表，在每个商品名旁边显示当前数量，当库存低于我设定的数值时自动变红或者有什么提示，最好在页面顶部还有一个单独的区域，把所有库存不足的商品汇总在一起，这样我可以先处理这些，不用翻来翻去找。</v>
+        <v>做一个简单的应用，让我一眼就能看出每个商品还剩多少库存，然后自动把快断货的东西标出来，这样我就不用每天早上一个一个去查了——我老是忘记补货，等到东西完全卖光了才反应过来，然后就被老板骂，所以我就需要一个列表，每个商品名旁边直接显示当前库存数量，库存低于我自己设定的那个数之后就变红或者有个什么明显提示，然后最好在页面顶部再来一个单独的区域，把所有库存不足的商品都归到一起，这样我可以先集中处理这些，不用翻来翻去找。</v>
       </c>
       <c r="K114" t="str">
         <v/>
@@ -4430,10 +4430,10 @@
         <v>15600</v>
       </c>
       <c r="I115" t="str">
-        <v>Attendance and remaining leave summary page for employees — basically every time someone asks how many days off they have left I have to go dig through three different spreadsheets and it's killing me. Want a single page that lists each person with their current month check-in stats and their leftover annual leave, sick leave, and personal leave counts all shown together, so I can just tap someone's name and instantly see their breakdown without hunting anything down.</v>
+        <v>Attendance and remaining leave summary app for employees — basically every time someone asks how many days off they have left I have to go dig through three different spreadsheets and it's killing me. Want a single app that lists each person with their current month check-in stats and their leftover annual leave, sick leave, and personal leave counts all shown together, so I can just tap someone's name and instantly see their breakdown without hunting anything down.</v>
       </c>
       <c r="J115" t="str">
-        <v>想做一个员工考勤和剩余假期汇总页面——现在每次有人来问还剩多少假，我都要翻三张不同的表格，太崩溃了。想要一个页面把所有人列出来，直接显示他们当月的打卡情况，以及剩余年假、病假、事假的天数，全部放在一起，点一下某个人的名字就能马上看到他的详细明细，再也不用到处找了。</v>
+        <v>做一个员工考勤和剩余假期汇总的应用——现在每次有人来问还剩几天假，我都得翻三张不同的表格，太折磨人了。想要一个页面能把所有人列出来，同时显示他们本月的打卡情况，以及剩余年假、病假、事假的天数，点一下某个人的名字就能马上看到他的详细明细，再也不用到处找了。</v>
       </c>
       <c r="K115" t="str">
         <v/>
@@ -4465,10 +4465,10 @@
         <v>13788</v>
       </c>
       <c r="I116" t="str">
-        <v>Need a mobile page that shows me at a glance whether my project is on track or quietly falling apart, basically a simple chart that shows how much work is left versus how many days are left, so I can stop manually counting tasks in a spreadsheet every Monday morning and just open my phone to see if the team is behind schedule or not — it should also show a little status indicator somewhere that turns red when things are going badly so I don't have to stare at numbers to figure it out.</v>
+        <v>Need a mobile app that shows me at a glance whether my project is on track or quietly falling apart, basically a simple chart that shows how much work is left versus how many days are left, so I can stop manually counting tasks in a spreadsheet every Monday morning and just open my phone to see if the team is behind schedule or not — it should also show a little status indicator somewhere that turns red when things are going badly so I don't have to stare at numbers to figure it out.</v>
       </c>
       <c r="J116" t="str">
-        <v>需要一个移动端页面，让我一眼就能看出项目是在正常推进还是已经悄悄跑偏，核心就是一个简单的图表，能直观对比剩余工作量和剩余天数，这样我就不用每周一早上还要手动在表格里数任务了，直接掏出手机就知道团队有没有落后于计划——另外页面上最好有个小的状态指示器，一旦情况变差就自动变红，省得我还要盯着数字去判断到底出没出问题。</v>
+        <v>想做一个手机应用，让我一眼就能看出项目是在正常推进还是悄悄跑偏——核心就是一个简单的图表，显示剩余工作量和剩余天数的对比，这样我就不用每周一早上对着表格手动数任务了，直接打开手机就能知道团队有没有落后于计划。另外希望在某个地方加一个小的状态指示器，一旦进度变差就自动变红，省得我还要盯着一堆数字去判断情况到底好不好。</v>
       </c>
       <c r="K116" t="str">
         <v/>
@@ -4500,10 +4500,10 @@
         <v>17516</v>
       </c>
       <c r="I117" t="str">
-        <v>Need a simple phone page that shows my company's monthly profit and loss in one place — income up top, expenses below it, and the final number at the bottom so I can immediately tell if we made or lost money that month without digging through five different spreadsheets. Let me tap through different months to compare, and throw in a small bar chart or something showing the last six months side by side so I can see whether things are getting better or worse without doing the math myself.</v>
+        <v>Need a simple phone app that shows my company's monthly profit and loss in one place — income up top, expenses below it, and the final number at the bottom so I can immediately tell if we made or lost money that month without digging through five different spreadsheets. Let me tap through different months to compare, and throw in a small bar chart or something showing the last six months side by side so I can see whether things are getting better or worse without doing the math myself.</v>
       </c>
       <c r="J117" t="str">
-        <v>需要做一个简单的手机页面，把公司每个月的损益情况汇总在一起——收入放最上面，支出在它下面，最底部显示最终结余，这样我一眼就能看出这个月是赚了还是亏了，不用再翻来翻去查五六个不同的表格。要能点击切换不同月份方便对比，另外加一个小柱状图之类的，把最近六个月并排展示出来，让我直接看出趋势是在好转还是在变差，不用自己去算。</v>
+        <v>想做一个简单的手机应用，把公司每个月的损益情况都汇总在一个页面里——上面显示收入，下面列出支出，最底部直接给出当月盈亏结果，这样我一眼就能看出这个月是赚了还是亏了，不用再翻来覆去地对五六张表格。希望能点击切换不同月份方便对比，另外加一个小柱状图之类的，把最近六个月的数据并排展示出来，让我不用自己算也能直观看出趋势是在好转还是在变差。</v>
       </c>
       <c r="K117" t="str">
         <v/>
@@ -4538,7 +4538,7 @@
         <v>Need a research note experience that feels like a beautifully curated editorial spread — when I clip something from the web, I want it to show up as a clean little preview card with the site thumbnail, headline, and source name, almost like a magazine pull-quote sitting inside my notes rather than a raw ugly link. Citations should feel considered too, maybe displayed as a soft-styled callout with the author and publication subtly labeled, so the whole note looks intentional and polished instead of just a pile of copied text and URLs thrown together.</v>
       </c>
       <c r="J118" t="str">
-        <v>想做一个研究笔记的体验，整体感觉要像一份精心排版的杂志编辑页面——当我从网页剪藏内容时，希望它能以一张干净的小预览卡片的形式出现在笔记里，带有网站缩略图、标题和来源名称，就像杂志里的引言块嵌在笔记中，而不是一条光秃秃的丑链接。引用的处理也要有质感，比如用一个柔和风格的标注块来展示，低调地标注作者和出处，让整篇笔记看起来是经过用心设计的，而不是一堆复制来的文字和 URL 随便堆在一起。</v>
+        <v>想要一个像精心排版的杂志版面那样好看的研究笔记体验——当我从网页上剪藏内容时，希望它能以一张干净的小预览卡片的形式出现在笔记里，带着网站缩略图、标题和来源名称，就像杂志里的引用摘要嵌在笔记中一样，而不是一条难看的裸链接。引用的样式也要有质感，最好用一个柔和风格的标注块来呈现，把作者名和出版物名低调地标注出来，让整篇笔记看起来是经过用心设计的，而不是一堆复制来的文字和 URL 随意堆砌在一起。</v>
       </c>
       <c r="K118" t="str">
         <v/>
@@ -4570,10 +4570,10 @@
         <v>20478</v>
       </c>
       <c r="I119" t="str">
-        <v>Build a mobile document editing space where multiple people can write and edit together at the same time, and the whole experience feels warm and alive — like you can actually sense other people's presence on the page without it becoming noisy or overwhelming. I want each collaborator to have a soft, distinct color that quietly traces where they're writing, almost like watching ink bloom on paper in real time, with gentle little animations when new words appear so the document feels breathing and shared rather than cold and mechanical. The overall mood should feel closer to a beautifully kept shared journal than a corporate workspace — calm, paper-toned background, clean readable typography, and nothing that screams "office software.</v>
+        <v>Build a mobile document editing space where multiple people can write and edit together at the same time, and the whole experience feels warm and alive — like you can actually sense other people's presence on the app without it becoming noisy or overwhelming. I want each collaborator to have a soft, distinct color that quietly traces where they're writing, almost like watching ink bloom on paper in real time, with gentle little animations when new words appear so the document feels breathing and shared rather than cold and mechanical. The overall mood should feel closer to a beautifully kept shared journal than a corporate workspace — calm, paper-toned background, clean readable typography, and nothing that screams "office software.</v>
       </c>
       <c r="J119" t="str">
-        <v>做一个移动端的多人协同文档编辑空间，支持多个人同时写作和编辑，整体体验要温暖、有生命感——让人能真切感受到其他人也在页面上的存在，但又不会显得嘈杂或令人不安。我希望每位协作者都有一个柔和且各不相同的专属颜色，轻轻勾勒出他们正在书写的区域，就像看着墨水在纸上悄然晕开，新文字出现时配上细腻的小动画，让整个文档感觉像是在呼吸、被共同书写，而不是冰冷机械的工具。整体氛围要更接近一本用心维护的共享手记，而不是企业办公软件——背景用沉静的纸质色调，排版干净易读，不要有任何让人联想到"办公软件"的设计元素。</v>
+        <v>做一个移动端的多人实时协作文档编辑空间，支持多个人同时写作和编辑，整体体验要有温度、有生命感——让人在用的时候能感觉到其他人的存在，但又不会显得嘈杂或压迫。每位协作者都有一个柔和而各异的专属颜色，轻轻勾勒出他们正在书写的位置，就像看着墨水在纸上慢慢晕开，新文字出现时带着细腻的动画，让整个文档像在呼吸一样，有一种共同书写的温暖感，而不是冷冰冰的机械感。整体的氛围要更接近一本精心维护的共享手账，而不是企业办公软件——背景用沉静的纸色调，排版干净易读，没有任何让人联想到"办公室软件"的东西。</v>
       </c>
       <c r="K119" t="str">
         <v/>
@@ -4605,10 +4605,10 @@
         <v>11172</v>
       </c>
       <c r="I120" t="str">
-        <v>Create a note template gallery that feels like flipping through a beautifully curated magazine rack, where each template shows a rich little preview of what your note would actually look like — soft color palettes, clean typographic layouts, maybe a weekly planner feel or a mood-board style — and when you tap one you love, it just flows into your blank note instantly without any extra steps, keeping that same warmth and visual tone throughout the whole page.</v>
+        <v>Create a note template gallery that feels like flipping through a beautifully curated magazine rack, where each template shows a rich little preview of what your note would actually look like — soft color palettes, clean typographic layouts, maybe a weekly planner feel or a mood-board style — and when you tap one you love, it just flows into your blank note instantly without any extra steps, keeping that same warmth and visual tone throughout the whole app.</v>
       </c>
       <c r="J120" t="str">
-        <v>做一个笔记模板库，感觉就像在翻阅一排精心陈列的杂志，每个模板都配有丰富的小预览，直观呈现笔记实际写出来的样子——柔和的配色、干净的排版布局，可以是周计划风格，也可以是灵感拼板的感觉——点到喜欢的那款，内容直接流入空白笔记，不需要任何多余步骤，整个页面自始至终都保持那种温润统一的视觉氛围。</v>
+        <v>做一个笔记模板库，要有种在精心陈列的杂志架前随手翻阅的感觉，每个模板都呈现一小块真实效果预览——柔和的配色、干净的排版，也许是周计划本的质感，或者情绪板的风格——当你点到某个喜欢的模板时，内容直接无缝流入空白笔记，不需要任何多余步骤，整个应用自始至终都保持着那种温暖而统一的视觉调性。</v>
       </c>
       <c r="K120" t="str">
         <v/>
@@ -4640,10 +4640,10 @@
         <v>42202</v>
       </c>
       <c r="I121" t="str">
-        <v>Need a folder and notebook hierarchy organiser that feels like flipping through a beautifully curated shelf — each folder should have a distinct visual weight, maybe with soft color coding and subtle texture differences so you can instantly tell which level you're on without having to read anything, and when you drill down into nested notebooks the transition should feel like gently opening something rather than just jumping to a new screen, with the parent folder still visible as a soft backdrop so you never feel lost in the structure.</v>
+        <v>Need a folder and notebook hierarchy organiser that feels like flipping through a beautifully curated shelf — each folder should have a distinct visual weight, maybe with soft color coding and subtle texture differences so you can instantly tell which level you're on without having to read anything, and when you drill down into nested notebooks the transition should feel like gently opening something rather than just jumping to a new app, with the parent folder still visible as a soft backdrop so you never feel lost in the structure.</v>
       </c>
       <c r="J121" t="str">
-        <v>需要做一个文件夹与笔记本的层级管理器，整体感觉要像翻阅一个精心布置的书架——每个文件夹都应该有各自鲜明的视觉分量，通过柔和的色彩编码加上细微的质感差异来区分层级，让用户不用看任何文字就能立刻判断自己当前处于哪一层。向下钻入嵌套笔记本时，过渡动效要像是轻轻翻开某样东西，而不是生硬地跳转到新页面，上级文件夹始终以柔和的底层背景形式保持可见，让用户在整个层级结构中随时都有方向感，不会迷失。</v>
+        <v>想做一个文件夹和笔记本的层级管理界面，整体感觉要像在翻阅一个精心陈列的书架——每个文件夹都要有明显的视觉分量，通过柔和的色彩编码和细腻的纹理差异来区分层级，让用户不用刻意去读文字就能凭直觉判断自己身处哪一层；当深入展开嵌套笔记本时，过渡动效要像是轻轻揭开某样东西，而不是突兀地跳转到一个新界面，父文件夹应该以朦胧的背景形式留在画面里，让用户在整个层级结构中始终保有方位感，不会感到迷失。</v>
       </c>
       <c r="K121" t="str">
         <v/>
@@ -4678,7 +4678,7 @@
         <v>Build a hydration reminder app where I can set how often I want to be reminded to drink water — like every 30 minutes or every hour — and it sends me a push notification each time that interval is up. I want to be able to pick a start time and an end time for the reminders so it stops bugging me once I go to bed, and there should be a simple place to tap and log each glass I drink so I can see my total count for the day.</v>
       </c>
       <c r="J122" t="str">
-        <v>做一个喝水提醒应用，我可以自己设置提醒间隔，比如每30分钟或每小时提醒一次，时间到了就推送通知。我还想设置开始时间和结束时间，睡觉后就不再打扰我。另外需要有一个简单的按钮，每喝一杯水就点一下记录，这样能看到当天总共喝了多少杯。</v>
+        <v>做一个喝水提醒的app，可以自己设置提醒间隔，比如每30分钟或每小时提醒一次，时间一到就发推送通知。我想能设定提醒的开始时间和结束时间，这样睡觉之后就不会再打扰我了。另外要有个简单的按钮，每喝一杯水点一下就能记录，还能看到今天一共喝了几杯。</v>
       </c>
       <c r="K122" t="str">
         <v/>
@@ -4710,10 +4710,10 @@
         <v>13480</v>
       </c>
       <c r="I123" t="str">
-        <v>Need a feature in my medication reminder app where I can take a photo of a pill and it matches it against a reference to show me exactly what the pill is — I want it to clearly display the pill name, dosage, and purpose right after it identifies it, and I also need it to keep a small history log of pills I've already looked up so I can go back and check them later without having to re-photograph everything.</v>
+        <v>Need a tool in my medication reminder app where I can take a photo of a pill and it matches it against a reference to show me exactly what the pill is — I want it to clearly display the pill name, dosage, and purpose right after it identifies it, and I also need it to keep a small history log of pills I've already looked up so I can go back and check them later without having to re-photograph everything.</v>
       </c>
       <c r="J123" t="str">
-        <v>我想在我的用药提醒应用里加一个功能，可以直接拍一张药片的照片，然后让它跟数据库里的参考资料进行比对，识别出这颗药到底是什么——识别完成后要清楚地显示药品名称、剂量和用途。另外我还需要一个小的历史查询记录，把我之前查过的药片都保存下来，这样以后想回头查的时候不用重新拍照，直接看记录就行。</v>
+        <v>我在做一个用药提醒应用，需要加一个功能：用户可以直接拍一张药片的照片，系统自动和数据库比对，识别出这是什么药——识别完成后要清晰地展示药品名称、剂量和用途。另外还需要一个小的历史查询记录，把之前查过的药都保存下来，这样用户以后想复查的时候直接翻记录就行，不用再重新拍照。</v>
       </c>
       <c r="K123" t="str">
         <v/>
@@ -4745,10 +4745,10 @@
         <v>13701</v>
       </c>
       <c r="I124" t="str">
-        <v>Create a refill reminder screen for a medication tracking app where I can enter how many pills I currently have and how many I take each day, and it automatically calculates how many days of supply I have left, then reminds me a set number of days before I run out so I have enough time to go get a refill — I want to be able to choose how many days in advance the reminder fires (like 3 days or 7 days), and I'd also like a simple list showing all my medications with the days remaining clearly labeled next to each one.</v>
+        <v>Create a refill reminder app for a medication tracking app where I can enter how many pills I currently have and how many I take each day, and it automatically calculates how many days of supply I have left, then reminds me a set number of days before I run out so I have enough time to go get a refill — I want to be able to choose how many days in advance the reminder fires (like 3 days or 7 days), and I'd also like a simple list showing all my medications with the days remaining clearly labeled next to each one.</v>
       </c>
       <c r="J124" t="str">
-        <v>帮我做一个药物管理应用里的补货提醒页面，我可以输入当前手头还剩多少颗药、每天需要服用几颗，系统自动算出还能用几天，然后在快断药前提前几天发提醒，让我有足够时间去配药——我希望能自己设置提前多少天提醒（比如提前3天或7天），另外还想要一个简单的列表，把我所有的药物都列出来，每种药旁边清楚地标注剩余可用天数。</v>
+        <v>做一个用于药物管理应用的补药提醒功能，我可以输入当前手头有多少粒药、每天服用几粒，系统自动算出还剩多少天的用量，然后在快用完之前提前几天提醒我去补药——我希望能自己设定提前几天触发提醒，比如提前3天或者7天，另外还想要一个简单的药品列表，每种药旁边清楚地标出剩余天数。</v>
       </c>
       <c r="K124" t="str">
         <v/>
@@ -4780,10 +4780,10 @@
         <v>15685</v>
       </c>
       <c r="I125" t="str">
-        <v>Build a mobile page where I can log side effects and symptoms tied to whichever medication I just took, so each entry automatically gets connected to that specific medicine — I want to pick the medication name first, then write down things like headache, nausea, or dizziness along with a severity level (like mild, moderate, severe), and there should be a simple history list at the bottom where past entries are grouped by medicine name so I can easily look back and see if a certain drug keeps causing the same problem.</v>
+        <v>Build a mobile app where I can log side effects and symptoms tied to whichever medication I just took, so each entry automatically gets connected to that specific medicine — I want to pick the medication name first, then write down things like headache, nausea, or dizziness along with a severity level (like mild, moderate, severe), and there should be a simple history list at the bottom where past entries are grouped by medicine name so I can easily look back and see if a certain drug keeps causing the same problem.</v>
       </c>
       <c r="J125" t="str">
-        <v>做一个手机页面，让我可以记录刚刚服用的某种药物引发的副作用和不适症状，每条记录会自动关联到对应的那款药。我想先选择药品名称，然后填写具体症状，比如头痛、恶心或头晕，同时标注严重程度，比如轻度、中度、重度。页面底部要有一个简单的历史列表，按药品名称分组展示过去的记录，这样我可以方便地回顾某种药是不是一直在引发同样的问题。</v>
+        <v>做一个手机应用，让我可以记录每次服药后出现的副作用和症状，每条记录会自动关联到对应的药物——我想先选择药品名称，再填写头痛、恶心、头晕之类的症状，同时标注严重程度（比如轻度、中度、重度），页面下方要有一个简单的历史记录列表，按药品名称分组展示过去的记录，方便我回看某种药是不是一直在引发同样的问题。</v>
       </c>
       <c r="K125" t="str">
         <v/>
@@ -4818,7 +4818,7 @@
         <v>Build a yoga session flow and pose sequence tracker where I can write out all my poses in order before I start, then tap through them one by one during the session to mark each one done — I want to see the full list laid out so I always know what's coming next, and each pose should show the name and how long to hold it. I also need to be able to save a few different session lists, like a short morning one and a longer evening one, so I can just pick the right list and start without retyping everything each time.</v>
       </c>
       <c r="J126" t="str">
-        <v>帮我做一个瑜伽练习流程和体式序列追踪工具，我可以在开始之前把所有体式按顺序写好，然后在练习过程中一个一个点过去、标记完成——我希望能看到完整的列表，这样随时都知道下一个是什么，每个体式要显示名称和保持时长。另外我还需要能保存几套不同的序列，比如一套短一点的晨练方案和一套时间更长的晚练方案，这样直接选好对应的列表就能开始，不用每次重新输入。</v>
+        <v>做一个瑜伽课程流程和体式序列记录工具，让我可以在开始练习前把所有体式按顺序写好，然后在练习过程中逐个点击来标记每个体式已完成——我希望能看到完整的体式列表，这样随时都能知道下一个是什么，每个体式要显示名称和需要保持的时长。另外我还需要能保存几套不同的课程列表，比如一套短的晨练和一套长的晚练，这样每次直接选好对应的列表就能开始，不用重新把所有东西再输一遍。</v>
       </c>
       <c r="K126" t="str">
         <v/>
@@ -4850,10 +4850,10 @@
         <v>16184</v>
       </c>
       <c r="I127" t="str">
-        <v>A HIIT timer screen where the round counter is always clearly visible at the top — something like "Round 3 of 8" so I always know where I am in the workout. The big countdown clock in the middle should switch between work time and rest time and change color so I can tell at a glance which phase I'm in, and there should be a simple label underneath saying "Work" or "Rest" in plain text. The start, pause, and reset buttons need to be big enough to tap quickly without stopping to look carefully.</v>
+        <v>A HIIT timer app where the round counter is always clearly visible at the top — something like "Round 3 of 8" so I always know where I am in the workout. The big countdown clock in the middle should switch between work time and rest time and change color so I can tell at a glance which phase I'm in, and there should be a simple label underneath saying "Work" or "Rest" in plain text. The start, pause, and reset buttons need to be big enough to tap quickly without stopping to look carefully.</v>
       </c>
       <c r="J127" t="str">
-        <v>做一个HIIT计时器页面，顶部要始终清晰地显示当前轮次，比如"第3轮，共8轮"这样的格式，让我随时知道训练进行到哪里了。中间的大倒计时时钟要能在训练时间和休息时间之间切换，并且通过颜色变化让我一眼就能判断当前处于哪个阶段，时钟下方用简单的文字标注"训练"或"休息"。开始、暂停和重置按钮要足够大，方便我在运动中不用仔细看就能快速点到。</v>
+        <v>做一个HIIT计时器应用，顶部要始终清晰显示当前轮次，比如"第3轮 / 共8轮"这样的格式，让我随时知道训练进度。中间的大倒计时在工作时间和休息时间之间切换时要变换颜色，一眼就能分辨当前处于哪个阶段，下方用普通文字显示"训练"或"休息"的简单标签。开始、暂停和重置按钮要足够大，不用仔细看就能快速点到。</v>
       </c>
       <c r="K127" t="str">
         <v/>
@@ -4879,16 +4879,16 @@
         <v>medium</v>
       </c>
       <c r="G128">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H128">
         <v>17464</v>
       </c>
       <c r="I128" t="str">
-        <v>Create a gym check-in and personal record log page for a mobile app where I can tap a button to log that I went to the gym today, and below that I want to see a clear list of all my past visits showing the date and how long I worked out each time, plus a small section near the top that shows my total check-ins this month and my current streak so I can easily see how consistent I've been.</v>
+        <v>Create a gym check-in and personal record log app for a mobile app where I can tap a button to log that I went to the gym today, and below that I want to see a clear list of all my past visits showing the date and how long I worked out each time, plus an app near the top that shows my total check-ins this month and my current streak so I can easily see how consistent I've been.</v>
       </c>
       <c r="J128" t="str">
-        <v>帮我做一个健身房打卡和个人记录页面，用在手机 App 里。页面上要有一个按钮，点一下就能记录今天去健身房了；按钮下方要有一个清晰的历史打卡列表，每条记录显示日期和当次锻炼时长；页面顶部附近还要有一个小区域，展示我这个月的总打卡次数和当前连续打卡天数，让我一眼就能看出自己的坚持情况。</v>
+        <v>做一个手机端的健身打卡与个人记录应用，页面上要有一个按钮，点击后可以记录今天去健身房了，按钮下方展示一个清晰的历史打卡列表，显示每次的日期和锻炼时长，页面顶部附近还要有一个区域，显示我本月的累计打卡次数和当前连续打卡天数，让我能一眼看出自己的坚持情况。</v>
       </c>
       <c r="K128" t="str">
         <v/>
@@ -4920,10 +4920,10 @@
         <v>13143</v>
       </c>
       <c r="I129" t="str">
-        <v>Build a workout tracking app where I can plan out a progressive overload schedule for each exercise — things like increasing weight by a small amount or adding one more rep every week — and then see a clear side-by-side comparison between this week and last week so I can easily check if I'm actually moving forward. I want it to track at least the weight, sets, and reps for each exercise, and the week-over-week view should show a simple mark next to each item showing whether it went up, stayed the same, or dropped, so I don't have to figure it out myself.</v>
+        <v>Build a workout tracking app where I can plan out a progressive overload schedule for each exercise — things like increasing weight by a small amount or adding one more rep every week — and then see a clear side-by-side comparison between this week and last week so I can easily check if I'm actually moving forward. I want it to track at least the weight, sets, and reps for each exercise, and the week-over-week app should show a simple mark next to each item showing whether it went up, stayed the same, or dropped, so I don't have to figure it out myself.</v>
       </c>
       <c r="J129" t="str">
-        <v>做一个健身训练记录应用，让我能为每个动作规划渐进超负荷的训练计划——比如每周小幅增加重量，或者每周多加一个次数——同时能直观地并排对比本周和上周的数据，方便我确认自己是否真的在进步。每个动作至少要能记录重量、组数和次数，周环比视图要在每项数据旁边显示一个简单的标记，说明这项数据是上升了、持平还是下降了，这样我就不用自己去算了。</v>
+        <v>做一个健身训练记录应用，让我能够为每个动作制定渐进超负荷计划，比如每周小幅增加重量或者多加一个次数，然后用左右对比的方式直观展示本周和上周的数据，方便我确认自己是否真的在进步。每个动作至少要记录重量、组数和次数，周环比视图里每项数据旁边要有一个简单的标记，直接告诉我是涨了、没变还是降了，不用我自己去算。</v>
       </c>
       <c r="K129" t="str">
         <v/>
@@ -4955,10 +4955,10 @@
         <v>13470</v>
       </c>
       <c r="I130" t="str">
-        <v>Build a simple sleep recorder where I can tap in the time I fell asleep and the time I woke up each night, and it saves everything as a neat list I can scroll through to check past entries. Each row in the list should clearly show the date, the two times I entered, and the total hours slept so I don't have to do the math myself, and there should be a small weekly summary somewhere on the page that adds up my average sleep hours for the week.</v>
+        <v>Build a simple sleep recorder where I can tap in the time I fell asleep and the time I woke up each night, and it saves everything as a neat list I can scroll through to check past entries. Each row in the list should clearly show the date, the two times I entered, and the total hours slept so I don't have to do the math myself, and there should be a small weekly summary somewhere on the app that adds up my average sleep hours for the week.</v>
       </c>
       <c r="J130" t="str">
-        <v>做一个简单的睡眠记录工具，每晚可以手动输入入睡时间和起床时间，所有记录自动保存成一个列表，方便我上下滑动查看历史条目。列表里每一行要清楚显示日期、我填的两个时间，以及自动算好的总睡眠时长，不用我自己去算。另外页面上还要有一个小的周统计区域，显示我这一周的平均睡眠时长。</v>
+        <v>做一个简单的睡眠记录应用，我可以每晚手动输入入睡时间和起床时间，所有记录会保存成一个列表，方便我上下滑动查看历史条目。列表里的每一行都要清楚地显示日期、我输入的两个时间点，以及当晚的总睡眠时长，这样我就不用自己算了。另外页面上还要有一个小的每周汇总模块，统计出我这一周的平均睡眠时长。</v>
       </c>
       <c r="K130" t="str">
         <v/>
@@ -4990,10 +4990,10 @@
         <v>11945</v>
       </c>
       <c r="I131" t="str">
-        <v>Make a sleep quality score page that pulls data from my wearable device and shows the score clearly at the top, then breaks it down into a few separate items like deep sleep time, times I woke up, and how long it took me to fall asleep, so I can see exactly what went wrong each night instead of just one number.</v>
+        <v>Make a sleep quality score app that pulls data from my wearable device and shows the score clearly at the top, then breaks it down into a few separate items like deep sleep time, times I woke up, and how long it took me to fall asleep, so I can see exactly what went wrong each night instead of just one number.</v>
       </c>
       <c r="J131" t="str">
-        <v>做一个睡眠质量评分页面，从我的可穿戴设备同步数据，在顶部醒目地显示总评分，然后拆解成几个单独的指标，比如深度睡眠时长、夜间醒来次数、入睡花了多久，这样我每天晚上到底哪里没睡好，一眼就能看清楚，而不是只盯着一个分数猜。</v>
+        <v>做一个睡眠质量评分的应用，从我的可穿戴设备拉取数据，在页面顶部醒目地展示总评分，然后把评分拆解成几个独立的细项，比如深度睡眠时长、夜间醒来次数、入睡花了多久之类的，这样我每晚都能看清楚到底哪个环节出了问题，而不是只看一个笼统的分数。</v>
       </c>
       <c r="K131" t="str">
         <v/>
@@ -5025,10 +5025,10 @@
         <v>14765</v>
       </c>
       <c r="I132" t="str">
-        <v>Build a period tracking section in my health app that automatically notices when my cycle starts acting unusual and shows me a clear alert about it — specifically I want it to flag things like if my cycle suddenly gets much shorter or longer than my normal range, or if it keeps shifting by more than a few days each month. The alert should be a simple notice that tells me exactly what the irregularity is, not just a vague warning, and there should be a small list underneath showing the last three or four cycle lengths so I can see the pattern myself and compare.</v>
+        <v>Build a period tracking app in my health app that automatically notices when my cycle starts acting unusual and shows me a clear alert about it — specifically I want it to flag things like if my cycle suddenly gets much shorter or longer than my normal range, or if it keeps shifting by more than a few days each month. The alert should be a simple notice that tells me exactly what the irregularity is, not just a vague warning, and there should be a small list underneath showing the last three or four cycle lengths so I can see the pattern myself and compare.</v>
       </c>
       <c r="J132" t="str">
-        <v>在我的健康应用里做一个经期追踪模块，能自动识别周期出现异常的情况并给出清晰的提示——具体来说，如果我的周期突然比平时明显缩短或延长，或者每个月的经期开始时间持续偏移超过几天，就需要触发提醒。提示内容要直接说明是哪种异常，不能只是模糊地警告一下。提示下方还要有一个小列表，展示最近三四次的周期天数，让我能自己看出规律、进行对比。</v>
+        <v>在我的健康应用里做一个经期追踪功能，能自动识别周期出现异常的情况并给我发出明确提示——具体来说，如果我的周期突然比正常范围短很多或长很多，或者每个月的经期开始时间持续偏移超过几天，都需要标记出来。提示内容要直接说明是什么异常，不能只是一个含糊的警告，提示下方还要有一个小列表，显示最近三四次的周期天数，让我自己能看到规律、做对比。</v>
       </c>
       <c r="K132" t="str">
         <v/>
@@ -5063,7 +5063,7 @@
         <v>Make a pregnancy week-by-week milestone tracker that lists all 40 weeks in order, where each week shows a short note about what the baby is developing that week, and I can tap to mark a week as completed so I know where I am, with a simple bar at the top that fills up as the weeks go by to show how far along the pregnancy is overall.</v>
       </c>
       <c r="J133" t="str">
-        <v>做一个孕期逐周里程碑打卡追踪器，按顺序列出全部40周，每一周显示一段关于宝宝当周发育情况的简短说明，我可以点击某一周将其标记为已完成，方便随时知道自己目前进展到哪里，页面顶部有一个简单的进度条，随着完成的周数增加逐渐填满，直观呈现整个孕期的总体进度。</v>
+        <v>做一个孕期每周里程碑追踪器，按顺序列出全部40周，每一周显示一段关于宝宝当周发育情况的简短说明，我可以点击某一周来标记为已完成，方便知道自己目前处于哪个阶段，页面顶部有一个简单的进度条，随着周数推进逐渐填满，直观显示整个孕期的进度。</v>
       </c>
       <c r="K133" t="str">
         <v/>
@@ -5095,10 +5095,10 @@
         <v>11586</v>
       </c>
       <c r="I134" t="str">
-        <v>Create a weekly sleep quality trend chart for a health tracking app that shows each week's average sleep score as a line going up and down across the screen, so I can clearly see whether my sleep is getting better or worse over time, and I want each weekly point to show the exact score number right on it, plus a simple color difference between good weeks and bad weeks so I don't have to guess which ones were bad.</v>
+        <v>Create a weekly sleep quality trend chart for a health tracking app that shows each week's average sleep score as a line going up and down across the app, so I can clearly see whether my sleep is getting better or worse over time, and I want each weekly point to show the exact score number right on it, plus a simple color difference between good weeks and bad weeks so I don't have to guess which ones were bad.</v>
       </c>
       <c r="J134" t="str">
-        <v>帮我在健康追踪应用里做一个每周睡眠质量趋势图，用一条折线展示每周的平均睡眠评分，这样我能直观地看出睡眠质量是在变好还是变差。每个周的数据点上要直接显示具体分数，而且好的周和差的周要用不同颜色区分，不然我根本看不出哪几周睡得不好。</v>
+        <v>帮我在健康追踪应用里做一个每周睡眠质量趋势图，用一条折线展示每周平均睡眠评分的高低变化，让我能直观地看出自己的睡眠是在变好还是变差。每个周的数据点上要直接标出具体分数，另外睡眠好的周和差的周用不同颜色加以区分，这样我不用猜就能一眼看出哪几周睡眠质量不好。</v>
       </c>
       <c r="K134" t="str">
         <v/>
@@ -5130,10 +5130,10 @@
         <v>13332</v>
       </c>
       <c r="I135" t="str">
-        <v>Make a nutrition macro balance wheel for a health tracking app that shows how your daily calories are split between carbs, protein, and fat as a round chart, with each section clearly labeled with both the gram amount and the percentage so I can see right away which one is too high or too low, and use three noticeably different colors for the sections so they're easy to tell apart on a small phone screen without squinting.</v>
+        <v>Make a nutrition macro balance wheel for a health tracking app that shows how your daily calories are split between carbs, protein, and fat as a round chart, with each app clearly labeled with both the gram amount and the percentage so I can see right away which one is too high or too low, and use three noticeably different colors for the sections so they're easy to tell apart on a small phone app without squinting.</v>
       </c>
       <c r="J135" t="str">
-        <v>帮我做一个健康追踪应用里的营养素宏量比例环形图，用来展示每日卡路里在碳水、蛋白质和脂肪之间的分配情况，图表要是圆形的，每个区块都要清晰标注克数和百分比，让我一眼就能看出哪个摄入偏高或偏低，同时给三个区块分别用三种辨识度高的颜色，确保在手机小屏幕上不用眯眼也能轻松区分。</v>
+        <v>做一个健康追踪应用里的营养宏量平衡轮，用圆形图表展示每天摄入的卡路里是怎么在碳水、蛋白质和脂肪之间分配的，每个扇区都要同时标出克数和百分比，让我一眼就能看出哪个偏高或者偏低，三个区域分别用视觉差异明显的颜色区分，保证在手机小屏上也能直接看清，不用眯眼。</v>
       </c>
       <c r="K135" t="str">
         <v/>
@@ -5165,10 +5165,10 @@
         <v>19410</v>
       </c>
       <c r="I136" t="str">
-        <v>A chart that puts my daily water intake and my energy level side by side over time, so I can actually see whether drinking more water really does affect how I feel — both values plotted together on the same view with their own clearly labeled lines or bars, and I want to be able to switch between the last 7 days and the last 30 days, with water measured in glasses and energy shown as a simple 1-to-5 score I log myself each day.</v>
+        <v>A chart that puts my daily water intake and my energy level side by side over time, so I can actually see whether drinking more water really does affect how I feel — both values plotted together on the same app with their own clearly labeled lines or bars, and I want to be able to switch between the last 7 days and the last 30 days, with water measured in glasses and energy shown as a simple 1-to-5 score I log myself each day.</v>
       </c>
       <c r="J136" t="str">
-        <v>我想要一个图表，把我每天的饮水量和精力状态放在一起，按时间轴对比展示，这样我就能直观地看出多喝水到底有没有影响我的状态——两个数据显示在同一个视图里，各自有清晰标注的折线或柱状图。我还希望能切换近7天和近30天两个时间范围来查看，饮水量用"杯"作为单位，精力值是我每天自己记录的1到5分的简单评分。</v>
+        <v>做一个图表，把我每天的饮水量和精力状态并排放在同一条时间轴上，让我能直观看出多喝水到底有没有影响我的感受——两组数据显示在同一个图里，各自用清晰标注的折线或柱状图区分，同时支持切换"近7天"和"近30天"两个时间范围，饮水量以杯为单位，精力值是我每天自己记录的1到5分。</v>
       </c>
       <c r="K136" t="str">
         <v/>
@@ -5200,10 +5200,10 @@
         <v>13593</v>
       </c>
       <c r="I137" t="str">
-        <v>Make a screen in my health app that shows how my resting heart rate has changed over time, with a simple line chart that I can switch between views like the past week, past month, and past three months, and I want it to clearly show the highest and lowest points so I can tell at a glance whether things are getting better or worse.</v>
+        <v>Make an app in my health app that shows how my resting heart rate has changed over time, with a simple line chart that I can switch between views like the past week, past month, and past three months, and I want it to clearly show the highest and lowest points so I can tell at a glance whether things are getting better or worse.</v>
       </c>
       <c r="J137" t="str">
-        <v>帮我在健康应用里做一个页面，用来展示静息心率随时间的变化趋势，用一个简洁的折线图呈现，支持切换"近一周""近一个月""近三个月"这几个时间维度，同时要把最高值和最低值明显标注出来，让我一眼就能看出心率是在改善还是在恶化。</v>
+        <v>在我的健康应用里做一个页面，用来展示我的静息心率随时间的变化趋势，用一个简洁的折线图来呈现，可以在近一周、近一个月、近三个月这几个时间段之间切换，同时要把最高点和最低点标注清楚，让我一眼就能看出心率是在往好的方向走还是在变差。</v>
       </c>
       <c r="K137" t="str">
         <v/>
@@ -5235,10 +5235,10 @@
         <v>10819</v>
       </c>
       <c r="I138" t="str">
-        <v>Create a soft, immersive screen for a safe-place meditation that guides you through building your own mental sanctuary — like imagine slowly painting a peaceful scene in your mind, maybe a quiet forest or a warm sunlit room, and the app visually reflects that mood with gentle shifting colors and a slow dreamy blur effect in the background as the meditation narrates each detail of the space, so the whole thing feels like you're sinking into a painting rather than just listening to audio.</v>
+        <v>Create a soft, immersive app for a safe-place meditation that guides you through building your own mental sanctuary — like imagine slowly painting a peaceful scene in your mind, maybe a quiet forest or a warm sunlit room, and the app visually reflects that mood with gentle shifting colors and a slow dreamy blur effect in the background as the meditation narrates each detail of the space, so the whole thing feels like you're sinking into a painting rather than just listening to audio.</v>
       </c>
       <c r="J138" t="str">
-        <v>做一个柔和沉浸式的冥想页面，主题是"安全之所"，引导用户在脑海中一步步构建属于自己的心灵庇护所——就像在脑子里慢慢描绘一幅宁静的画面，可能是一片幽静的森林，也可能是一间阳光温柔洒落的小屋。随着冥想旁白逐步讲述这个空间里的每处细节，应用的背景色也跟着情绪缓缓流动变换，同时叠加一层慢速的梦幻虚化效果，整体体验不像是在听音频，而更像是整个人慢慢沉进了一幅画里。</v>
+        <v>做一个氛围柔和、沉浸感强的冥想应用，主题是引导用户在脑海中搭建属于自己的"心灵圣所"——就像慢慢在脑子里勾勒一幅宁静的画面，可以是幽静的森林，也可以是阳光暖洋洋的房间，应用界面要随着冥想的氛围同步变化，背景颜色缓缓流动切换，同时有一种慢速的梦幻模糊效果在底层晕开，配合旁白逐一描述空间里的每一处细节，整体体验要让人感觉是在慢慢沉进一幅画里，而不只是在听一段音频。</v>
       </c>
       <c r="K138" t="str">
         <v/>
@@ -5270,10 +5270,10 @@
         <v>14955</v>
       </c>
       <c r="I139" t="str">
-        <v>Need a progressive muscle relaxation guide that feels like leafing through a beautifully curated wellness editorial — each body area gets its own full-screen moment with soft, warm-toned visuals and gentle illustrative cues showing where to tense and release, giving the whole thing an unhurried, almost spa-like quality rather than anything clinical or chart-heavy, and as you move through the sequence the transitions should be slow and silky so the mood never breaks.</v>
+        <v>Need a progressive muscle relaxation guide that feels like leafing through a beautifully curated wellness editorial — each body area gets its own full-app moment with soft, warm-toned visuals and gentle illustrative cues showing where to tense and release, giving the whole thing an unhurried, almost spa-like quality rather than anything clinical or chart-heavy, and as you move through the sequence the transitions should be slow and silky so the mood never breaks.</v>
       </c>
       <c r="J139" t="str">
-        <v>想做一个渐进式肌肉放松引导页面，整体感觉要像在翻阅一本精心策划的高质感养生杂志——每个身体部位都独占一屏，搭配柔和暖调的视觉画面，用轻柔的插画示意标出需要收紧和放松的位置，整体氛围要慢下来、有点像水疗馆那种感觉，不要任何临床感或密密麻麻的图表；在依次浏览各个部位的过程中，页面切换要缓慢丝滑，始终保持那种沉浸放松的情绪不被打断。</v>
+        <v>想做一个渐进式肌肉放松引导应用，整体感觉要像翻阅一本精心编排的wellness生活杂志——每个身体部位都独占整个屏幕，搭配柔和暖调的视觉画面和轻柔的插画提示，直观地呈现哪里需要收紧、哪里需要放松，整体氛围要慢下来、有那种spa般的从容质感，绝对不能有任何临床感或密密麻麻的图表。在依次进行各个部位的过程中，页面切换要缓慢丝滑，始终不能打破那种放松的情绪。</v>
       </c>
       <c r="K139" t="str">
         <v/>
@@ -5305,10 +5305,10 @@
         <v>17743</v>
       </c>
       <c r="I140" t="str">
-        <v>Need a screen that guides you through box breathing to ease anxiety, with this really soft, almost meditative visual — like a glowing square shape that slowly expands as you inhale, holds steady, gently contracts as you exhale, then rests before the next round, all perfectly timed to that four-count rhythm — the whole thing should feel incredibly still and hushed, maybe deep navy or dusty sage tones with a barely-there pulse of warm light around the shape, and just the quietest label fading in to tell you which part of the breath you're on, no distractions, so the entire experience feels like the visual itself is breathing with you.</v>
+        <v>Need an app that guides you through box breathing to ease anxiety, with this really soft, almost meditative visual — like a glowing square shape that slowly expands as you inhale, holds steady, gently contracts as you exhale, then rests before the next round, all perfectly timed to that four-count rhythm — the whole thing should feel incredibly still and hushed, maybe deep navy or dusty sage tones with a barely-there pulse of warm light around the shape, and just the quietest label fading in to tell you which part of the breath you're on, no distractions, so the entire experience feels like the visual itself is breathing with you.</v>
       </c>
       <c r="J140" t="str">
-        <v>需要做一个引导用户进行「方块呼吸」练习的页面，用来缓解焦虑情绪，整体视觉风格要极度柔和、近乎冥想感——核心元素是一个发光的方形，吸气时缓缓向外扩展，屏息时静静悬停，呼气时轻柔地收缩回来，然后在下一轮开始前短暂停歇，全程精准契合四拍的节奏。整个画面应该给人一种极静、极轻的感受，配色可以用深海军蓝或者雾霾豆绿这类沉静的色调，方形周围有一圈若隐若现、温暖的光晕微微脉动，同时有一行极淡的文字轻轻淡入，提示当前处于哪个呼吸阶段，除此之外没有任何多余的元素，让整个体验感觉就像那个图形本身也在和你一起呼吸。</v>
+        <v>想做一个引导用户进行方块呼吸、帮助缓解焦虑的应用，视觉风格要非常柔和、接近冥想的感觉——核心是一个发光的方形，吸气时缓缓向外扩展，屏息时静静保持不动，呼气时轻柔地收缩回去，然后在下一轮开始前短暂停歇，整个过程严格遵循四拍节奏。整体氛围要极度宁静、近乎无声，配色可以考虑深海军蓝或带点灰调的鼠尾草绿，方形周围有若隐若现的温暖光晕轻轻律动，同时有极为克制的文字提示淡入淡出，告诉用户当前处于哪个呼吸阶段，没有任何多余的干扰元素，让人感觉整个画面本身就在跟着你一起呼吸。</v>
       </c>
       <c r="K140" t="str">
         <v/>
@@ -5340,10 +5340,10 @@
         <v>10999</v>
       </c>
       <c r="I141" t="str">
-        <v>Make a screen for a Wim Hof breathwork instructor session that feels raw and elemental — think icy blue tones fading into deep slate, like being half-submerged in cold water with light breaking through, not the usual soft wellness pastels. The instructor's face or silhouette should feel present and grounding, almost like you're in the room with them, and the breathing rhythm indicator should look more like a living pulse or wave than a mechanical timer, something you can feel rather than just read.</v>
+        <v>Make an app for a Wim Hof breathwork instructor session that feels raw and elemental — think icy blue tones fading into deep slate, like being half-submerged in cold water with light breaking through, not the usual soft wellness pastels. The instructor's face or silhouette should feel present and grounding, almost like you're in the room with them, and the breathing rhythm indicator should look more like a living pulse or wave than a mechanical timer, something you can feel rather than just read.</v>
       </c>
       <c r="J141" t="str">
-        <v>做一个维姆·霍夫呼吸法教练课程的界面，整体风格要原始、有力量感——配色用冰蓝色渐变到深石板灰，像半身浸在冷水里、光线从水面破入的那种感觉，不要那种常见的柔和wellness粉彩色调。教练的面部或剪影要有存在感和临场感，让人觉得像是真的跟教练处在同一个空间里；呼吸节奏指示器不要做成机械计时器的样子，要像有生命力的脉搏或波浪，是那种能让人感受到、而不只是用眼睛读数的东西。</v>
+        <v>做一个维姆·霍夫呼吸法教练课程的应用，整体风格要有原始、粗粝的质感——配色用冰蓝色慢慢渐变到深石板灰，像是半浸在冷水里、光线从水面折射进来的那种感觉，不要用那种千篇一律的柔和健康系马卡龙色。教练的面部或剪影要有真实的存在感和力量感，让人感觉好像真的和他们同处一室，呼吸节奏的指示也不要做成机械感的计时器，而是要像有生命的脉搏或波浪那样，是那种能让你感受到、而不只是盯着读数看的东西。</v>
       </c>
       <c r="K141" t="str">
         <v/>
@@ -5375,10 +5375,10 @@
         <v>16272</v>
       </c>
       <c r="I142" t="str">
-        <v>A section in the trip planner that keeps flights and hotels together on the same screen for each trip, where every entry has a direct link I can tap to go straight to the booking page — the two things I care most about are that the flight dates and hotel check-in/check-out dates line up side by side so I can immediately see if there's any gap or mismatch, and that each item shows a short status note like "confirmed" or "not booked yet" right next to its booking link.</v>
+        <v>A app in the trip planner that keeps flights and hotels together on the same app for each trip, where every entry has a direct link I can tap to go straight to the booking app — the two things I care most about are that the flight dates and hotel check-in/check-out dates line up side by side so I can immediately see if there's any gap or mismatch, and that each item shows a short status note like "confirmed" or "not booked yet" right next to its booking link.</v>
       </c>
       <c r="J142" t="str">
-        <v>行程规划里需要一个模块，把每次出行的机票和酒店信息集中放在同一个页面里，每条记录都带一个可以直接跳转到预订页面的链接。我最在意两点：一是航班日期和酒店入住、退房日期要并排显示，让我一眼就能看出有没有空档或者日期对不上的地方；二是每一项旁边要有一个简短的状态备注，比如"已确认"或者"尚未预订"，就贴在预订链接旁边。</v>
+        <v>做一个行程规划应用，能把每次出行的机票和酒店信息集中放在同一个页面里管理，每条记录都附有一个可以直接点击跳转到对应订票App的链接。我最在意两点：一是机票日期和酒店入住、退房日期要并排展示，让我一眼就能看出有没有时间空档或者日期对不上的情况；二是每条记录在订票链接旁边都要有一个简短的状态标注，比如"已确认"或者"尚未预订"。</v>
       </c>
       <c r="K142" t="str">
         <v/>
@@ -5410,10 +5410,10 @@
         <v>15468</v>
       </c>
       <c r="I143" t="str">
-        <v>Make a section in the trip planner where each leg of my itinerary has its own transport option listed — like subway, bus, taxi, or walking — so I can clearly see and pick how I'm getting from one place to the next for each part of the trip, and I want each leg to show the estimated travel time for whichever option I choose, so I can keep my whole day neatly accounted for.</v>
+        <v>Make an app in the trip planner where each leg of my itinerary has its own transport option listed — like subway, bus, taxi, or walking — so I can clearly see and pick how I'm getting from one place to the next for each part of the trip, and I want each leg to show the estimated travel time for whichever option I choose, so I can keep my whole day neatly accounted for.</v>
       </c>
       <c r="J143" t="str">
-        <v>在行程规划器里加一个板块，让行程里的每一段路都能单独选择出行方式——比如地铁、公交、出租车或者步行——这样我可以清楚地看到并选择每段怎么走，同时每段还要显示我所选出行方式对应的预计用时，方便我把一整天的时间安排得明明白白。</v>
+        <v>在行程规划应用里，给行程中的每一段路程都单独列出交通方式选项，比如地铁、公交、出租车或步行，让我能清楚地看到并选择从一个地点到下一个地点该怎么走，同时每段路程还要根据我选的交通方式显示预计所需时间，这样我就能把一整天的安排都规划得井井有条。</v>
       </c>
       <c r="K143" t="str">
         <v/>
@@ -5445,10 +5445,10 @@
         <v>15956</v>
       </c>
       <c r="I144" t="str">
-        <v>Make a page where I can browse and book activities and local experiences for my trip, and I want it organized so I can filter things by type — like outdoor, food, culture, and so on — because I hate scrolling through a big mixed pile of everything. Each activity should show the price, how long it takes, and whether spots are still open, and there should be a simple way to save the ones I like to a list so I can compare them before deciding which ones to actually book.</v>
+        <v>Make an app where I can browse and book activities and local experiences for my trip, and I want it organized so I can filter things by type — like outdoor, food, culture, and so on — because I hate scrolling through a big mixed pile of everything. Each activity should show the price, how long it takes, and whether spots are still open, and there should be a simple way to save the ones I like to a list so I can compare them before deciding which ones to actually book.</v>
       </c>
       <c r="J144" t="str">
-        <v>帮我做一个可以浏览和预订旅行活动及当地体验的页面，我希望能按类型筛选，比如户外、美食、文化之类的，因为我很不喜欢所有东西混在一起让我一直往下翻。每个活动要显示价格、所需时长，以及是否还有名额，另外要有一个简单的方式可以把感兴趣的活动收藏到一个清单里，这样我能货比三家，再决定到底订哪几个。</v>
+        <v>做一个可以浏览和预订旅行活动与本地体验的应用，我希望能按类型筛选，比如户外、美食、文化之类的，因为我很讨厌所有东西混在一起让我一直往下翻。每个活动要显示价格、所需时长以及是否还有名额，另外要有一个简单的方式把感兴趣的活动保存到收藏列表里，方便我货比三家再决定最终预订哪些。</v>
       </c>
       <c r="K144" t="str">
         <v/>
@@ -5480,10 +5480,10 @@
         <v>14793</v>
       </c>
       <c r="I145" t="str">
-        <v>Create a section in the packing list app where I can save my finished packing lists as templates to reuse for future trips, and each saved template should have a clear edit button so I can add or remove items without starting from scratch, plus a duplicate option so I can copy the whole thing when I want a similar list for a different trip without touching the original saved one.</v>
+        <v>Create an app in the packing list app where I can save my finished packing lists as templates to reuse for future trips, and each saved template should have a clear edit button so I can add or remove items without starting from scratch, plus a duplicate option so I can copy the whole thing when I want a similar list for a different trip without touching the original saved one.</v>
       </c>
       <c r="J145" t="str">
-        <v>在打包清单应用里加一个专区，让我可以把整理好的清单保存成模板，方便以后出行时复用。每个已保存的模板都要有一个明显的编辑按钮，这样我可以直接增删物品，不用从头重新建一份；另外还要有一个复制功能，当我下次要出行、需要一份类似的清单时，可以直接复制整个模板来用，同时不影响原来保存的那份。</v>
+        <v>在打包清单应用里加一个功能，让我可以把整理完的打包清单保存成模板，方便以后出行时直接复用。每个已保存的模板都要有一个清晰的编辑按钮，这样我可以直接在上面增减物品，不用从头重新填。另外还需要一个复制选项，当我想为另一次行程做一份类似的清单时，可以直接把整份模板复制一份来改，完全不影响原来保存好的那个。</v>
       </c>
       <c r="K145" t="str">
         <v/>
@@ -5518,7 +5518,7 @@
         <v>Need a travel prep app where I pick a destination country and it gives me a full checklist of all the documents and visa things I need — stuff like passport validity requirements, visa type, travel insurance, and any arrival forms I have to fill out. I want to be able to check things off one by one as I get them sorted, and there should be a clear way to see at a glance which items are still missing so I don't forget anything before I leave.</v>
       </c>
       <c r="J146" t="str">
-        <v>想做一个出行准备的应用，我可以选择目的地国家，然后它会自动生成一份完整的清单，列出我需要准备的所有证件和签证相关事项——比如护照有效期要求、签证类型、旅行保险，以及需要提前填写的入境表格之类的。我希望可以逐条打勾确认已经办好的项目，同时要有一个一目了然的方式来查看哪些东西还没搞定，这样出发前就不会漏掉任何东西。</v>
+        <v>想做一个出行准备的应用，可以选择目的地国家，然后自动生成一份完整的证件和签证清单——包括护照有效期要求、签证类型、旅行保险、以及需要提前填写的入境表格之类的内容。希望能逐项打勾确认进度，同时要有一个一目了然的方式看到哪些东西还没搞定，这样出发前就不会漏掉任何东西。</v>
       </c>
       <c r="K146" t="str">
         <v/>
@@ -5550,10 +5550,10 @@
         <v>14141</v>
       </c>
       <c r="I147" t="str">
-        <v>Build a travel medication and first-aid kit reminder page in a packing app where I can go through a list of common items like band-aids, fever reducer, antidiarrheal pills, and allergy medicine and check each one off as I pack it, and if I haven't checked everything off by the evening before my departure it should send me a reminder so I don't forget anything, and I also want to be able to add my own extra items to the list because everyone's situation is a little different.</v>
+        <v>Build a travel medication and first-aid kit reminder app in a packing app where I can go through a list of common items like band-aids, fever reducer, antidiarrheal pills, and allergy medicine and check each one off as I pack it, and if I haven't checked everything off by the evening before my departure it should send me a reminder so I don't forget anything, and I also want to be able to add my own extra items to the list because everyone's situation is a little different.</v>
       </c>
       <c r="J147" t="str">
-        <v>在打包行李的应用里做一个旅行药品和急救包提醒页面，里面列出常见的物品，比如创可贴、退烧药、止泻药、抗过敏药之类的，我可以一边打包一边逐项打勾，如果出发前一天晚上还有没勾完的，就自动发一条提醒，免得漏带东西，另外我还想能自己往清单里加额外的物品，因为每个人的情况不太一样。</v>
+        <v>帮我在一个行李打包应用里做一个旅行药品和急救包提醒功能，里面要有一份常用物品清单，像创可贴、退烧药、止泻药、抗过敏药这些，我可以一边打包一边逐项打勾确认，如果出发前一天晚上还有没勾完的东西，就自动给我发一条提醒，免得漏掉什么，另外我还希望能自己往清单里添加额外的物品，毕竟每个人的需求都不太一样。</v>
       </c>
       <c r="K147" t="str">
         <v/>
@@ -5585,10 +5585,10 @@
         <v>14191</v>
       </c>
       <c r="I148" t="str">
-        <v>Create a mobile page where I just type in my destination and it shows me the best route combining walking, metro, and bus all in one place — I'm so tired of switching between different apps to piece together my commute every morning, so just give me the full trip broken down step by step like "walk 8 minutes to the nearest stop, take Bus 302 for 5 stops, transfer to Metro Line 3, get off and walk 3 minutes" with the total travel time shown clearly at the top so I can tell at a glance whether I need to leave now or have a few more minutes.</v>
+        <v>Create a mobile app where I just type in my destination and it shows me the best route combining walking, metro, and bus all in one place — I'm so tired of switching between different apps to piece together my commute every morning, so just give me the full trip broken down step by step like "walk 8 minutes to the nearest stop, take Bus 302 for 5 stops, transfer to Metro Line 3, get off and walk 3 minutes" with the total travel time shown clearly at the top so I can tell at a glance whether I need to leave now or have a few more minutes.</v>
       </c>
       <c r="J148" t="str">
-        <v>做一个手机页面，我只需要输入目的地，它就能把步行、地铁、公交全部整合在一起，给我规划出最优路线——我真的受够了每天早上要在好几个App之间来回切换才能拼凑出一条通勤路线，所以希望直接把完整行程一步一步拆解清楚，比如"步行8分钟到最近的站台，乘坐302路公交坐5站，换乘地铁3号线，出站后步行3分钟"这种格式，同时在页面顶部醒目地显示总用时，让我一眼就能判断现在是该立刻出门还是还有几分钟可以缓一缓。</v>
+        <v>做一个手机应用，我只需要输入目的地，它就能把步行、地铁、公交全部整合在一起，给我规划出最优路线——我真的受够了每天早上在好几个App之间来回切换才能拼出一条通勤路线，所以直接给我一条完整的分步导航，就像"步行8分钟到最近的站点，乘坐302路公交车坐5站，换乘地铁3号线，下车后步行3分钟"这种格式，然后把总用时醒目地显示在最顶部，让我一眼就能判断现在是该立刻出门还是还有几分钟可以缓一缓。</v>
       </c>
       <c r="K148" t="str">
         <v/>
@@ -5620,10 +5620,10 @@
         <v>13491</v>
       </c>
       <c r="I149" t="str">
-        <v>Create a page where I can put in my start and end point for a road trip and it just shows me a scenic alternative route instead of the boring fastest highway one, because every time I drive somewhere I waste like 20 minutes on Google trying to find if there's a nicer road that goes through mountains or coastline or whatever — just show me the detour option right there with roughly how much extra time it adds, and maybe a few quick notes like "passes through X area" so I know if it's actually worth it before I commit.</v>
+        <v>Create an app where I can put in my start and end point for a road trip and it just shows me a scenic alternative route instead of the boring fastest highway one, because every time I drive somewhere I waste like 20 minutes on Google trying to find if there's a nicer road that goes through mountains or coastline or whatever — just show me the detour option right there with roughly how much extra time it adds, and maybe a few quick notes like "passes through X area" so I know if it's actually worth it before I commit.</v>
       </c>
       <c r="J149" t="str">
-        <v>做一个页面，让我能输入自驾游的出发地和目的地，然后直接给我推荐一条风景好的备选路线，而不是那种无聊的最快高速路——因为我每次开车出门都要在导航或者地图上折腾二十分钟，就为了找有没有更漂亮的路，比如穿山越岭或者沿海岸线走的那种。就直接把绕行方案显示出来，告诉我大概多花多少时间，再附几句简短说明，比如"途经某某地区"，让我在决定走不走之前就能判断值不值得绕。</v>
+        <v>做一个公路旅行路线规划的应用，我输入出发地和目的地之后，它直接给我推荐风景好的替代路线，而不是那种无聊的最快高速路方案——因为每次开车出行我都要在谷歌地图上浪费二十分钟，翻来覆去找有没有穿越山区或者沿海岸线走的更美的路。就直接把那条绕行路线给我显示出来，顺便告诉我大概多花多少时间，再加几句简短的提示，比如"途经某某地区"，让我在决定走不走之前就能判断这条路值不值得绕。</v>
       </c>
       <c r="K149" t="str">
         <v/>
@@ -5658,7 +5658,7 @@
         <v>Build a mobile navigation app where I can pick a city or region on the map, download it to my phone before I leave, and then get turn-by-turn directions without needing any internet connection at all — I'm always going to places with bad signal or I don't want to burn through my data plan, so the offline part has to actually work reliably, not just show a static map with no routing, and it should let me manage which areas I've downloaded so I can delete old ones when my phone storage gets full.</v>
       </c>
       <c r="J150" t="str">
-        <v>做一个手机导航应用，能在地图上选择某个城市或地区，出发前提前下载到手机里，之后在完全没有网络的情况下也能用逐向导航——我经常去信号差的地方，或者不想消耗流量，所以离线功能必须真的能用，不能只是展示一张静态地图却没法规划路线。另外还要能管理已下载的区域，手机存储快满的时候可以把旧的删掉腾出空间。</v>
+        <v>做一个手机导航应用，能让我在地图上选一个城市或地区，出发前把地图数据下载到手机里，之后在完全没有网络的情况下也能用逐步导航——我经常去信号差的地方，或者不想消耗流量，所以离线功能必须真的好用，不能只是显示一张静态地图却没法规划路线，另外还得能管理已下载的区域，手机存储不够的时候可以把旧的删掉。</v>
       </c>
       <c r="K150" t="str">
         <v/>
@@ -5690,10 +5690,10 @@
         <v>16968</v>
       </c>
       <c r="I151" t="str">
-        <v>Need a page that just tells me the current air quality number and right away tells me what I should actually do — like whether I should wear a mask outside or just stay in — because every time I look up the AQI I have no idea if 87 is bad or fine and I have to go search what it means anyway, so just show me a simple colored level with a plain one-line tip like "don't go for a run today" or "air is fine, windows open is okay," something I can glance at in two seconds before I head out.</v>
+        <v>Need an app that just tells me the current air quality number and right away tells me what I should actually do — like whether I should wear a mask outside or just stay in — because every time I look up the AQI I have no idea if 87 is bad or fine and I have to go search what it means anyway, so just show me a simple colored level with a plain one-line tip like "don't go for a run today" or "air is fine, windows open is okay," something I can glance at in two seconds before I head out.</v>
       </c>
       <c r="J151" t="str">
-        <v>想要一个页面，直接告诉我当前的空气质量数值，然后立刻告诉我该怎么做——比如出门要不要戴口罩、还是干脆别出去——因为每次查AQI我都搞不清楚87到底算差还是还好，还得再去搜一遍才明白，所以就给我显示一个带颜色的简单等级，再配一行大白话提示，像"今天别去跑步"或者"空气不错，开窗透气没问题"这种，让我出门前两秒钟扫一眼就够了。</v>
+        <v>想要一个能直接告诉我当前空气质量数值、然后马上告诉我该怎么做的应用——比如出门要不要戴口罩、还是干脆别出去——因为每次查AQI我都搞不清楚87到底是好是坏，还得再去搜一遍才知道什么意思，所以就给我显示一个带颜色的简单等级，再配一句大白话的提示，比如"今天别去跑步"或者"空气不错，开窗没问题"那种，出门前两秒钟扫一眼就能知道该怎么办。</v>
       </c>
       <c r="K151" t="str">
         <v/>
@@ -5725,10 +5725,10 @@
         <v>15213</v>
       </c>
       <c r="I152" t="str">
-        <v>Need a simple page that shows me the UV index for my current location throughout the day and just tells me straight up what time windows I should avoid being outside without sunscreen — like "11am to 2pm is bad, slap on SPF before you go out" kind of thing, not just a number I have to look up what it means myself. It should send me a reminder in the morning so I don't forget to check before I head out, and ideally mark the safe times versus the risky times in some easy way so I can plan when to grab lunch or run errands without getting fried.</v>
+        <v>Need a simple app that shows me the UV index for my current location throughout the day and just tells me straight up what time windows I should avoid being outside without sunscreen — like "11am to 2pm is bad, slap on SPF before you go out" kind of thing, not just a number I have to look up what it means myself. It should send me a reminder in the morning so I don't forget to check before I head out, and ideally mark the safe times versus the risky times in some easy way so I can plan when to grab lunch or run errands without getting fried.</v>
       </c>
       <c r="J152" t="str">
-        <v>想做一个简单的页面，能显示我当前位置全天的紫外线指数，而且要直接告诉我哪些时间段出门不抹防晒霜会有风险——就是那种"上午11点到下午2点紫外线很强，出门前记得涂防晒"的说法，而不是甩给我一个数字让我自己去查是什么意思。页面最好能在早上推送一条提醒，让我出门前不会忘记看一眼，同时用某种直观的方式把安全时段和高风险时段区分开来，这样我就能合理安排去外面吃午饭或者跑腿办事的时间，不至于被晒伤。</v>
+        <v>想做一个简单的应用，能显示我当前位置全天的紫外线指数，而且要直接告诉我哪些时间段不涂防晒不能出门——就是那种"上午11点到下午2点紫外线很强，出门前记得涂防晒霜"这样的提示，而不是甩给我一个数字让我自己去查什么意思。最好早上能推送一条提醒，让我出门前别忘了看一眼。还希望能用某种直观的方式把安全时段和危险时段标出来，方便我规划什么时候去吃午饭、跑腿办事，别把自己晒伤了。</v>
       </c>
       <c r="K152" t="str">
         <v/>
@@ -5760,10 +5760,10 @@
         <v>16008</v>
       </c>
       <c r="I153" t="str">
-        <v>Pollen count and allergy warning section on the main screen that just tells me straight up whether today is going to destroy my nose or not — I'm so tired of having to look this up separately every morning before leaving the house, so just show a simple level like low/medium/high with a short note on whether I should actually take my allergy pills, and then a 3-day outlook below so I know if I need to carry tissues the whole week or just today.</v>
+        <v>Pollen count and allergy warning app on the main app that just tells me straight up whether today is going to destroy my nose or not — I'm so tired of having to look this up separately every morning before leaving the house, so just show a simple level like low/medium/high with a short note on whether I should actually take my allergy pills, and then a 3-day outlook below so I know if I need to carry tissues the whole week or just today.</v>
       </c>
       <c r="J153" t="str">
-        <v>主界面上加一个花粉浓度和过敏预警的区块，直接告诉我今天出门鼻子会不会遭罪——我真的烦透了每天早上出门前还要专门去查这个，就显示个简单的等级，低/中/高，然后配一句简短的提示，说我今天到底需不需要提前吃抗过敏药，下面再加一个三天的花粉趋势预报，这样我就知道是只有今天需要带纸巾，还是整周都得备着。</v>
+        <v>在主应用里做一个花粉浓度和过敏预警的功能，直接告诉我今天会不会把我鼻子搞垮——我真的烦透了每天早上出门前还要单独去查这个，就显示一个简单的等级，比如低/中/高，再附一句要不要吃抗过敏药就行，然后下面放个三天的预报，让我知道是整周都得揣着纸巾还是只有今天需要。</v>
       </c>
       <c r="K153" t="str">
         <v/>
@@ -5795,10 +5795,10 @@
         <v>23916</v>
       </c>
       <c r="I154" t="str">
-        <v>Create a mobile page where I can just pick my starting dock and where I'm going and instantly see the ferry crossing times for today, because every single time I need to catch a boat I end up digging through some random government website or calling around, and half the time I still miss the last crossing — I just need to see the next few departure times at a glance and roughly how long each crossing takes, nothing fancy.</v>
+        <v>Create a mobile app where I can just pick my starting dock and where I'm going and instantly see the ferry crossing times for today, because every single time I need to catch a boat I end up digging through some random government website or calling around, and half the time I still miss the last crossing — I just need to see the next few departure times at a glance and roughly how long each crossing takes, nothing fancy.</v>
       </c>
       <c r="J154" t="str">
-        <v>做一个手机页面，让我能直接选出发码头和目的地，然后马上看到今天的轮渡班次，因为每次要赶船都得去翻什么政府网站或者到处打电话问，搞半天还是经常赶不上末班船——我就想一眼看到接下来几班的出发时间，以及每趟大概要多久，不需要别的花里胡哨的东西。</v>
+        <v>做一个手机App，让我能直接选出发码头和目的地，然后马上看到今天的轮渡班次时间——因为每次要赶船，我都得去翻某个政府网站或者到处打电话问，结果有一半时间还是错过了末班船。我就想一眼看到接下来几班的发船时间，以及大概需要多久能到对岸，不需要什么花里胡哨的功能。</v>
       </c>
       <c r="K154" t="str">
         <v/>
@@ -5830,10 +5830,10 @@
         <v>13762</v>
       </c>
       <c r="I155" t="str">
-        <v>Build a mobile page where I can look up the subway map and instantly see how much the fare is between any two stations, because I'm always guessing at the ticket machine and sometimes I don't have enough on my card which is super embarrassing — I just want to tap my starting station, tap where I'm going, and have it tell me the price right there on the map without me doing any math or digging through some website.</v>
+        <v>Build a mobile app where I can look up the subway map and instantly see how much the fare is between any two stations, because I'm always guessing at the ticket machine and sometimes I don't have enough on my card which is super embarrassing — I just want to tap my starting station, tap where I'm going, and have it tell me the price right there on the map without me doing any math or digging through some website.</v>
       </c>
       <c r="J155" t="str">
-        <v>帮我做一个手机页面，可以查地铁线路图，而且能直接看到任意两站之间的票价，因为我每次在自动售票机前都要瞎猜，有时候卡里余额不够，特别尴尬——我就想点一下出发站，再点一下目的地，票价直接显示在线路图上，不用自己算，也不用去翻什么网站。</v>
+        <v>帮我做一个手机应用，能查地铁线路图，而且可以直接看出任意两站之间的票价，因为我每次在自动售票机前都要瞎猜，有时候卡里余额不够特别尴尬——我就想点一下出发站、再点一下目的地，票价就直接显示在地图上，不用自己算也不用去翻什么网站。</v>
       </c>
       <c r="K155" t="str">
         <v/>
@@ -5865,10 +5865,10 @@
         <v>14517</v>
       </c>
       <c r="I156" t="str">
-        <v>A page for checking intercity coach schedules where you just type in where you're leaving from and where you're going, pick a date, and instantly see all the buses that day lined up by departure time with the price and remaining seats shown right there — no clicking into each one just to find out it's full or costs way more than expected, and there should be a quick way to book the one you want without jumping through a bunch of extra steps.</v>
+        <v>A app for checking intercity coach schedules where you just type in where you're leaving from and where you're going, pick a date, and instantly see all the buses that day lined up by departure time with the price and remaining seats shown right there — no clicking into each one just to find out it's full or costs way more than expected, and there should be a quick way to book the one you want without jumping through a bunch of extra steps.</v>
       </c>
       <c r="J156" t="str">
-        <v>做一个查询城际大巴班次的页面，输入出发地和目的地、选好日期，就能直接看到当天所有班次按发车时间排列，票价和剩余座位数直接显示在列表里——不用点进去才发现已经没票了或者价格贵得离谱，同时要有个简便的方式直接预订想要的那班车，别跳来跳去搞一堆多余的步骤。</v>
+        <v>做一个查城际大巴班次的应用，输入出发地和目的地、选好日期，就能直接看到当天所有班次按发车时间排好，票价和剩余座位数直接显示在列表里，不用一个个点进去才发现已经没座了或者价格贵得离谱，而且看到合适的班次要能直接订票，不要跳来跳去走一堆多余的步骤。</v>
       </c>
       <c r="K156" t="str">
         <v/>
@@ -5897,10 +5897,10 @@
         <v>12920</v>
       </c>
       <c r="I157" t="str">
-        <v>Make a mobile page for a little "what should I eat today" picker app where you can add a bunch of food places or dishes you like and then hit a big button to randomly land on one for you, something like a spinning wheel or just a fun reveal moment, and also let you tag each option with stuff like "cheap" or "spicy" or "near me" so you can filter before it picks, because I always waste like 20 minutes going back and forth with friends about where to eat and this would just settle it for us.</v>
+        <v>Make a mobile app for a little "what should I eat today" picker app where you can add a bunch of food places or dishes you like and then hit a big button to randomly land on one for you, something like a spinning wheel or just a fun reveal moment, and also let you tag each option with stuff like "cheap" or "spicy" or "near me" so you can filter before it picks, because I always waste like 20 minutes going back and forth with friends about where to eat and this would just settle it for us.</v>
       </c>
       <c r="J157" t="str">
-        <v>做一个移动端的"今天吃什么"随机选择小应用，可以把自己喜欢的餐厅或者菜品都加进去，然后点一个大按钮随机抽一个出来，最好有转盘或者什么有意思的揭晓动效，另外每个选项可以打标签，比如"便宜""辣""附近"这些，这样在随机之前可以先筛一下范围，因为每次跟朋友纠结去哪吃饭都要磨蹭二十分钟，有这个直接就能拍板了。</v>
+        <v>帮我做一个手机app，就是那种"今天吃什么"随机选择器，可以把自己喜欢的餐厅或者菜品都加进去，然后点一个大按钮随机抽一个，最好有转盘或者什么有意思的揭晓动效，另外每个选项可以打标签，比如"便宜""辣""附近"之类的，这样在随机之前可以先筛选一下，因为我每次跟朋友纠结吃什么都要磨叽二十多分钟，有这个app直接就能定下来了。</v>
       </c>
       <c r="K157" t="str">
         <v/>
@@ -5929,10 +5929,10 @@
         <v>16831</v>
       </c>
       <c r="I158" t="str">
-        <v>Make a little phone page for randomly picking what to eat today — there's a big round spin button in the middle you tap, and it cycles through a bunch of food options before landing on one like a wheel-of-fortune thing, and I want to be able to add my own restaurant names or dish types to the list myself beforehand so it only picks from places I actually feel like going to, not random stuff I don't care about.</v>
+        <v>Make a little phone app for randomly picking what to eat today — there's a big round spin button in the middle you tap, and it cycles through a bunch of food options before landing on one like a wheel-of-fortune thing, and I want to be able to add my own restaurant names or dish types to the list myself beforehand so it only picks from places I actually feel like going to, not random stuff I don't care about.</v>
       </c>
       <c r="J158" t="str">
-        <v>做一个手机端的今日吃什么随机选择页面——中间放一个大圆形按钮，点下去之后在一堆食物选项里快速滚动，最后像转盘抽奖一样定格在某一个上面。我还希望能提前自己往列表里加餐厅名称或者菜品类型，这样它只会从我真正想去的地方里面挑，不会冒出一些我完全不在乎的选项。</v>
+        <v>做一个手机小应用，用来随机决定今天吃什么——界面中间有一个大圆形按钮，点一下就会像转盘抽奖那样快速滚动浏览一堆食物选项，最后停在某一个上面。我还想事先自己往列表里加餐厅名字或者菜品类型，这样它只会从我真正想去的地方里挑，而不是随便给我推荐一些我根本不感兴趣的东西。</v>
       </c>
       <c r="K158" t="str">
         <v/>
@@ -5961,10 +5961,10 @@
         <v>15743</v>
       </c>
       <c r="I159" t="str">
-        <v>Random food spinner screen for those days when nobody can agree on where to eat — there's a big round button in the middle you tap, and it shuffles through a bunch of restaurant options kind of like a spinning wheel before landing on one, showing the place name, a little food photo, and the general vibe like "spicy noodles" or "hotpot." Want to be able to add your own spots to the list too, so it only picks from places you actually like and not random stuff you'd never go to.</v>
+        <v>Random food spinner app for those days when nobody can agree on where to eat — there's a big round button in the middle you tap, and it shuffles through a bunch of restaurant options kind of like a spinning wheel before landing on one, showing the place name, a little food photo, and the general vibe like "spicy noodles" or "hotpot." Want to be able to add your own spots to the list too, so it only picks from places you actually like and not random stuff you'd never go to.</v>
       </c>
       <c r="J159" t="str">
-        <v>做一个随机选餐的界面，专门用来解决大家纠结吃什么、谁都拍不了板的问题。界面正中间有个大圆形按钮，点一下就会像转盘一样快速滚动浏览一堆餐厅选项，最后停在某一家，显示出店名、一张小食物图和大概的风格标签，比如"麻辣面"或者"火锅"之类的。另外希望能自己往列表里添加常去的店，这样它只会从你真正喜欢的地方里随机挑，而不是乱推一些你压根不会去的地方。</v>
+        <v>今天不知道去哪吃饭？做个随机选餐的 app 解决选择困难症——中间放一个大圆按钮，点一下就开始像转盘一样快速切换各种餐厅选项，最后停在某一家，显示餐厅名字、一张小食物图片，还有大概的风格标签，比如"麻辣面条"或者"火锅"之类的。还想能自己往列表里加常去的店，这样转出来的都是自己真正喜欢的地方，不会随机蹦出些从来不会去的地方。</v>
       </c>
       <c r="K159" t="str">
         <v/>
@@ -5996,10 +5996,10 @@
         <v>16765</v>
       </c>
       <c r="I160" t="str">
-        <v>Need a simple phone page where I can set a daily calorie limit and then log whatever I eat throughout the day so I can instantly see how many calories I have left — I'm tired of doing the mental math every time I grab something to eat, I just want to tap in the food and a number, and the remaining budget updates right there on screen, and there should be a running list of everything I logged today so I can scroll back and see what I already ate without having to remember it all myself.</v>
+        <v>Need a simple phone app where I can set a daily calorie limit and then log whatever I eat throughout the day so I can instantly see how many calories I have left — I'm tired of doing the mental math every time I grab something to eat, I just want to tap in the food and a number, and the remaining budget updates right there on app, and there should be a running list of everything I logged today so I can scroll back and see what I already ate without having to remember it all myself.</v>
       </c>
       <c r="J160" t="str">
-        <v>想做一个简单的手机页面，可以设置每天的卡路里上限，然后随时记录吃了什么，这样就能立刻看到今天还剩多少热量额度——每次吃东西都要自己心算实在太烦了，我只想输入食物名称和卡路里数，剩余额度马上在页面上更新，另外还要有一个今日饮食的滚动列表，这样不用靠脑子记，往上翻一翻就能看到自己今天都吃了什么。</v>
+        <v>想做一个简单的手机应用，可以设定每天的卡路里上限，然后随时记录吃了什么东西，这样就能马上看到今天还剩多少卡路里可以吃——每次拿东西吃之前都要在脑子里算来算去实在太烦了，我就想点进去输个食物名称和数字，剩余额度立刻在页面上更新，另外还要有一个今天已记录的清单，可以往下滑查看自己都吃了什么，不用靠自己一条条回忆。</v>
       </c>
       <c r="K160" t="str">
         <v/>
@@ -6031,10 +6031,10 @@
         <v>13647</v>
       </c>
       <c r="I161" t="str">
-        <v>Make a page where I can search any food and instantly see how much protein, carbs, and fat it has per 100g, because I'm always standing in a convenience store or at some restaurant trying to figure out if I should eat something and I end up just googling forever and giving up. Just show the three numbers big and clear, and put a simple little bar next to each one so I can tell at a glance which macro is the biggest without having to do any math myself.</v>
+        <v>Make an app where I can search any food and instantly see how much protein, carbs, and fat it has per 100g, because I'm always standing in a convenience store or at some restaurant trying to figure out if I should eat something and I end up just googling forever and giving up. Just show the three numbers big and clear, and put a simple little bar next to each one so I can tell at a glance which macro is the biggest without having to do any math myself.</v>
       </c>
       <c r="J161" t="str">
-        <v>做一个页面，可以搜索任意食物，立刻显示每100克含多少蛋白质、碳水和脂肪——因为我经常站在便利店或餐厅里，想搞清楚这东西能不能吃，结果一直在手机上刷来刷去最后直接放弃。就把这三个数字显示得大大的、清清楚楚的，每个数字旁边配一条简单的小进度条，让我一眼就能看出哪个营养素占比最高，完全不用自己算。</v>
+        <v>做一个能搜索任意食物、立刻显示每100克含多少蛋白质、碳水化合物和脂肪的应用。因为我经常站在便利店或者餐厅里，想搞清楚某样东西到底能不能吃，结果在网上翻来翻去半天什么都没查到，最后直接放弃了。就把这三个数字显示得大大的、清清楚楚的，然后在每个数字旁边放一根简单的小进度条，让我一眼就能看出哪种宏量营养素占比最多，不用自己动脑子算。</v>
       </c>
       <c r="K161" t="str">
         <v/>
@@ -6066,10 +6066,10 @@
         <v>15707</v>
       </c>
       <c r="I162" t="str">
-        <v>Need a page in my food tracking app where I can quickly figure out which vitamins or minerals I'm probably low on based on what I've been eating — I keep feeling sluggish and have no idea if it's iron, B12, vitamin D, or whatever, and I don't want to go Google every symptom one by one. I just want to pick or log a few recent meals and have it show me a short list of nutrients I'm likely missing, with a simple note next to each one like "you haven't eaten enough of X, try eating Y or Z" so I can actually do something about it without thinking too hard.</v>
+        <v>Need an app in my food tracking app where I can quickly figure out which vitamins or minerals I'm probably low on based on what I've been eating — I keep feeling sluggish and have no idea if it's iron, B12, vitamin D, or whatever, and I don't want to go Google every symptom one by one. I just want to pick or log a few recent meals and have it show me a short list of nutrients I'm likely missing, with a simple note next to each one like "you haven't eaten enough of X, try eating Y or Z" so I can actually do something about it without thinking too hard.</v>
       </c>
       <c r="J162" t="str">
-        <v>我的饮食记录应用里需要一个页面，让我能快速看出自己最近吃的东西里可能缺了哪些维生素或矿物质——我总是感觉无精打采，但根本不知道是缺铁、缺B12、缺维生素D还是别的什么，也不想一个一个症状去谷歌查。我只想选几顿或记录几顿最近吃的饭，然后页面直接给我列出我可能摄入不足的营养素，每条旁边附一句简单的提示，比如"你最近X吃得不够，可以试试吃Y或Z"，这样我不用费太多脑子就能直接照着做。</v>
+        <v>想在我的饮食记录应用里加一个功能，能根据我最近吃的东西快速判断我可能缺哪些维生素或矿物质——我最近老是感觉没精神，但不知道是缺铁、缺B12、缺维生素D还是别的什么，也不想一个一个症状去谷歌查。我只想选几顿最近吃过的饭或者随手记录一下，然后让它给我列出一个简短的可能缺乏的营养素清单，每条旁边附一句简单的提示，比如"你最近X吃得不够，可以试试吃Y或者Z"，这样我不用费太多脑子就能知道该怎么调整饮食。</v>
       </c>
       <c r="K162" t="str">
         <v/>
@@ -6104,7 +6104,7 @@
         <v>Need a recipe creator where I can pick two different food cultures — say, Japanese and Mexican, or Indian and Italian — and it combines them into one fusion recipe with a clear step-by-step cooking list and a separate ingredients checklist I can go through one by one, and I want it to show which flavors or techniques come from which culture so I actually understand why the combination works, not just a random mashup.</v>
       </c>
       <c r="J163" t="str">
-        <v>想做一个融合菜谱生成器，可以让我选两种不同的饮食文化——比如日式和墨西哥，或者印度和意大利——然后把它们合并成一道完整的融合菜谱，要有清晰的分步烹饪流程，还要有一个可以逐条勾选的食材清单。另外我希望它能标注出每种风味或烹饪技法分别来自哪个文化，让我真正明白这个组合为什么合理，而不是感觉只是随便拼凑在一起的。</v>
+        <v>想做一个融合菜谱生成器，可以选择两种不同的饮食文化——比如日式和墨西哥，或者印度和意大利——然后把它们合并成一道融合菜，要有清晰的分步烹饪流程，还有一个可以逐条勾选的食材清单，同时我希望它能标注出每种口味或烹饪技巧分别来自哪个文化，让我真正理解这个搭配为什么合理，而不只是随便乱拼一通。</v>
       </c>
       <c r="K163" t="str">
         <v/>
@@ -6136,10 +6136,10 @@
         <v>13374</v>
       </c>
       <c r="I164" t="str">
-        <v>A recipe filter and suggestion screen where I can check off my dietary restrictions from a clear list — things like gluten-free, dairy-free, nut allergy, low-sodium, vegetarian — and then only see recipes that match everything I checked. Each suggested recipe should show a short list of key ingredients right on the preview so I don't have to open it just to find out if something conflicts with my restrictions, and there should be a way to save the filter settings I use most often so I don't have to re-check everything each time.</v>
+        <v>A recipe filter and suggestion app where I can check off my dietary restrictions from a clear list — things like gluten-free, dairy-free, nut allergy, low-sodium, vegetarian — and then only see recipes that match everything I checked. Each suggested recipe should show a short list of key ingredients right on the preview so I don't have to open it just to find out if something conflicts with my restrictions, and there should be a way to save the filter settings I use most often so I don't have to re-check everything each time.</v>
       </c>
       <c r="J164" t="str">
-        <v>一个食谱筛选与推荐页面，我可以在一个清晰的列表里勾选我的饮食限制，比如无麸质、不含乳制品、坚果过敏、低钠、素食等，然后页面只显示符合我所有勾选条件的食谱。每张食谱预览卡上要直接展示几个关键食材，这样我不用点进去就能判断有没有和我的忌口冲突的东西。另外还需要有个保存常用筛选方案的功能，这样下次不用重新一个个勾选。</v>
+        <v>做一个食谱筛选和推荐的应用，我可以在一个清晰的列表里勾选我的饮食限制，比如无麸质、无乳制品、坚果过敏、低钠、素食之类的，然后只显示满足我所有勾选条件的食谱。每个推荐食谱在预览卡片上就要直接列出几个主要食材，这样我不用点进去就能知道有没有跟我的忌口冲突的东西，另外还需要有一个功能可以保存我常用的筛选组合，不用每次都重新勾一遍。</v>
       </c>
       <c r="K164" t="str">
         <v/>
@@ -6171,10 +6171,10 @@
         <v>10019</v>
       </c>
       <c r="I165" t="str">
-        <v>Need a cooking screen that shows each step one at a time with a built-in countdown timer for that step, so I can just follow along without losing my place — I want to see the current step clearly, tap to start the timer, and have it automatically move to the next step when time is up, with the total number of steps shown somewhere so I always know how far along I am.</v>
+        <v>Need a cooking app that shows each step one at a time with a built-in countdown timer for that step, so I can just follow along without losing my place — I want to see the current step clearly, tap to start the timer, and have it automatically move to the next step when time is up, with the total number of steps shown somewhere so I always know how far along I am.</v>
       </c>
       <c r="J165" t="str">
-        <v>想做一个烹饪步骤页面，每次只显示一个步骤，并且每个步骤都带有内置的倒计时器，这样我可以边做边看、不容易跟丢进度——我希望当前步骤显示得清清楚楚，点一下就能启动计时，时间到了自动跳到下一步，同时页面上要有总步骤数，让我随时知道现在做到第几步了。</v>
+        <v>想做一个烹饪应用，每次只显示一个步骤，并且每个步骤都有内置的倒计时器，这样做菜的时候就不会搞混进度——我希望当前步骤能清晰呈现，点一下就能启动计时，时间到了自动跳到下一步，同时在某个地方显示总步骤数，让我随时知道做到哪一步了。</v>
       </c>
       <c r="K165" t="str">
         <v/>
@@ -6206,10 +6206,10 @@
         <v>20710</v>
       </c>
       <c r="I166" t="str">
-        <v>The wait time and reservation availability section on a restaurant detail page needs to feel like it belongs in a curated food editorial, not a hospital queue board — right now that kind of info always looks so sterile and forgettable. I want the current wait estimate displayed in a way that feels warm and a little artisanal, maybe in a rounded, slightly handwritten-style number against a soft cream or warm amber background, so it reads as "worth the wait" rather than stressful. The available booking time slots should sit below it in a gentle, evenly-spaced row where open slots glow with a subtle warm highlight and taken ones just quietly dim out, so the whole thing feels like a calm, tasteful moment instead of a frantic grab for seats.</v>
+        <v>The wait time and reservation availability app on a restaurant detail app needs to feel like it belongs in a curated food editorial, not a hospital queue board — right now that kind of info always looks so sterile and forgettable. I want the current wait estimate displayed in a way that feels warm and a little artisanal, maybe in a rounded, slightly handwritten-style number against a soft cream or warm amber background, so it reads as "worth the wait" rather than stressful. The available booking time slots should sit below it in a gentle, evenly-spaced row where open slots glow with a subtle warm highlight and taken ones just quietly dim out, so the whole thing feels like a calm, tasteful moment instead of a frantic grab for seats.</v>
       </c>
       <c r="J166" t="str">
-        <v>餐厅详情页上的等位时间和预订可用性模块，现在看起来太冷冰冰了，完全像医院叫号屏，毫无温度可言。我希望这块内容能有精品美食杂志的那种感觉。当前等待时长的数字，希望用一种圆润、略带手写感的字体来呈现，搭配奶油白或暖琥珀色的背景，让人第一眼就觉得"等这一下完全值"，而不是焦虑催促的感觉。下方的可预订时间段排成一排，间距均匀、节奏舒缓，空闲的时间格带一点微微发光的暖色高亮，已被占用的就静静地暗下去，整体氛围平和、有品质，不要那种哄抢座位的紧张感。</v>
+        <v>餐厅详情页里的等位时间和预订可用性模块，现在看起来太死板了，像医院叫号系统一样毫无温度、让人印象全无——我希望它能融入那种精心策划的美食杂志风格。当前等位时长的展示方式要有温暖感和一点手工质感，比如用圆润、略带手写风格的字体来呈现数字，搭配柔和的奶油色或暖琥珀色背景，让人感觉"等得值"，而不是焦虑催促。可预订的时间段放在下方，以舒缓、均匀间距排成一行：有空位的时段用微妙的暖色高亮轻轻发光，已满的时段则低调地淡化变暗——整体氛围要像一个从容、有品位的瞬间，而不是疯抢座位的紧张感。</v>
       </c>
       <c r="K166" t="str">
         <v/>
@@ -6244,7 +6244,7 @@
         <v>A quiet little corner of the app dedicated to surfacing restaurants that haven't been overrun yet — the kind of places that feel like a personal find, not something already plastered across every foodie account. The whole mood should feel editorial and understated, like a hand-curated zine rather than an algorithm dump, maybe with muted warm tones and just enough whitespace to make each recommendation feel considered. Each spot should show something that communicates its low-traffic nature in a charming way — like "only 12 people have been here this month" — so it feels exclusive and intimate rather than abandoned. Want it to have a slow, unhurried scroll pace visually, where the photos feel film-like and honest rather than oversaturated and staged.</v>
       </c>
       <c r="J167" t="str">
-        <v>想在应用里开辟一个安静的小角落，专门用来推荐那些还没被人潮淹没的餐厅——那种感觉像是自己悄悄挖到的宝藏，而不是已经被每个美食号刷烂了的网红店。整体基调要偏编辑风、克制低调，像一本手工精选的独立小志，而不是算法批量倒出来的推荐列表，可以用低饱和的暖色调，留白要足够，让每一条推荐都显得经过认真思量。每个地方最好有个能体现其小众属性的细节，比如"本月只有12人来过"这样的文案，让人感觉这里独家、私密，而不是无人问津的冷清角落。视觉上想要一种慢悠悠、不急不躁的滚动节奏，照片要有胶片质感、真实自然，不要那种色彩过度鲜艳、摆拍痕迹很重的风格。</v>
+        <v>应用里有一个安静的小角落，专门用来推荐那些还没被人潮淹没的餐厅——那种让你觉得是自己私下发掘的地方，而不是已经被各路美食账号刷烂了的网红店。整体氛围要有点像编辑精选的独立杂志，克制、低调，不像算法推荐那么生硬，配色可以用带点温度的哑光色调，留白要足够，让每一条推荐都显得经过认真筛选。每个地方都要用一种有趣的方式传达它的低人气特质——比如"本月只有12人到访过"——让用户感觉到的是专属感和亲密感，而不是冷清或被遗忘。视觉上希望有一种慢节奏、不紧不慢的滚动感，照片风格要像胶片感十足的真实记录，而不是那种过度饱和、摆拍痕迹明显的精修图。</v>
       </c>
       <c r="K167" t="str">
         <v/>
@@ -6279,7 +6279,7 @@
         <v>A ranked showcase of the top 10 local specialty dishes that feels like flipping through a beautifully curated food editorial — each dish gets its own full-bleed moody close-up photo, a short evocative line about what makes it special to the region, and a large elegant ranking number laid softly over the image. The overall vibe should feel warm and slightly cinematic, like a high-taste food journal rather than a plain numbered list, with a rich earthy color palette, generous breathing room between entries, and the dish name styled in a clean serif font that feels intentional and refined.</v>
       </c>
       <c r="J168" t="str">
-        <v>做一个当地特色菜肴Top 10的排行展示页面，整体感觉要像在翻阅一本精心策划的美食大片杂志——每道菜都有一张撑满全屏的氛围感特写大图，配一句简短又有意境的文案，说说这道菜对这片土地的独特意义，再把一个大气优雅的排名数字轻轻叠在图片上。整体基调要温暖、略带电影感，像一本有格调的美食手记，而不是普通的数字列表。色调用浓郁的大地色系，每个条目之间要有充裕的呼吸空间，菜名用一款简洁的衬线字体来排版，要有那种经过认真考量、精致克制的感觉。</v>
+        <v>做一个当地十大特色菜的排行展示页面，整体感觉要像是在翻阅一本精心策划的美食杂志大片——每道菜都有自己专属的满版氛围感特写照片，配上一句点出这道菜在当地独特魅力的意境短句，再把大号优雅的排名数字轻柔地叠压在图片上。整体风格要温暖、带点电影质感，像一本有品位的美食手记，而不是普通的编号清单。色调采用浓郁的大地色系，每个条目之间留出充足的呼吸空间，菜名用一款简洁的衬线字体来排版，看上去考究、有格调。</v>
       </c>
       <c r="K168" t="str">
         <v/>
@@ -6314,7 +6314,7 @@
         <v>Need a little word game where you get a bunch of scrambled letters and have to figure out what the real word is, like you see "LAPEP" and you have to rearrange it to spell "APPLE" before the timer runs out — I want it to feel like a quick fun challenge you can play on your phone when you're bored, maybe with different difficulty levels so easier words show up first and the harder longer ones come later, and after you guess right it should feel satisfying with some kind of little celebration animation or sound, nothing fancy just something that makes it feel alive.</v>
       </c>
       <c r="J169" t="str">
-        <v>做一个字母重排的小文字游戏，给你一堆打乱顺序的字母，让你猜出原来的单词是什么，比如看到"LAPEP"就要在计时结束前把它重新排列拼出"APPLE"——我希望整体感觉像是无聊的时候掏出手机随手玩一把的那种轻松小挑战，最好有不同难度等级，简单的短词先出，越到后面单词越长越难，猜对了之后要有点爽感，整一个小庆祝动画或者音效之类的，不用多炫，就是让游戏感觉有点活气就行。</v>
+        <v>想做一个字母重排的小文字游戏，就是给你一堆打乱顺序的字母，你要在计时结束前把它们重新排列成正确的单词，比如看到"LAPEP"就要拼出"APPLE"——整体感觉要像那种无聊的时候掏出手机随手玩两把的轻松小游戏，最好有难度分级，简单的短词先出，越到后面单词越长越难，猜对之后要有点成就感，来个小小的庆祝动画或者音效之类的，不用多炫，就是让游戏有点生气、有点反馈感就好。</v>
       </c>
       <c r="K169" t="str">
         <v/>
@@ -6346,10 +6346,10 @@
         <v>13206</v>
       </c>
       <c r="I170" t="str">
-        <v>Need a little hangman guessing game I can play on my phone where I can pick what kind of words to guess from — like animals, food, countries, that kind of thing — and also switch between English and Spanish so I can practice both languages a bit while having fun, the game should show the usual blank letter spots and a stick figure that slowly draws itself when I get letters wrong, and maybe a simple screen at the start where I choose the topic and language before the game begins.</v>
+        <v>Need a little hangman guessing game I can play on my phone where I can pick what kind of words to guess from — like animals, food, countries, that kind of thing — and also switch between English and Spanish so I can practice both languages a bit while having fun, the game should show the usual blank letter spots and a stick figure that slowly draws itself when I get letters wrong, and maybe a simple app at the start where I choose the topic and language before the game begins.</v>
       </c>
       <c r="J170" t="str">
-        <v>想做一个可以在手机上玩的简单猜单词游戏（就是那种经典的刽子手游戏），可以让玩家自己选择猜词的类别，比如动物、食物、国家之类的，另外还能在英语和西班牙语之间切换，这样玩的同时也能练练两门语言，游戏界面要有那种经典的字母横线空格，每猜错一次就一步一步把小火柴人画出来，最好在游戏开始前有一个简单的首页让玩家先选好主题和语言再进入游戏。</v>
+        <v>想做一个能在手机上玩的猜单词小游戏，就是那种经典的刽子手游戏，玩之前可以选择猜哪类词——比如动物、食物、国家之类的——还能在英语和西班牙语之间切换，这样玩的同时也能练练这两门语言，挺好的。游戏界面要有那种一格一格的字母空位，猜错了就一笔一笔把小火柴人画出来，另外最好在开始前有个简单的首页，让我先选好主题和语言再进入游戏。</v>
       </c>
       <c r="K170" t="str">
         <v/>
@@ -6381,10 +6381,10 @@
         <v>13102</v>
       </c>
       <c r="I171" t="str">
-        <v>Need a little daily riddle game where you get one fresh brain teaser each day and the answer doesn't just show up right away — instead there's a countdown ticking down, maybe like 60 seconds, and you have to sit with the question and think, and once the timer hits zero the answer slowly reveals itself on the screen, so you can't just rush to peek at it early, kind of forcing you to actually try before you see if you got it right.</v>
+        <v>Need a little daily riddle game where you get one fresh brain teaser each day and the answer doesn't just show up right away — instead there's a countdown ticking down, maybe like 60 seconds, and you have to sit with the question and think, and once the timer hits zero the answer slowly reveals itself on the app, so you can't just rush to peek at it early, kind of forcing you to actually try before you see if you got it right.</v>
       </c>
       <c r="J171" t="str">
-        <v>想做一个每日小谜题游戏，每天刷新一道脑筋急转弯，答案不会立刻显示出来——而是有一个倒计时，大概60秒，让你在这段时间里好好思考题目，等倒计时归零之后答案才会慢慢浮现在屏幕上，这样就没办法提前偷看，相当于强制你先认真想一想，再看自己有没有猜对。</v>
+        <v>想做一个每日脑筋急转弯小游戏，每天刷新一道新谜题，答案不能一上来就显示出来——而是要有一个倒计时，大概60秒那种，让你盯着题目好好想，等倒计时归零之后答案才慢慢浮现出来，这样就没办法偷懒直接跳过去看答案，相当于强迫你真的思考一下，再看自己有没有猜对。</v>
       </c>
       <c r="K171" t="str">
         <v/>
@@ -6416,10 +6416,10 @@
         <v>17444</v>
       </c>
       <c r="I172" t="str">
-        <v>A spinning prize wheel for little friend giveaway games where I get to type in my own prizes before each spin — so like I'd put in stuff like "free bubble tea" or "get to skip dishes tonight" or whatever random fun things fit the moment, and the wheel slices just fill themselves in based on however many things I added. Then someone taps to spin it, it slows down dramatically and lands on a slice, and a little celebration thing pops up showing what prize they won. Nothing fancy needed, just want it to feel fun and responsive on a phone screen, and I should be able to clear the list and start fresh whenever I want to run a new round.</v>
+        <v>A spinning prize wheel for little friend giveaway games where I get to type in my own prizes before each spin — so like I'd put in stuff like "free bubble tea" or "get to skip dishes tonight" or whatever random fun things fit the moment, and the wheel slices just fill themselves in based on however many things I added. Then someone taps to spin it, it slows down dramatically and lands on a slice, and a little celebration thing pops up showing what prize they won. Nothing fancy needed, just want it to feel fun and responsive on a phone app, and I should be able to clear the list and start fresh whenever I want to run a new round.</v>
       </c>
       <c r="J172" t="str">
-        <v>想做一个可以自定义奖品的转盘抽奖小游戏，用来给小伙伴搞福利活动——每次转之前我可以自己输入奖品，比如"免费一杯珍珠奶茶"、"今晚不用洗碗"之类的，填什么都行，反正是当下觉得好玩的东西就够了，转盘的扇形格子会根据我填了多少条奖品自动均分。然后有人点一下开始旋转，转盘慢慢减速，最后停在某一格上，屏幕弹出一个庆祝效果，告诉大家抽到了什么奖。不需要做得多精致，但在手机上用起来要有那种好玩、流畅的感觉，而且我随时可以清空奖品列表、重新填写，开始新一轮抽奖。</v>
+        <v>做一个可以自定义奖品的转盘抽奖小游戏，适合和朋友一起玩。每次转动之前我可以自己输入奖品内容，比如"免费一杯奶茶"啊、"今晚不用洗碗"之类的，想到什么填什么，填几个奖品转盘就自动分成几格，不用手动调。然后点一下开始转，转盘慢慢减速，有种悬念感，最后停在某一格上，弹出一个欢庆的小动画告诉大家中了什么奖。不需要做得多复杂，就是要在手机上用起来顺手、感觉好玩，另外每轮结束后我能一键清空列表、重新填奖品再来一轮就行。</v>
       </c>
       <c r="K172" t="str">
         <v/>
@@ -6451,10 +6451,10 @@
         <v>12345</v>
       </c>
       <c r="I173" t="str">
-        <v>Make a little app where a group of friends can all type in their names, then one by one each person taps a button to randomly draw who they're buying a gift for, and the result only shows on their own screen so nobody else accidentally sees it — I want it to feel fun like a lottery scratch thing, maybe with a little spinning or reveal animation when the name pops up, and it should make sure nobody draws themselves.</v>
+        <v>Make a little app where a group of friends can all type in their names, then one by one each person taps a button to randomly draw who they're buying a gift for, and the result only shows on their own app so nobody else accidentally sees it — I want it to feel fun like a lottery scratch thing, maybe with a little spinning or reveal animation when the name pops up, and it should make sure nobody draws themselves.</v>
       </c>
       <c r="J173" t="str">
-        <v>做一个小应用，一群朋友可以把各自的名字都输进去，然后每个人依次点一个按钮来随机抽签，看自己要给谁买礼物，抽到的结果只在自己屏幕上显示，这样其他人就不会不小心看到——我希望整个体验要有点刮彩票那种感觉，名字出现的时候最好有个旋转或者揭晓的小动画，而且要保证没人会抽到自己。</v>
+        <v>做一个小应用，让一群朋友可以把各自的名字都输进去，然后每个人依次点击按钮抽签，看自己要给谁买礼物，抽到的结果只在自己屏幕上显示，不让别人偷看——整体要有那种刮彩票的趣味感，名字出来的时候最好有个转盘转动或者揭晓的动画效果，另外要保证不能抽到自己。</v>
       </c>
       <c r="K173" t="str">
         <v/>
@@ -6489,7 +6489,7 @@
         <v>Build a little phone app where you dump in a bunch of people's names, pick how many teams you want, then hit a big button that does a fun shuffle animation and splits everyone into random groups — I want to use it for game nights with friends where we always argue about who goes with who, so it'd be nice if you can also reroll just one team without messing up the others, and maybe let me save the result so I can screenshot it easily.</v>
       </c>
       <c r="J174" t="str">
-        <v>做一个手机小应用，可以把一堆人的名字输进去，选好要分几组，然后点一个大按钮，触发一个好玩的洗牌动画，把所有人随机分成几队——我打算用来跟朋友玩游戏夜的时候分队，每次大家都要为分组吵来吵去，所以最好能支持单独重新随机某一组而不打乱其他组，另外要是能把结果保存下来方便截图就更好了。</v>
+        <v>想做一个手机小应用，可以把一堆朋友的名字输进去，选好要分几队，然后点一个大按钮，触发一个有趣的随机洗牌动画，把所有人分成随机小组——主要是用来跟朋友玩游戏的时候，每次都要为谁跟谁一队吵半天，所以要是能单独对某一队重新随机、又不打乱其他队就太好了，另外最好能把分组结果保存下来，方便直接截图。</v>
       </c>
       <c r="K174" t="str">
         <v/>
@@ -6524,7 +6524,7 @@
         <v>Need a match-3 color gem game where you tap or swap colorful gems on a grid and when three or more of the same color line up they burst and the gems above come falling down to fill the space, I want it to feel satisfying with little pop animations when gems disappear and maybe a score counter at the top so you can see how well you're doing, nothing too complicated just a clean fun little game I can open on my phone browser and play for a few minutes when I'm bored.</v>
       </c>
       <c r="J175" t="str">
-        <v>想做一个消消乐风格的彩色宝石小游戏，点击或滑动交换网格上的彩色宝石，当三个或三个以上同色宝石连成一排时就会爆开消除，上方的宝石随之掉落填补空位。希望消除的时候有那种小小的爆炸弹出动画，感觉要爽快一点，顶部加个分数计数器方便看自己打了多少分。不用太复杂，就是一个简单好玩的小游戏，能在手机浏览器上打开，无聊的时候随时玩几分钟就行。</v>
+        <v>想做一个消消乐风格的彩色宝石游戏，在格子上点击或滑动交换宝石，三个或三个以上相同颜色的宝石连成一排就会爆开消除，上方的宝石随即落下填补空位，希望消除的时候有那种爽快的弹出动画，顶部放个分数计数器方便看自己的成绩，不用太复杂，界面干净好看就行，主要是能在手机浏览器上打开，无聊的时候随手玩几分钟的那种小游戏。</v>
       </c>
       <c r="K175" t="str">
         <v/>
@@ -6556,10 +6556,10 @@
         <v>12447</v>
       </c>
       <c r="I176" t="str">
-        <v>Create a little snake game for my phone where the snake actually moves in a smooth curvy way instead of just snapping grid to grid, and I want the food to kind of pop up in random spots around the screen with a little bouncy animation so it feels alive — the snake should always be chasing after it and the trail behind should stay visible so you can see the path it's been taking, maybe make the body look like connected circles or bubbles rather than boring squares.</v>
+        <v>Create a little snake game for my phone where the snake actually moves in a smooth curvy way instead of just snapping grid to grid, and I want the food to kind of pop up in random spots around the app with a little bouncy animation so it feels alive — the snake should always be chasing after it and the trail behind should stay visible so you can see the path it's been taking, maybe make the body look like connected circles or bubbles rather than boring squares.</v>
       </c>
       <c r="J176" t="str">
-        <v>帮我做一个手机上的贪吃蛇游戏，蛇的移动要有流畅的曲线感，不是那种一格一格生硬跳动的方式，食物要随机蹦出来，出现的时候带个小弹跳动画，感觉像是活的一样——蛇要一直朝着食物追过去，身后留下的轨迹要持续显示出来，让玩家能看到它走过的路径，蛇身的造型最好用一串连在一起的圆形或者气泡，别用那种没意思的方块。</v>
+        <v>帮我做一个手机上的贪吃蛇小游戏，蛇移动的时候要有那种流畅的曲线感，不要一格一格硬跳的效果。食物要随机弹出在屏幕各个地方，出现的时候带个有弹性的小动画，看起来有生命力——蛇要一直追着食物跑，身后留下的轨迹要一直显示着，能让人看清楚它走过的路线。蛇身最好做成一串连在一起的圆形或者泡泡的样子，别用那种无聊的方块。</v>
       </c>
       <c r="K176" t="str">
         <v/>
@@ -6594,7 +6594,7 @@
         <v>Create a mobile Tetris game where colorful blocks fall from the top and you can move or rotate them to stack neatly at the bottom, and I want the blocks to look chunky and bright so it feels fun to play, plus make sure the speed picks up a little as you clear more rows so there's actually a challenge to keep going.</v>
       </c>
       <c r="J177" t="str">
-        <v>做一个手机版的俄罗斯方块游戏，彩色方块从顶部落下，可以左右移动和旋转来整齐地堆叠在底部，方块的样式要看起来粗壮饱满、颜色鲜艳，玩起来感觉轻快有趣，另外随着消除的行数增多，下落速度要逐渐加快，这样才有持续挑战的感觉。</v>
+        <v>做一个手机版俄罗斯方块游戏，彩色方块从顶部落下，玩家可以左右移动或旋转方块，把它们整齐地堆在底部，方块的样子要厚实鲜艳一点，让人觉得好玩有趣，另外消除的行数越多速度就要越来越快，这样才有继续玩下去的挑战感。</v>
       </c>
       <c r="K177" t="str">
         <v/>
@@ -6626,10 +6626,10 @@
         <v>26021</v>
       </c>
       <c r="I178" t="str">
-        <v>Sand drawing table that feels like tracing your fingers through warm desert sand — the surface should have that soft, slightly textured golden tone where untouched sand looks still and raked, and wherever you drag your finger it leaves those gentle raised-line marks you'd see in a real Zen garden tray. The erase gesture especially needs to feel right: a slow palm-swipe across the surface that smooths everything out in a rippling wave, like physically flattening the sand, not just a harsh wipe-clear — the whole screen should softly blur and resettle into a clean flat layer as if the grains are actually settling back down.</v>
+        <v>Sand drawing table that feels like tracing your fingers through warm desert sand — the surface should have that soft, slightly textured golden tone where untouched sand looks still and raked, and wherever you drag your finger it leaves those gentle raised-line marks you'd see in a real Zen garden tray. The erase gesture especially needs to feel right: a slow palm-swipe across the surface that smooths everything out in a rippling wave, like physically flattening the sand, not just a harsh wipe-clear — the whole app should softly blur and resettle into a clean flat layer as if the grains are actually settling back down.</v>
       </c>
       <c r="J178" t="str">
-        <v>做一个沙画桌，要那种手指划过温热沙漠沙粒时的真实触感——整个沙面呈现出柔和、略带颗粒质感的金色调，未触碰的区域安静平整，带着若有若无的耙痕纹理；手指拖动过的地方则留下那种细腻的凸起线条，就像真正的禅意沙盘里才有的那种痕迹。擦除手势尤其要做对：手掌在屏幕上缓缓横扫，沙面要像被真实地抚平一样，以一道涟漪般的波动把所有痕迹柔和地抹去，而不是粗暴地直接清空——整个画面应该轻轻模糊、慢慢沉淀，最终归于一层干净平整的沙面，仿佛沙粒真的在一粒一粒地重新落定。</v>
+        <v>做一个沙画桌应用，要让人感觉像是真的把手指划过温热的沙漠细沙——沙面整体要呈现那种柔软、略带颗粒质感的金色调，未触碰的区域看起来平静如经过精心耙梳，而手指划过的地方则留下那种细腻的凸起线痕，就像真实禅意沙盘里的纹路一样。尤其是清除手势必须做出真实的感觉：用手掌缓缓在沙面上扫过，带起一阵涟漪般向外扩散的波纹，把所有线条轻柔地抹平，像是真的在用手压平沙子，而不是生硬地"一键清空"——整个应用应该柔和地模糊、慢慢回落，呈现出一片干净平整的沙面，仿佛沙粒真的在一点一点沉落归位。</v>
       </c>
       <c r="K178" t="str">
         <v/>
@@ -6661,10 +6661,10 @@
         <v>20760</v>
       </c>
       <c r="I179" t="str">
-        <v>Kinetic sand that flows and shifts under your finger like the real thing — warm desert tones, think terracotta mixed with pale gold, the kind of muted earthy palette you'd see in an ASMR unboxing video. When you drag slowly it should pile up in soft ridges at the edges of your trail, and when you swipe fast it scatters and slowly settles back down with this satisfying heaviness to it. The texture should look almost powdery and velvety at the same time, like you can sense the weight just by looking at the screen. The background should be a clean off-white or soft stone color so the sand really pops, and the whole thing should feel calming and tactile — no flashy effects, just that deeply satisfying feeling of real kinetic sand responding to exactly how you touch it.</v>
+        <v>Kinetic sand that flows and shifts under your finger like the real thing — warm desert tones, think terracotta mixed with pale gold, the kind of muted earthy palette you'd see in an ASMR unboxing video. When you drag slowly it should pile up in soft ridges at the edges of your trail, and when you swipe fast it scatters and slowly settles back down with this satisfying heaviness to it. The texture should look almost powdery and velvety at the same time, like you can sense the weight just by looking at the app. The background should be a clean off-white or soft stone color so the sand really pops, and the whole thing should feel calming and tactile — no flashy effects, just that deeply satisfying feeling of real kinetic sand responding to exactly how you touch it.</v>
       </c>
       <c r="J179" t="str">
-        <v>做一个动感沙的交互效果，手指触摸时沙子要像真实动感沙一样流动和位移——颜色用温暖的沙漠色调，类似陶土混合浅金的感觉，就是那种在 ASMR 开箱视频里常见的低饱和度大地色系。慢慢拖动时，沙子应该在滑过的轨迹边缘堆积出柔软的小脊，快速划过时则四散开来，然后带着一种令人满足的沉重感缓缓沉降复位。质感要看起来既有粉质感又有丝绒感，那种光看屏幕就能感受到重量的视觉效果。背景用干净的米白或柔和的石灰色，让沙子的颜色更突出。整体氛围要平静、有触感，不要花哨的特效，就是那种真实动感沙精准响应你每一个触碰动作时带来的深度满足感。</v>
+        <v>做一个动感沙子的互动效果，手指滑过去的时候沙子要像真的一样流动和位移——颜色用暖沙漠调，类似赤陶土混浅金色那种，就是你在ASMR开箱视频里常见的那种低饱和大地色系。慢慢拖动的时候，沙子应该在轨迹边缘堆起柔软的小脊，快速划过去的话沙子会四散开来，然后带着那种很解压的沉重感慢慢沉落归位。质感要看起来既像粉状又像丝绒那种感觉，光看着就能感受到重量。背景用干净的米白色或者柔和的石灰色，让沙子更突出，整体氛围要有那种平静、触感真实的感觉——不要浮夸的特效，就是那种真实动感沙根据你的触摸力度和速度做出精准反应的深度解压感。</v>
       </c>
       <c r="K179" t="str">
         <v/>
@@ -6696,10 +6696,10 @@
         <v>18458</v>
       </c>
       <c r="I180" t="str">
-        <v>Create a squishy, gooey slime toy screen that looks incredibly satisfying to interact with — the slime should have this rich, translucent jelly-like quality with soft pastel or iridescent colors that shift slightly when you poke and drag it, almost like real slime catching light. It should feel genuinely tactile and stress-melting, where stretching it leaves these slow, glossy trails and poking it creates a little dimple that slowly bounces back, all with smooth buttery motion that never feels snappy or cheap. Keep the background minimal and moody — maybe a soft dark surface so the slime really glows and pops visually.</v>
+        <v>Create a squishy, gooey slime toy app that looks incredibly satisfying to interact with — the slime should have this rich, translucent jelly-like quality with soft pastel or iridescent colors that shift slightly when you poke and drag it, almost like real slime catching light. It should feel genuinely tactile and stress-melting, where stretching it leaves these slow, glossy trails and poking it creates a little dimple that slowly bounces back, all with smooth buttery motion that never feels snappy or cheap. Keep the background minimal and moody — maybe a soft dark surface so the slime really glows and pops visually.</v>
       </c>
       <c r="J180" t="str">
-        <v>做一个超解压的史莱姆玩具交互页面，看起来要让人忍不住想戳——史莱姆要有那种饱满通透的果冻质感，带着柔和的马卡龙色或彩虹光泽，戳和拖动的时候颜色会随着光线微微流转，几乎像真实的史莱姆在捕捉光芒。整体手感要真实到位、极度解压，拉伸时会留下缓缓消散的光泽拖尾，戳下去会出现一个小凹坑然后慢慢弹回来，所有动画都要顺滑绵软，绝不能有任何生硬或廉价的跳帧感。背景保持简洁、有氛围感——可以用深色磨砂质感的底面，让史莱姆的光泽和色彩真正发光出跳。</v>
+        <v>做一个捏起来软乎乎、黏糊糊的史莱姆玩具应用，看上去要极度治愈、让人忍不住一直戳——史莱姆本身要有那种饱满的半透明果冻质感，颜色用柔和的马卡龙色或者幻彩渐变色，戳它、拖拽它的时候颜色会微微流动变幻，就像真实史莱姆在光线下折射的效果。整体手感要真实到能解压，拉伸的时候拖出缓缓收拢的亮面丝光尾迹，戳下去会出现一个小凹坑然后慢慢弹回来，所有动画都要顺滑绵软，绝对不能有任何生硬或廉价的跳帧感。背景保持简洁、有点氛围感，可以用深色磨砂质感的底面，这样史莱姆的光泽和颜色能更突出、更有发光的感觉。</v>
       </c>
       <c r="K180" t="str">
         <v/>
@@ -6731,10 +6731,10 @@
         <v>18528</v>
       </c>
       <c r="I181" t="str">
-        <v>Build a photo editing experience that makes cropping feel intentional and beautiful — when I'm preparing a shot for my feed or stories, I want to switch between the perfect square format and the tall vertical format with just a gentle tap, and as I drag my photo around, a soft overlay should show me exactly where the safe zone is so faces and important details never get cut off awkwardly by the platform. The safe zone guide should feel like a delicate frosted frame rather than harsh grid lines, something that blends into the aesthetic without feeling clinical, and the whole cropping canvas should have a clean, airy look with the photo feeling like the star of the screen.</v>
+        <v>Build a photo editing experience that makes cropping feel intentional and beautiful — when I'm preparing a shot for my feed or stories, I want to switch between the perfect square format and the tall vertical format with just a gentle tap, and as I drag my photo around, a soft overlay should show me exactly where the safe zone is so faces and important details never get cut off awkwardly by the platform. The safe zone guide should feel like a delicate frosted frame rather than harsh grid lines, something that blends into the aesthetic without feeling clinical, and the whole cropping canvas should have a clean, airy look with the photo feeling like the star of the app.</v>
       </c>
       <c r="J181" t="str">
-        <v>想做一个照片裁剪体验，让整个操作过程既有仪式感又好看——在给发圈或者发故事准备素材的时候，我希望能轻轻一点就在完美的方形比例和竖版比例之间切换，拖动照片调整构图时，画面上应该浮现一层柔和的蒙层，清晰地告诉我哪里是安全区，这样人脸和关键细节就不会被平台莫名其妙地截掉。这个安全区引导框的感觉应该像一圈精致的磨砂边框，而不是那种生硬的网格线，要和整体氛围自然融合，不能显得太工具感，整个裁剪画布要干净、透气，让照片本身成为画面的绝对主角。</v>
+        <v>做一个让裁剪体验既有仪式感又好看的照片编辑功能——我在准备发动态或者发故事的时候，希望轻轻点一下就能在标准正方形比例和竖向长图格式之间切换，拖动照片调整位置时，画面上要有一层柔和的蒙版实时显示安全区范围，这样脸部和关键细节就不会被平台莫名其妙裁掉。这个安全区引导层要有磨砂玻璃边框的那种精致质感，不要那种硬邦邦的网格参考线，整体要融入画面氛围，不能显得太工具化、太冷硬；整个裁剪界面要干净、透气，让照片本身成为绝对的视觉主角。</v>
       </c>
       <c r="K181" t="str">
         <v/>
@@ -6769,7 +6769,7 @@
         <v>Create a photo collage builder that feels like flipping through a beautifully curated editorial spread, where you can pick from a set of pre-arranged grid layouts — some with one big hero photo and a few smaller ones tucked beside it, others with an even mosaic of equal-sized frames — and each template should feel intentional and magazine-worthy rather than generic. The overall mood should lean warm and minimal, with thin white borders between photos and a soft background so the images breathe, and when you tap a frame to swap in a photo the transition should feel smooth and satisfying, not abrupt.</v>
       </c>
       <c r="J182" t="str">
-        <v>做一个照片拼贴编辑器，整体感觉像在翻阅一本精心策划的时尚编辑大片——用户可以从一批预设好的网格版式中挑选，有的版式是一张大主图搭配几张小图错落排布在旁边，有的则是大小相等的方块整齐铺满整个画面，每套模板都要有设计感和杂志质感，而不是那种千篇一律的通用布局。整体氛围偏温暖、简约，照片之间用细白边间隔，背景柔和，让图片有充分的呼吸空间；点击某个框换入照片时，切换动效要顺滑流畅、有满足感，不能显得突兀生硬。</v>
+        <v>做一个照片拼贴编辑器，整体感觉像在翻阅一本精心策划的杂志大片。用户可以从一组预设的网格版式中选择——有的版式是一张大的主视觉图配几张小图错落排布在旁边，有的是均匀的马赛克网格、每个格子大小相同——每套模板都要有设计感、像杂志排版一样经过深思熟虑，而不是那种随便套用的通用样式。整体基调要偏温暖、简洁克制，照片之间用细白边隔开，背景要柔和，让画面有足够的留白和呼吸感。当用户点击某个格子替换照片时，切换动效要流畅、有质感，不能生硬突兀。</v>
       </c>
       <c r="K182" t="str">
         <v/>
@@ -6801,10 +6801,10 @@
         <v>18543</v>
       </c>
       <c r="I183" t="str">
-        <v>Make a photo tuning screen that feels really tactile and visual — like when you slide to adjust the brightness, contrast, or saturation, you can actually feel it in the image in real time, not just see a number change. The three sliders should each have their own warm, distinct look so they don't feel like copies of each other, maybe brightness feels light and airy, contrast feels sharp and bold, saturation feels rich and colorful. The whole thing should have a dark background so the photo being edited is the real star, and the controls underneath stay clean and minimal without getting in the way.</v>
+        <v>Make a photo tuning app that feels really tactile and visual — like when you slide to adjust the brightness, contrast, or saturation, you can actually feel it in the image in real time, not just see a number change. The three sliders should each have their own warm, distinct look so they don't feel like copies of each other, maybe brightness feels light and airy, contrast feels sharp and bold, saturation feels rich and colorful. The whole thing should have a dark background so the photo being edited is the real star, and the controls underneath stay clean and minimal without getting in the way.</v>
       </c>
       <c r="J183" t="str">
-        <v>做一个照片调节页面，要有很强的触感和视觉反馈——比如滑动调整亮度、对比度或饱和度的时候，效果要直接体现在图片上，让人真实感受到变化，而不只是看到一个数字在跳。三个滑块各自要有不同的风格，不能看起来像复制粘贴出来的，比如亮度滑块给人轻盈通透的感觉，对比度滑块锐利有力，饱和度滑块则浓郁鲜艳。整体用深色背景，让被编辑的照片成为绝对主角，下方的控件保持干净简洁，不抢镜。</v>
+        <v>做一个触感十足、视觉冲击力强的照片调色应用——拖动滑条调整亮度、对比度或饱和度的时候，那种变化要能直接"砸"在画面上，让人一眼就感受到，而不只是看着一个数字在跳。三个滑条各自要有独特的气质，不能长得像复制粘贴出来的：亮度那条给人轻盈通透的感觉，对比度那条犀利有力，饱和度那条浓郁鲜活。整体用深色背景，让被编辑的照片成为绝对主角，下方的控件保持干净克制，不抢戏。</v>
       </c>
       <c r="K183" t="str">
         <v/>
@@ -6839,7 +6839,7 @@
         <v>Create a business card front-and-back designer that feels like it's actually mine, not some generic corporate template factory — I want to flip between the front and back of the card and edit each side separately, with a clean canvas where I can place my name, a short line about what I do, and maybe a small personal logo or symbol, nothing more. No cheesy stock clipart, no pre-filled "CEO / Founder" placeholder nonsense, and absolutely no rainbow gradient packs — just a few tasteful color schemes and honest fonts that don't scream "I downloaded this from a free site." The whole point is that when someone looks at this card they see me, not a template.</v>
       </c>
       <c r="J184" t="str">
-        <v>做一个名片正反面设计工具，要让人感觉这张名片真的是我的，而不是从某个千篇一律的企业模板工厂套出来的——我想要能在正面和反面之间来回翻转，分别编辑两面的内容，画布要干净清爽，让我放上自己的名字、一句简短的职业介绍，以及一个小小的个人标志或图形符号，仅此而已。不要那些土气的剪贴画，不要预填好的"CEO / 创始人"之类的占位废话，更不要什么彩虹渐变配色包——只需要几套有品位的配色方案，加上几款不会让人一眼看出"这是从免费网站下的"的正经字体。这个工具存在的意义就是：别人拿到这张名片，看到的是我这个人，而不是一套模板。</v>
+        <v>做一个名片正反面设计工具，要让人感觉这张卡片真的是我自己的，而不是从什么通用企业模板工厂批量生产出来的——我希望能在正面和反面之间来回翻转，分别单独编辑每一面，有一块干净的画布让我放上自己的名字、一行简短的职业描述，以及一个小小的个人标志或图形，仅此而已。不要那些土气的剪贴画，不要预填好的"CEO / 创始人"之类的占位废话，更不要什么彩虹渐变配色包——只要几套有品位的配色方案和看起来不廉价的字体，别让人一眼看出这是从免费网站下载的东西。整件事的重点就是：别人拿到这张名片，看到的是我这个人，而不是一套模板。</v>
       </c>
       <c r="K184" t="str">
         <v/>
@@ -6874,7 +6874,7 @@
         <v>Make a wedding invitation card creator that feels personal and handcrafted, not like some cookie-cutter template factory — I want a small set of maybe four or five elegant layouts I can actually customize with our names, date, and a short line of text, and the font choices should lean traditional and warm, not trendy sans-serif stuff. No stock photo backgrounds, no cartoon illustrations, no confetti animations — just clean, tasteful design with maybe a soft floral border option. It should feel like something I made myself, not something that came off an assembly line.</v>
       </c>
       <c r="J185" t="str">
-        <v>做一个婚礼请柬制作工具，要有那种亲手制作的温度感，不要那种流水线模板的感觉——我想要四五个精致的版式可以选，能自定义我们的名字、日期和一句简短的文字，字体要偏传统、有温度的那种，别用什么时髦的无衬线体。不要素材库里的背景图，不要卡通插画，不要撒纸屑的动效——整体设计要干净、有品位，可以有一个柔和的花卉边框选项。整个东西要让人感觉是我自己用心做出来的，不是从流水线上批出来的。</v>
+        <v>做一个婚礼请柬制作工具，要有那种亲手设计的温馨感，而不是流水线出来的千篇一律模板——我想要四五种精致的排版样式，能真正自定义我们的名字、日期和一句简短的文字，字体要偏传统、有温度，不要那种时髦的无衬线风格。不要素材库里的背景图，不要卡通插画，不要撒纸屑的动画效果——就是干净、有品味的设计，可以加一个淡雅的花卉边框选项。整体感觉要像是我自己亲手做的，不像是机器批量生产出来的。</v>
       </c>
       <c r="K185" t="str">
         <v/>
@@ -6906,10 +6906,10 @@
         <v>14734</v>
       </c>
       <c r="I186" t="str">
-        <v>Create a mobile page for making animated Instagram story templates that feels personal and hand-crafted — I want a small curated set of real aesthetic styles like film grain, soft light, and bold editorial type, where I can swap in my own text and tweak the color palette myself, but do NOT load it up with generic influencer gradients or trendy Y2K stickers that everyone else is using, and absolutely no watermark or tool branding stamped on the output, because the whole point is that it looks like it came from me, not from some template factory.</v>
+        <v>Create a mobile app for making animated Instagram story templates that feels personal and hand-crafted — I want a small curated set of real aesthetic styles like film grain, soft light, and bold editorial type, where I can swap in my own text and tweak the color palette myself, but do NOT load it up with generic influencer gradients or trendy Y2K stickers that everyone else is using, and absolutely no watermark or tool branding stamped on the output, because the whole point is that it looks like it came from me, not from some template factory.</v>
       </c>
       <c r="J186" t="str">
-        <v>做一个移动端页面，用来制作有动效的 Instagram Story 模板，整体感觉要个人化、有手作质感——我想要一套精心挑选的真实美学风格，比如胶片颗粒、柔光效果和粗体杂志排版，让我能替换成自己的文字，也能自己调整配色，但千万不要塞一堆烂大街的网红渐变色或者那种人人都在用的 Y2K 贴纸，更不能在导出的内容上打水印或者任何工具品牌标识，因为我要的就是看起来像我自己做的东西，而不是从某个模板流水线上批量生产出来的。</v>
+        <v>做一个用来制作动态 Instagram Story 模板的手机应用，整体感觉要有个人风格、像是手工打造的那种——我想要一小套精选的真实美学风格，比如胶片颗粒感、柔和光线、还有那种硬朗的编辑排版，让我可以换上自己的文字、自己调整配色，但绝对不要塞那些烂大街的网红渐变色或者流行的Y2K贴纸，别人都在用的那套我不要，而且输出的成品上一定不能有任何水印或者工具品牌标记，因为我做这个的意义就在于看起来是我自己的东西，而不是从什么模板工厂批量出来的。</v>
       </c>
       <c r="K186" t="str">
         <v/>
@@ -6941,10 +6941,10 @@
         <v>11264</v>
       </c>
       <c r="I187" t="str">
-        <v>Make a listening experience screen for an audiobook app that feels warm and immersive, like settling into a cozy reading nook — the chapter list should feel like flipping through a beautifully typeset table of contents, with each chapter title shown in an elegant serif font alongside a subtle progress indicator that glows softly to show how far you've listened, and the player controls at the bottom should have that calm, minimal feel with a muted earthy color palette, nothing too flashy, just a gentle current-chapter highlight and smooth transitions when you move between chapters.</v>
+        <v>Make a listening experience app for an audiobook app that feels warm and immersive, like settling into a cozy reading nook — the chapter list should feel like flipping through a beautifully typeset table of contents, with each chapter title shown in an elegant serif font alongside a subtle progress indicator that glows softly to show how far you've listened, and the player controls at the bottom should have that calm, minimal feel with a muted earthy color palette, nothing too flashy, just a gentle current-chapter highlight and smooth transitions when you move between chapters.</v>
       </c>
       <c r="J187" t="str">
-        <v>帮我做一个有声书应用的收听页面，整体氛围要温暖沉浸，像窝在一个惬意的阅读角落里的感觉——章节列表要有翻阅精心排版目录的质感，每个章节标题用优雅的衬线字体展示，旁边配一个细腻的进度指示器，用柔和的微微发光效果来呈现当前的收听进度；底部的播放控件要保持那种安静、克制的风格，色调用低饱和度的大地色系，不要太张扬，只需要对当前播放章节做一个轻柔的高亮处理，切换章节时有顺滑自然的过渡动画就好。</v>
+        <v>做一个有声书的听书页面，整体氛围要温暖、有沉浸感，像窝在一个舒适的阅读角落里那种感觉——章节列表要有一种在翻阅精心排版的目录的质感，每个章节标题用优雅的衬线字体展示，旁边配一个细腻的进度指示器，用柔和的发光效果来显示当前听到了哪里；底部的播放控件要保持那种安静、克制的风格，色调用低饱和的大地色系，不要太抢眼，只需要一个轻柔的当前章节高亮，以及在章节切换时有丝滑的过渡动画就好。</v>
       </c>
       <c r="K187" t="str">
         <v/>
@@ -6976,10 +6976,10 @@
         <v>10551</v>
       </c>
       <c r="I188" t="str">
-        <v>Need a karaoke-style lyrics display that feels like those polished music apps where the current line glows and gradually fills with color as the song plays — the kind where unplayed lines sit in a soft muted tone and the active one pops with a warm highlight that sweeps across word by word in sync with the beat, so it almost feels like the text is singing along with the music rather than just sitting there static on screen.</v>
+        <v>Need a karaoke-style lyrics display that feels like those polished music apps where the current line glows and gradually fills with color as the song plays — the kind where unplayed lines sit in a soft muted tone and the active one pops with a warm highlight that sweeps across word by word in sync with the beat, so it almost feels like the text is singing along with the music rather than just sitting there static on app.</v>
       </c>
       <c r="J188" t="str">
-        <v>想做一个卡拉OK风格的歌词展示效果，要有那种精致音乐App的质感——当前歌词行随着歌曲播放会发光，并逐渐被颜色填满；未播放的歌词行以柔和低饱和的色调显示，而正在播放的那行则用温暖的高亮色突出显示，高亮效果随着节拍逐字扫过，让人感觉文字本身在跟着音乐一起"唱"，而不是静静地摆在那里。</v>
+        <v>想做一个卡拉OK风格的歌词显示效果，要有那种精致音乐App的感觉——当前歌词行会发光，并随着歌曲播放逐渐被颜色填满，未播放的歌词行呈现柔和的低饱和色调，而正在播放的那行则用温暖的高亮色逐字扫过，节奏感要跟上音乐的节拍，整体看起来就像文字在跟着音乐一起"唱"，而不是死板地贴在屏幕上。</v>
       </c>
       <c r="K188" t="str">
         <v/>
@@ -7011,10 +7011,10 @@
         <v>10251</v>
       </c>
       <c r="I189" t="str">
-        <v>Make a screenplay writing page that feels like you're working inside a real film script — clean, professional, almost like the actual Final Draft look but on your phone, with that warm off-white paper texture as the background and a classic monospaced typewriter font so everything feels cinematic and intentional. The layout should automatically shift the text into proper script format depending on whether you're typing a scene heading, character name, or dialogue, so it naturally guides you into the right structure without you having to think about it, and there should be a subtle side panel where you can see all your scenes listed so you can jump around easily.</v>
+        <v>Make a screenplay writing app that feels like you're working inside a real film script — clean, professional, almost like the actual Final Draft look but on your phone, with that warm off-white paper texture as the background and a classic monospaced typewriter font so everything feels cinematic and intentional. The layout should automatically shift the text into proper script format depending on whether you're typing a scene heading, character name, or dialogue, so it naturally guides you into the right structure without you having to think about it, and there should be a subtle side panel where you can see all your scenes listed so you can jump around easily.</v>
       </c>
       <c r="J189" t="str">
-        <v>做一个剧本写作页面，要让人感觉真的在写电影剧本那种——干净、专业，有点像Final Draft的风格，但是在手机上用的，背景用那种温暖的米白色纸张质感，配上经典的等宽打字机字体，整体看起来有电影感、有仪式感。排版要能根据你当前输入的内容自动切换格式，不管是场景说明、角色名还是对白，都能自动对齐到正确的剧本格式，不用自己去想排版的事，自然而然地引导你写出规范的结构。另外侧边要有一个低调的面板，把所有场景列出来，方便随时跳转。</v>
+        <v>做一个剧本创作应用，整体感觉就像在真正的电影剧本里写作一样——干净、专业，有点像 Final Draft 的风格，但是是手机版的，背景用那种温暖的米白色纸张质感，字体用经典的等宽打字机字体，让整个界面看起来充满电影感和仪式感。排版要能根据你当前输入的内容自动切换格式，不管是场景标题、角色名还是对白，都能自动对齐到正确的剧本格式，让你不用费心去想格式的问题，自然而然地就写进正确的结构里了。另外侧边要有一个低调的场景列表面板，可以看到所有场景，方便随时跳转。</v>
       </c>
       <c r="K189" t="str">
         <v/>
@@ -7049,7 +7049,7 @@
         <v>Create a podcast episode outline builder that feels like a beautifully curated editorial notebook — think warm cream background, soft serif headings, and sections that stack neatly like journal pages, giving the whole thing that calm, intentional energy of a well-designed indie publication. Each episode should have a title and mood-note area at the top, followed by clearly spaced segments where I can write in talking points, timestamps, or guest names, and the spacing between sections should feel generous enough that it never looks crowded or rushed. The overall vibe should make someone actually want to sit down and plan their episode rather than dread the process.</v>
       </c>
       <c r="J190" t="str">
-        <v>做一个播客单集大纲编辑器，整体氛围要像一本精心设计的编辑手账——温暖的米白色背景、柔和的衬线字体标题，各个板块像日记页面一样整齐叠落，透出那种独立出版物特有的从容与克制感。每一集顶部要有标题和情绪备注区，下方是间距宽松的分段区域，可以填写话题要点、时间戳或嘉宾名字，段落之间的留白要足够充裕，绝对不能显得拥挤或仓促。整体的感觉要让人真的想坐下来好好规划一期节目，而不是一打开就觉得头疼。</v>
+        <v>做一个播客单集大纲编辑器，整体氛围要像一本精心设计的编辑手记——暖奶油色背景、柔和的衬线字体标题，各个版块像日记页面一样整齐叠放，透出那种独立刊物才有的从容与克制感。每集内容的顶部留有标题栏和情绪备注区，下方是间距宽松的分段区域，可以填写谈话要点、时间戳或嘉宾姓名，段落之间的留白要足够充裕，绝对不能显得拥挤或仓促。整个页面的气质要让人真正愿意坐下来好好规划一期节目，而不是一打开就想逃。</v>
       </c>
       <c r="K190" t="str">
         <v/>
@@ -7081,7 +7081,7 @@
         <v>Need a simple news reading app for my phone where I can scroll through a bunch of articles from topics I actually care about, like tech stuff and food and maybe local things, and the articles should show up as little cards with a picture and a short title so I can quickly decide if I want to read more, and there should be some way to save the ones I like so I can come back to them later without losing them when I close the app.</v>
       </c>
       <c r="J191" t="str">
-        <v>想做一个手机上用的简单新闻阅读应用，可以刷各种我感兴趣的话题里的文章，比如科技、美食，还有本地资讯之类的，文章要以卡片的形式展示，每张卡片有一张配图和一个简短的标题，这样我能快速判断要不要点进去看，另外还需要有收藏功能，把喜欢的文章存起来，关掉应用之后再打开也不会丢，方便随时回来看。</v>
+        <v>想做一个手机上用的简单新闻阅读应用，可以刷各种我感兴趣的话题，比如科技、美食，还有本地资讯之类的，文章要以卡片形式展示，带封面图和简短标题，让我能快速判断要不要点进去看，另外要有收藏功能，把喜欢的文章存起来，关掉应用也不会丢失。</v>
       </c>
       <c r="K191" t="str">
         <v/>
@@ -7110,10 +7110,10 @@
         <v>11012</v>
       </c>
       <c r="I192" t="str">
-        <v>Create a simple news feed page for my phone app where I can browse through short articles one by one, each card shows the headline and a small picture on the side, and there's a little category label like "tech" or "food" so I know what kind of story it is before I tap in — I mainly want it to feel easy to scroll through during a lunch break without getting overwhelmed by too much stuff on screen at once.</v>
+        <v>Create a simple news feed app for my phone app where I can browse through short articles one by one, each card shows the headline and a small picture on the side, and there's a little category label like "tech" or "food" so I know what kind of story it is before I tap in — I mainly want it to feel easy to scroll through during a lunch break without getting overwhelmed by too much stuff on app at once.</v>
       </c>
       <c r="J192" t="str">
-        <v>帮我做一个手机应用的简单新闻流页面，可以一条一条地浏览短文章，每张卡片左边或右边配一张小图，标题旁边有个小标签显示分类，比如"科技"或"美食"，这样点进去之前就能知道是什么类型的内容——主要想让整体看起来清爽不拥挤，适合午休时随手刷刷，不想屏幕上塞太多东西。</v>
+        <v>帮我做一个手机用的简单新闻流页面，可以一条一条浏览短文章，每张卡片左边或右边放一张小图，旁边显示标题，还有一个小标签标注"科技"或"美食"这类分类，让我点进去之前就知道是什么类型的内容——主要想要那种午休时随手刷、不会觉得信息量太大、看着很轻松的感觉。</v>
       </c>
       <c r="K192" t="str">
         <v/>
@@ -7148,7 +7148,7 @@
         <v>Create a reading experience where you can press and hold on any sentence in an article and it glows with a soft amber highlight, then a small elegant card floats up showing just that quoted line in a beautiful serif font with the article title beneath it — the whole thing feels like those aesthetic quote screenshots people share on Instagram, warm and editorial, not cold and techy, so when someone saves or shares it the image already looks polished and intentional without any extra effort.</v>
       </c>
       <c r="J193" t="str">
-        <v>做一个阅读体验：长按文章中的任意一句话，那句话会泛出柔和的琥珀色光晕，然后一张小巧精致的卡片从下方轻轻浮起，用漂亮的衬线字体只呈现那句被选中的文字，下方配上文章标题——整体氛围就像那些在 Instagram 上广为流传的美学引用截图，温暖、有编辑质感，绝不冷硬科技感，这样用户在保存或分享时，图片本身就已经精致、有格调，完全不需要再做任何额外的处理和美化。</v>
+        <v>做一个阅读体验，长按文章里的任意一句话，那句话就会亮起柔和的琥珀色高亮，然后一张小巧精致的卡片从下方浮现出来，只展示那句引文，用漂亮的衬线字体排版，下方附上文章标题——整体感觉就像那种大家在 ins 上分享的美感语录截图，温暖、有编辑质感，不要那种冷冰冰的科技风，这样用户保存或分享的时候，图片本身已经很精致、很有设计感了，完全不需要再做任何额外处理。</v>
       </c>
       <c r="K193" t="str">
         <v/>
@@ -7180,10 +7180,10 @@
         <v>9574</v>
       </c>
       <c r="I194" t="str">
-        <v>Make a reading experience where tapping on a highlighted term inside an article brings up a soft little definition card that feels like it belongs in an editorial magazine — something that gently lifts off the page without covering the whole screen, with clean typography, maybe a subtle warm tint to set it apart from the article background, and a quiet fade-in that doesn't feel jarring or mechanical.</v>
+        <v>Make a reading experience where tapping on a highlighted term inside an article brings up a soft little definition card that feels like it belongs in an editorial magazine — something that gently lifts off the app without covering the whole app, with clean typography, maybe a subtle warm tint to set it apart from the article background, and a quiet fade-in that doesn't feel jarring or mechanical.</v>
       </c>
       <c r="J194" t="str">
-        <v>做一个阅读体验，点击文章里高亮的词汇时，会弹出一张小小的释义卡片，感觉像是属于精品杂志那种调性——轻轻从页面上浮起来，不会遮住整个屏幕，排版干净利落，背景可以带一点微微的暖色调，和文章底色区分开来，入场动效是那种轻柔的淡入，不突兀，不生硬。</v>
+        <v>做一个阅读体验，点击文章里高亮的词汇时，会弹出一个轻柔的释义小卡片，整体感觉像精品杂志里的设计——卡片从页面里轻轻浮起来，但不会遮住整个界面，字体要干净好看，背景可以带一点微微的暖色调，和文章底色区分开，出现的时候用那种不突兀、不机械的淡入动效，整体要很安静、很克制。</v>
       </c>
       <c r="K194" t="str">
         <v/>
@@ -7215,10 +7215,10 @@
         <v>11455</v>
       </c>
       <c r="I195" t="str">
-        <v>Build a feature in my news app where I can connect my email account and have all my newsletter subscriptions automatically pulled in so I can read them inside the app, and I want a few specific things: there should be a clear list view showing each newsletter by sender name and date received, unread ones should be visually marked so I can tell at a glance what I haven't gotten to yet, and when I tap one to open it the content should display cleanly without all the extra email clutter around it.</v>
+        <v>Build a tool in my news app where I can connect my email account and have all my newsletter subscriptions automatically pulled in so I can read them inside the app, and I want a few specific things: there should be a clear list app showing each newsletter by sender name and date received, unread ones should be visually marked so I can tell at a glance what I haven't gotten to yet, and when I tap one to open it the content should display cleanly without all the extra email clutter around it.</v>
       </c>
       <c r="J195" t="str">
-        <v>在我的新闻应用里做一个功能，让我可以绑定邮箱账号，然后自动把我订阅的所有Newsletter都同步进来，这样我就能直接在应用里阅读了。具体有几个要求：需要有一个清晰的列表视图，按发件人名称和收件日期显示每一封Newsletter；未读的要有明显的视觉标记，让我一眼就能看出哪些还没读过；点开某一封后，内容要干净地呈现出来，不要带那些多余的邮件界面元素。</v>
+        <v>在我的新闻应用里做一个功能，让我可以绑定邮箱账号，自动把所有订阅的Newsletter都同步进来，直接在应用内阅读。具体有几个要求：要有一个清晰的列表页，按发件人名称和收件日期展示每封Newsletter；未读的要有明显的视觉标记，让我一眼就能看出哪些还没看；点进去之后，内容要干净地呈现出来，不要带着原始邮件那些乱七八糟的东西。</v>
       </c>
       <c r="K195" t="str">
         <v/>
@@ -7250,10 +7250,10 @@
         <v>12487</v>
       </c>
       <c r="I196" t="str">
-        <v>Need a simple screen where I can add an RSS feed just by pasting in a URL, and it should check right away whether the link actually works before saving it — if something's wrong with the address, just show a clear message so I know to fix it. I also want it to pull in the feed name automatically so I don't have to type it myself, but still let me rename it if I want to keep things tidy in my list.</v>
+        <v>Need a simple app where I can add an RSS feed just by pasting in a URL, and it should check right away whether the link actually works before saving it — if something's wrong with the address, just show a clear message so I know to fix it. I also want it to pull in the feed name automatically so I don't have to type it myself, but still let me rename it if I want to keep things tidy in my list.</v>
       </c>
       <c r="J196" t="str">
-        <v>想做一个简单的页面，让我可以直接粘贴 URL 来添加 RSS 订阅源，粘贴之后要立刻验证这个链接是否有效，再保存——如果地址有问题，就给我一个清晰的提示，让我知道该怎么改。另外希望能自动抓取订阅源的名称，不用我手动输入，但如果我想自己改个名字方便管理列表，也要支持手动重命名。</v>
+        <v>想做一个简单的应用，只需要把 RSS 链接粘贴进去就能添加订阅源，粘贴后要立刻验证这个链接是否有效，如果地址有问题就直接显示一条清晰的提示，让我知道需要修正。另外希望能自动抓取订阅源的名称，不用我手动输入，但也要允许我自己重命名，方便把列表整理得整洁一些。</v>
       </c>
       <c r="K196" t="str">
         <v/>
@@ -7288,7 +7288,7 @@
         <v>Need a quick way to just type in a journalist or author's name and pull up everything they've written, because right now I have to scroll through endless articles guessing who wrote what and it wastes so much time — the search should actually recognize the person's full name and show all their pieces in one place, and ideally I can tap on a name directly from any article to see more from that same writer without having to go back and search all over again.</v>
       </c>
       <c r="J197" t="str">
-        <v>想要一个能直接输入记者或作者姓名、然后把他们写过的所有文章都列出来的功能，因为现在得没完没了地刷文章列表、靠猜来判断是谁写的，太浪费时间了——搜索要能准确识别人名全称，把这个人的所有稿件集中展示在一个页面，最好还能在任意一篇文章里直接点作者名字，就能跳转看这位作者的更多内容，不用再退出去重新搜一遍。</v>
+        <v>想要一个能直接输入记者或作者姓名、然后把他们所有文章都汇总显示出来的功能，因为现在每次都要在一堆文章里滚来滚去猜是谁写的，太浪费时间了——搜索要能准确识别人名全称，把这个人写的所有内容集中展示在一个地方，最好还能在任意一篇文章里直接点作者名字，就能看到这位作者的其他作品，不用再返回去重新搜索一遍。</v>
       </c>
       <c r="K197" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>Need a quick way to filter news by source or outlet name so I don't have to scroll through a million articles from sites I don't trust or just don't care about — basically I want to pick which outlets show up in my feed and block the ones I hate, and it should remember my choices so I don't have to redo it every single time I open the app.</v>
       </c>
       <c r="J198" t="str">
-        <v>想要一个能按新闻来源或媒体名称筛选的功能，这样就不用在一堆我不信任或根本不想看的网站文章里翻来翻去了——说白了就是能自己选哪些媒体出现在我的信息流里，不想看的直接屏蔽掉，而且要记住我的设置，不然每次打开应用都得重新配置一遍太烦了。</v>
+        <v>想要能按新闻来源或媒体名称快速过滤内容，不想每次都刷一堆我不信任或根本不感兴趣的网站的文章——就是希望能自己选择哪些媒体出现在我的信息流里，然后把那些不想看的直接屏蔽掉，而且要能记住我的设置，不然每次打开app都要重新配置一遍太烦了。</v>
       </c>
       <c r="K198" t="str">
         <v/>
@@ -7355,10 +7355,10 @@
         <v>14060</v>
       </c>
       <c r="I199" t="str">
-        <v>Create a size guide page where shoppers can fill in their own body measurements — things like height, weight, chest, waist, and hips — and get a clear size recommendation for the item they're looking at. Each input field should be labeled so it's obvious what to enter and what unit to use, and once all the numbers are filled in, the page should show the suggested size at the bottom along with a simple side-by-side comparison of the person's measurements versus the brand's size chart so they can double-check before deciding.</v>
+        <v>Create a size guide app where shoppers can fill in their own body measurements — things like height, weight, chest, waist, and hips — and get a clear size recommendation for the item they're looking at. Each input field should be labeled so it's obvious what to enter and what unit to use, and once all the numbers are filled in, the app should show the suggested size at the bottom along with a simple side-by-side comparison of the person's measurements versus the brand's size chart so they can double-check before deciding.</v>
       </c>
       <c r="J199" t="str">
-        <v>做一个尺码推荐页面，让顾客可以输入自己的身体数据——比如身高、体重、胸围、腰围和臀围——然后根据他们正在浏览的商品给出明确的尺码建议。每个输入框都要有清晰的标签，注明该填什么、用什么单位，等所有数据填完之后，页面底部显示推荐尺码，同时以左右对比的形式展示用户的实际尺寸和品牌尺码表的对应数据，方便顾客下单前自行核对。</v>
+        <v>做一个尺码推荐工具，让购物者可以输入自己的身体数据——比如身高、体重、胸围、腰围和臀围——然后根据他们正在看的商品给出明确的尺码建议。每个输入框都要有清晰的标签，说明该填什么内容以及使用什么单位。填完所有数据后，页面底部显示推荐尺码，同时提供一个简洁的对照表，把用户的实际测量数据和品牌尺码表并排展示，方便他们在下单前自行核对。</v>
       </c>
       <c r="K199" t="str">
         <v/>
@@ -7390,10 +7390,10 @@
         <v>12151</v>
       </c>
       <c r="I200" t="str">
-        <v>Build a mobile shopping cart page where I can move things I'm not buying right now into a "save for later" list with just one tap, because I hate having to delete stuff and then go search for it all over again when I actually want to buy it — the saved items should just sit there below the cart so I can see them and move them back whenever I'm ready to check out.</v>
+        <v>Build a mobile shopping cart app where I can move things I'm not buying right now into a "save for later" list with just one tap, because I hate having to delete stuff and then go search for it all over again when I actually want to buy it — the saved items should just sit there below the cart so I can see them and move them back whenever I'm ready to check out.</v>
       </c>
       <c r="J200" t="str">
-        <v>做一个手机端的购物车页面，我想一键把暂时不买的东西移到"留着以后买"的清单里，因为我特别烦每次删掉之后还要重新去搜——那些存起来的商品就放在购物车下面，随时能看到，等想结账的时候直接移回来就行。</v>
+        <v>做一个手机购物车应用，让我能一键把暂时不想买的东西移到「稍后购买」列表里——我最烦的就是把商品删掉，等真正想买的时候又得重新搜一遍。保存的商品就放在购物车下面，我随时能看到，准备结算的时候直接移回来就行了。</v>
       </c>
       <c r="K200" t="str">
         <v/>
@@ -7425,10 +7425,10 @@
         <v>13619</v>
       </c>
       <c r="I201" t="str">
-        <v>Build a page that shows me exactly where my package is right now using one of those step-by-step timeline things going from top to bottom, so I can stop refreshing five different apps just to find out if my stuff is still sitting in some warehouse — I want each step to show the time and a short description of what happened, and the current step should be highlighted so I can tell at a glance without actually reading everything.</v>
+        <v>Build an app that shows me exactly where my package is right now using one of those step-by-step timeline things going from top to bottom, so I can stop refreshing five different apps just to find out if my stuff is still sitting in some warehouse — I want each step to show the time and a short description of what happened, and the current step should be highlighted so I can tell at a glance without actually reading everything.</v>
       </c>
       <c r="J201" t="str">
-        <v>帮我做一个能实时显示包裹当前位置的页面，用那种从上到下的步骤时间轴来展示物流进度，这样我就不用一直刷好几个不同的APP去查我的东西是不是还压在某个仓库里——每个节点要显示时间和一句简短的状态描述，当前所在的步骤要高亮标出来，让我一眼就能看出进度到哪了，不用逐条去读。</v>
+        <v>做一个能实时显示我包裹当前位置的应用，用那种从上到下一步一步的时间轴来展示物流进度，这样我就不用反复刷好几个不同的App来确认我的东西是不是还压在某个仓库里——每个节点要显示时间和一句简短的状态说明，当前所在的步骤要高亮突出，让我一眼就能看出来，不用挨个去读所有内容。</v>
       </c>
       <c r="K201" t="str">
         <v/>
